--- a/docs/design/ACSMS-SCR-003/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_単価マスタ登録画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-003/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_単価マスタ登録画面_V1.0.xlsx
@@ -1767,7 +1767,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2193,7 +2193,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2692,7 +2692,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>TANKA_NOT_FOUND</t>
+          <t>NOT_FOUND</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -3008,7 +3008,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3345,7 +3345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK84"/>
+  <dimension ref="A1:AK86"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3506,7 +3506,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3860,7 +3860,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -4554,7 +4554,7 @@
       <c r="C32" s="38" t="n"/>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>tanka_type_label</t>
+          <t>tanka_code</t>
         </is>
       </c>
       <c r="E32" s="10" t="n"/>
@@ -4598,7 +4598,7 @@
       <c r="AE32" s="11" t="n"/>
       <c r="AF32" s="19" t="inlineStr">
         <is>
-          <t>tanka_typeのラベル</t>
+          <t>単価コード</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -4614,7 +4614,7 @@
       <c r="C33" s="38" t="n"/>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>tanka_code</t>
+          <t>tanka_name</t>
         </is>
       </c>
       <c r="E33" s="10" t="n"/>
@@ -4658,7 +4658,7 @@
       <c r="AE33" s="11" t="n"/>
       <c r="AF33" s="19" t="inlineStr">
         <is>
-          <t>単価コード</t>
+          <t>単価名</t>
         </is>
       </c>
       <c r="AG33" s="10" t="n"/>
@@ -4674,7 +4674,7 @@
       <c r="C34" s="38" t="n"/>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>tanka_name</t>
+          <t>kingaku_zeikomi</t>
         </is>
       </c>
       <c r="E34" s="10" t="n"/>
@@ -4687,7 +4687,7 @@
       <c r="L34" s="11" t="n"/>
       <c r="M34" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N34" s="10" t="n"/>
@@ -4707,7 +4707,7 @@
       <c r="X34" s="11" t="n"/>
       <c r="Y34" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z34" s="10" t="n"/>
@@ -4718,7 +4718,7 @@
       <c r="AE34" s="11" t="n"/>
       <c r="AF34" s="19" t="inlineStr">
         <is>
-          <t>単価名</t>
+          <t>税込金額（円）</t>
         </is>
       </c>
       <c r="AG34" s="10" t="n"/>
@@ -4734,7 +4734,7 @@
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>kingaku_zeikomi</t>
+          <t>kingaku_zeinuki</t>
         </is>
       </c>
       <c r="E35" s="10" t="n"/>
@@ -4778,7 +4778,7 @@
       <c r="AE35" s="11" t="n"/>
       <c r="AF35" s="19" t="inlineStr">
         <is>
-          <t>税込金額（円）</t>
+          <t>税抜金額（円）</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -4794,7 +4794,7 @@
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>kingaku_zeinuki</t>
+          <t>tax_rate</t>
         </is>
       </c>
       <c r="E36" s="10" t="n"/>
@@ -4820,7 +4820,11 @@
       </c>
       <c r="R36" s="10" t="n"/>
       <c r="S36" s="11" t="n"/>
-      <c r="T36" s="17" t="inlineStr"/>
+      <c r="T36" s="17" t="inlineStr">
+        <is>
+          <t>##.##</t>
+        </is>
+      </c>
       <c r="U36" s="10" t="n"/>
       <c r="V36" s="10" t="n"/>
       <c r="W36" s="10" t="n"/>
@@ -4838,7 +4842,7 @@
       <c r="AE36" s="11" t="n"/>
       <c r="AF36" s="19" t="inlineStr">
         <is>
-          <t>税抜金額（円）</t>
+          <t>税率（%）</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -4854,7 +4858,7 @@
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>tax_rate</t>
+          <t>tekiyo_start_date</t>
         </is>
       </c>
       <c r="E37" s="10" t="n"/>
@@ -4867,7 +4871,7 @@
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N37" s="10" t="n"/>
@@ -4882,7 +4886,7 @@
       <c r="S37" s="11" t="n"/>
       <c r="T37" s="17" t="inlineStr">
         <is>
-          <t>##.##</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="U37" s="10" t="n"/>
@@ -4902,7 +4906,7 @@
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>税率（%）</t>
+          <t>適用開始日</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -4918,7 +4922,7 @@
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>tekiyo_start_date</t>
+          <t>tekiyo_end_date</t>
         </is>
       </c>
       <c r="E38" s="10" t="n"/>
@@ -4966,7 +4970,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>適用開始日</t>
+          <t>適用終了日</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -4975,14 +4979,14 @@
       <c r="AJ38" s="10" t="n"/>
       <c r="AK38" s="11" t="n"/>
     </row>
-    <row r="39" ht="18" customHeight="1">
+    <row r="39" ht="36" customHeight="1">
       <c r="B39" s="31" t="n">
         <v>12</v>
       </c>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>tekiyo_end_date</t>
+          <t>active_flg</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -4995,7 +4999,7 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
@@ -5008,18 +5012,14 @@
       </c>
       <c r="R39" s="10" t="n"/>
       <c r="S39" s="11" t="n"/>
-      <c r="T39" s="17" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
+      <c r="T39" s="17" t="inlineStr"/>
       <c r="U39" s="10" t="n"/>
       <c r="V39" s="10" t="n"/>
       <c r="W39" s="10" t="n"/>
       <c r="X39" s="11" t="n"/>
       <c r="Y39" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z39" s="10" t="n"/>
@@ -5030,7 +5030,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>適用終了日</t>
+          <t>運用上の有効フラグ（FALSE時は新規割当不可。適用期間とは独立）</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -5046,7 +5046,7 @@
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>campaign_flg</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -5059,7 +5059,7 @@
       <c r="L40" s="11" t="n"/>
       <c r="M40" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N40" s="10" t="n"/>
@@ -5072,11 +5072,7 @@
       </c>
       <c r="R40" s="10" t="n"/>
       <c r="S40" s="11" t="n"/>
-      <c r="T40" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T40" s="17" t="inlineStr"/>
       <c r="U40" s="10" t="n"/>
       <c r="V40" s="10" t="n"/>
       <c r="W40" s="10" t="n"/>
@@ -5094,7 +5090,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>キャンペーンフラグ（TRUE: 有効, FALSE: 無効）</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -5107,10 +5103,10 @@
       <c r="B41" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="C41" s="39" t="n"/>
+      <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>biko</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -5136,18 +5132,14 @@
       </c>
       <c r="R41" s="10" t="n"/>
       <c r="S41" s="11" t="n"/>
-      <c r="T41" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T41" s="17" t="inlineStr"/>
       <c r="U41" s="10" t="n"/>
       <c r="V41" s="10" t="n"/>
       <c r="W41" s="10" t="n"/>
       <c r="X41" s="11" t="n"/>
       <c r="Y41" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z41" s="10" t="n"/>
@@ -5158,7 +5150,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>備考（NOT NULL、空欄は `""`）</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -5167,71 +5159,198 @@
       <c r="AJ41" s="10" t="n"/>
       <c r="AK41" s="11" t="n"/>
     </row>
-    <row r="42" ht="19.5" customHeight="1"/>
-    <row r="43" ht="19.5" customHeight="1">
-      <c r="B43" s="40" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="n"/>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="10" t="n"/>
+      <c r="L42" s="11" t="n"/>
+      <c r="M42" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N42" s="10" t="n"/>
+      <c r="O42" s="10" t="n"/>
+      <c r="P42" s="11" t="n"/>
+      <c r="Q42" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R42" s="10" t="n"/>
+      <c r="S42" s="11" t="n"/>
+      <c r="T42" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U42" s="10" t="n"/>
+      <c r="V42" s="10" t="n"/>
+      <c r="W42" s="10" t="n"/>
+      <c r="X42" s="11" t="n"/>
+      <c r="Y42" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z42" s="10" t="n"/>
+      <c r="AA42" s="10" t="n"/>
+      <c r="AB42" s="10" t="n"/>
+      <c r="AC42" s="10" t="n"/>
+      <c r="AD42" s="10" t="n"/>
+      <c r="AE42" s="11" t="n"/>
+      <c r="AF42" s="19" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="AG42" s="10" t="n"/>
+      <c r="AH42" s="10" t="n"/>
+      <c r="AI42" s="10" t="n"/>
+      <c r="AJ42" s="10" t="n"/>
+      <c r="AK42" s="11" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="C43" s="39" t="n"/>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="10" t="n"/>
+      <c r="J43" s="10" t="n"/>
+      <c r="K43" s="10" t="n"/>
+      <c r="L43" s="11" t="n"/>
+      <c r="M43" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N43" s="10" t="n"/>
+      <c r="O43" s="10" t="n"/>
+      <c r="P43" s="11" t="n"/>
+      <c r="Q43" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="11" t="n"/>
+      <c r="T43" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U43" s="10" t="n"/>
+      <c r="V43" s="10" t="n"/>
+      <c r="W43" s="10" t="n"/>
+      <c r="X43" s="11" t="n"/>
+      <c r="Y43" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z43" s="10" t="n"/>
+      <c r="AA43" s="10" t="n"/>
+      <c r="AB43" s="10" t="n"/>
+      <c r="AC43" s="10" t="n"/>
+      <c r="AD43" s="10" t="n"/>
+      <c r="AE43" s="11" t="n"/>
+      <c r="AF43" s="19" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AG43" s="10" t="n"/>
+      <c r="AH43" s="10" t="n"/>
+      <c r="AI43" s="10" t="n"/>
+      <c r="AJ43" s="10" t="n"/>
+      <c r="AK43" s="11" t="n"/>
+    </row>
+    <row r="44" ht="19.5" customHeight="1"/>
+    <row r="45" ht="19.5" customHeight="1">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="C44" s="19" t="inlineStr">
+    <row r="46" ht="18" customHeight="1">
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>GET /api/v1/tanka/1</t>
         </is>
       </c>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="10" t="n"/>
-      <c r="G44" s="10" t="n"/>
-      <c r="H44" s="10" t="n"/>
-      <c r="I44" s="10" t="n"/>
-      <c r="J44" s="10" t="n"/>
-      <c r="K44" s="10" t="n"/>
-      <c r="L44" s="10" t="n"/>
-      <c r="M44" s="10" t="n"/>
-      <c r="N44" s="10" t="n"/>
-      <c r="O44" s="10" t="n"/>
-      <c r="P44" s="10" t="n"/>
-      <c r="Q44" s="10" t="n"/>
-      <c r="R44" s="10" t="n"/>
-      <c r="S44" s="10" t="n"/>
-      <c r="T44" s="10" t="n"/>
-      <c r="U44" s="10" t="n"/>
-      <c r="V44" s="10" t="n"/>
-      <c r="W44" s="10" t="n"/>
-      <c r="X44" s="10" t="n"/>
-      <c r="Y44" s="10" t="n"/>
-      <c r="Z44" s="10" t="n"/>
-      <c r="AA44" s="10" t="n"/>
-      <c r="AB44" s="10" t="n"/>
-      <c r="AC44" s="10" t="n"/>
-      <c r="AD44" s="10" t="n"/>
-      <c r="AE44" s="10" t="n"/>
-      <c r="AF44" s="10" t="n"/>
-      <c r="AG44" s="10" t="n"/>
-      <c r="AH44" s="10" t="n"/>
-      <c r="AI44" s="10" t="n"/>
-      <c r="AJ44" s="10" t="n"/>
-      <c r="AK44" s="11" t="n"/>
-    </row>
-    <row r="46" ht="19.5" customHeight="1">
-      <c r="B46" s="40" t="inlineStr">
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n"/>
+      <c r="J46" s="10" t="n"/>
+      <c r="K46" s="10" t="n"/>
+      <c r="L46" s="10" t="n"/>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="10" t="n"/>
+      <c r="O46" s="10" t="n"/>
+      <c r="P46" s="10" t="n"/>
+      <c r="Q46" s="10" t="n"/>
+      <c r="R46" s="10" t="n"/>
+      <c r="S46" s="10" t="n"/>
+      <c r="T46" s="10" t="n"/>
+      <c r="U46" s="10" t="n"/>
+      <c r="V46" s="10" t="n"/>
+      <c r="W46" s="10" t="n"/>
+      <c r="X46" s="10" t="n"/>
+      <c r="Y46" s="10" t="n"/>
+      <c r="Z46" s="10" t="n"/>
+      <c r="AA46" s="10" t="n"/>
+      <c r="AB46" s="10" t="n"/>
+      <c r="AC46" s="10" t="n"/>
+      <c r="AD46" s="10" t="n"/>
+      <c r="AE46" s="10" t="n"/>
+      <c r="AF46" s="10" t="n"/>
+      <c r="AG46" s="10" t="n"/>
+      <c r="AH46" s="10" t="n"/>
+      <c r="AI46" s="10" t="n"/>
+      <c r="AJ46" s="10" t="n"/>
+      <c r="AK46" s="11" t="n"/>
+    </row>
+    <row r="48" ht="19.5" customHeight="1">
+      <c r="B48" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="306" customHeight="1">
-      <c r="C47" s="19" t="inlineStr">
+    <row r="49" ht="342" customHeight="1">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
     "tanka_id": 1,
     "ja_id": 1,
     "tanka_type": 1,
-    "tanka_type_label": "新聞購読料",
     "tanka_code": "T001",
     "tanka_name": "基本購読料（月額）",
     "kingaku_zeikomi": 4900,
@@ -5239,56 +5358,59 @@
     "tax_rate": 10.0,
     "tekiyo_start_date": "2026-01-01",
     "tekiyo_end_date": null,
+    "active_flg": true,
+    "campaign_flg": false,
+    "biko": "",
     "created_at": "2026-01-15T10:00:00Z",
     "updated_at": "2026-03-10T14:30:00Z"
   }
 }</t>
         </is>
       </c>
-      <c r="D47" s="10" t="n"/>
-      <c r="E47" s="10" t="n"/>
-      <c r="F47" s="10" t="n"/>
-      <c r="G47" s="10" t="n"/>
-      <c r="H47" s="10" t="n"/>
-      <c r="I47" s="10" t="n"/>
-      <c r="J47" s="10" t="n"/>
-      <c r="K47" s="10" t="n"/>
-      <c r="L47" s="10" t="n"/>
-      <c r="M47" s="10" t="n"/>
-      <c r="N47" s="10" t="n"/>
-      <c r="O47" s="10" t="n"/>
-      <c r="P47" s="10" t="n"/>
-      <c r="Q47" s="10" t="n"/>
-      <c r="R47" s="10" t="n"/>
-      <c r="S47" s="10" t="n"/>
-      <c r="T47" s="10" t="n"/>
-      <c r="U47" s="10" t="n"/>
-      <c r="V47" s="10" t="n"/>
-      <c r="W47" s="10" t="n"/>
-      <c r="X47" s="10" t="n"/>
-      <c r="Y47" s="10" t="n"/>
-      <c r="Z47" s="10" t="n"/>
-      <c r="AA47" s="10" t="n"/>
-      <c r="AB47" s="10" t="n"/>
-      <c r="AC47" s="10" t="n"/>
-      <c r="AD47" s="10" t="n"/>
-      <c r="AE47" s="10" t="n"/>
-      <c r="AF47" s="10" t="n"/>
-      <c r="AG47" s="10" t="n"/>
-      <c r="AH47" s="10" t="n"/>
-      <c r="AI47" s="10" t="n"/>
-      <c r="AJ47" s="10" t="n"/>
-      <c r="AK47" s="11" t="n"/>
-    </row>
-    <row r="49" ht="19.5" customHeight="1">
-      <c r="B49" s="40" t="inlineStr">
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="10" t="n"/>
+      <c r="J49" s="10" t="n"/>
+      <c r="K49" s="10" t="n"/>
+      <c r="L49" s="10" t="n"/>
+      <c r="M49" s="10" t="n"/>
+      <c r="N49" s="10" t="n"/>
+      <c r="O49" s="10" t="n"/>
+      <c r="P49" s="10" t="n"/>
+      <c r="Q49" s="10" t="n"/>
+      <c r="R49" s="10" t="n"/>
+      <c r="S49" s="10" t="n"/>
+      <c r="T49" s="10" t="n"/>
+      <c r="U49" s="10" t="n"/>
+      <c r="V49" s="10" t="n"/>
+      <c r="W49" s="10" t="n"/>
+      <c r="X49" s="10" t="n"/>
+      <c r="Y49" s="10" t="n"/>
+      <c r="Z49" s="10" t="n"/>
+      <c r="AA49" s="10" t="n"/>
+      <c r="AB49" s="10" t="n"/>
+      <c r="AC49" s="10" t="n"/>
+      <c r="AD49" s="10" t="n"/>
+      <c r="AE49" s="10" t="n"/>
+      <c r="AF49" s="10" t="n"/>
+      <c r="AG49" s="10" t="n"/>
+      <c r="AH49" s="10" t="n"/>
+      <c r="AI49" s="10" t="n"/>
+      <c r="AJ49" s="10" t="n"/>
+      <c r="AK49" s="11" t="n"/>
+    </row>
+    <row r="51" ht="19.5" customHeight="1">
+      <c r="B51" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="72" customHeight="1">
-      <c r="C50" s="19" t="inlineStr">
+    <row r="52" ht="72" customHeight="1">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -5296,50 +5418,50 @@
 }</t>
         </is>
       </c>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
-      <c r="F50" s="10" t="n"/>
-      <c r="G50" s="10" t="n"/>
-      <c r="H50" s="10" t="n"/>
-      <c r="I50" s="10" t="n"/>
-      <c r="J50" s="10" t="n"/>
-      <c r="K50" s="10" t="n"/>
-      <c r="L50" s="10" t="n"/>
-      <c r="M50" s="10" t="n"/>
-      <c r="N50" s="10" t="n"/>
-      <c r="O50" s="10" t="n"/>
-      <c r="P50" s="10" t="n"/>
-      <c r="Q50" s="10" t="n"/>
-      <c r="R50" s="10" t="n"/>
-      <c r="S50" s="10" t="n"/>
-      <c r="T50" s="10" t="n"/>
-      <c r="U50" s="10" t="n"/>
-      <c r="V50" s="10" t="n"/>
-      <c r="W50" s="10" t="n"/>
-      <c r="X50" s="10" t="n"/>
-      <c r="Y50" s="10" t="n"/>
-      <c r="Z50" s="10" t="n"/>
-      <c r="AA50" s="10" t="n"/>
-      <c r="AB50" s="10" t="n"/>
-      <c r="AC50" s="10" t="n"/>
-      <c r="AD50" s="10" t="n"/>
-      <c r="AE50" s="10" t="n"/>
-      <c r="AF50" s="10" t="n"/>
-      <c r="AG50" s="10" t="n"/>
-      <c r="AH50" s="10" t="n"/>
-      <c r="AI50" s="10" t="n"/>
-      <c r="AJ50" s="10" t="n"/>
-      <c r="AK50" s="11" t="n"/>
-    </row>
-    <row r="52" ht="19.5" customHeight="1">
-      <c r="B52" s="40" t="inlineStr">
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="10" t="n"/>
+      <c r="J52" s="10" t="n"/>
+      <c r="K52" s="10" t="n"/>
+      <c r="L52" s="10" t="n"/>
+      <c r="M52" s="10" t="n"/>
+      <c r="N52" s="10" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="10" t="n"/>
+      <c r="Q52" s="10" t="n"/>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="10" t="n"/>
+      <c r="T52" s="10" t="n"/>
+      <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
+      <c r="W52" s="10" t="n"/>
+      <c r="X52" s="10" t="n"/>
+      <c r="Y52" s="10" t="n"/>
+      <c r="Z52" s="10" t="n"/>
+      <c r="AA52" s="10" t="n"/>
+      <c r="AB52" s="10" t="n"/>
+      <c r="AC52" s="10" t="n"/>
+      <c r="AD52" s="10" t="n"/>
+      <c r="AE52" s="10" t="n"/>
+      <c r="AF52" s="10" t="n"/>
+      <c r="AG52" s="10" t="n"/>
+      <c r="AH52" s="10" t="n"/>
+      <c r="AI52" s="10" t="n"/>
+      <c r="AJ52" s="10" t="n"/>
+      <c r="AK52" s="11" t="n"/>
+    </row>
+    <row r="54" ht="19.5" customHeight="1">
+      <c r="B54" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="72" customHeight="1">
-      <c r="C53" s="19" t="inlineStr">
+    <row r="55" ht="72" customHeight="1">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -5347,101 +5469,101 @@
 }</t>
         </is>
       </c>
-      <c r="D53" s="10" t="n"/>
-      <c r="E53" s="10" t="n"/>
-      <c r="F53" s="10" t="n"/>
-      <c r="G53" s="10" t="n"/>
-      <c r="H53" s="10" t="n"/>
-      <c r="I53" s="10" t="n"/>
-      <c r="J53" s="10" t="n"/>
-      <c r="K53" s="10" t="n"/>
-      <c r="L53" s="10" t="n"/>
-      <c r="M53" s="10" t="n"/>
-      <c r="N53" s="10" t="n"/>
-      <c r="O53" s="10" t="n"/>
-      <c r="P53" s="10" t="n"/>
-      <c r="Q53" s="10" t="n"/>
-      <c r="R53" s="10" t="n"/>
-      <c r="S53" s="10" t="n"/>
-      <c r="T53" s="10" t="n"/>
-      <c r="U53" s="10" t="n"/>
-      <c r="V53" s="10" t="n"/>
-      <c r="W53" s="10" t="n"/>
-      <c r="X53" s="10" t="n"/>
-      <c r="Y53" s="10" t="n"/>
-      <c r="Z53" s="10" t="n"/>
-      <c r="AA53" s="10" t="n"/>
-      <c r="AB53" s="10" t="n"/>
-      <c r="AC53" s="10" t="n"/>
-      <c r="AD53" s="10" t="n"/>
-      <c r="AE53" s="10" t="n"/>
-      <c r="AF53" s="10" t="n"/>
-      <c r="AG53" s="10" t="n"/>
-      <c r="AH53" s="10" t="n"/>
-      <c r="AI53" s="10" t="n"/>
-      <c r="AJ53" s="10" t="n"/>
-      <c r="AK53" s="11" t="n"/>
-    </row>
-    <row r="55" ht="19.5" customHeight="1">
-      <c r="B55" s="40" t="inlineStr">
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="10" t="n"/>
+      <c r="K55" s="10" t="n"/>
+      <c r="L55" s="10" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="10" t="n"/>
+      <c r="O55" s="10" t="n"/>
+      <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="10" t="n"/>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="10" t="n"/>
+      <c r="T55" s="10" t="n"/>
+      <c r="U55" s="10" t="n"/>
+      <c r="V55" s="10" t="n"/>
+      <c r="W55" s="10" t="n"/>
+      <c r="X55" s="10" t="n"/>
+      <c r="Y55" s="10" t="n"/>
+      <c r="Z55" s="10" t="n"/>
+      <c r="AA55" s="10" t="n"/>
+      <c r="AB55" s="10" t="n"/>
+      <c r="AC55" s="10" t="n"/>
+      <c r="AD55" s="10" t="n"/>
+      <c r="AE55" s="10" t="n"/>
+      <c r="AF55" s="10" t="n"/>
+      <c r="AG55" s="10" t="n"/>
+      <c r="AH55" s="10" t="n"/>
+      <c r="AI55" s="10" t="n"/>
+      <c r="AJ55" s="10" t="n"/>
+      <c r="AK55" s="11" t="n"/>
+    </row>
+    <row r="57" ht="19.5" customHeight="1">
+      <c r="B57" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 404 Not Found）</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="72" customHeight="1">
-      <c r="C56" s="19" t="inlineStr">
+    <row r="58" ht="72" customHeight="1">
+      <c r="C58" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "TANKA_NOT_FOUND",
+  "error_code": "NOT_FOUND",
   "message": "指定された単価が見つかりません"
 }</t>
         </is>
       </c>
-      <c r="D56" s="10" t="n"/>
-      <c r="E56" s="10" t="n"/>
-      <c r="F56" s="10" t="n"/>
-      <c r="G56" s="10" t="n"/>
-      <c r="H56" s="10" t="n"/>
-      <c r="I56" s="10" t="n"/>
-      <c r="J56" s="10" t="n"/>
-      <c r="K56" s="10" t="n"/>
-      <c r="L56" s="10" t="n"/>
-      <c r="M56" s="10" t="n"/>
-      <c r="N56" s="10" t="n"/>
-      <c r="O56" s="10" t="n"/>
-      <c r="P56" s="10" t="n"/>
-      <c r="Q56" s="10" t="n"/>
-      <c r="R56" s="10" t="n"/>
-      <c r="S56" s="10" t="n"/>
-      <c r="T56" s="10" t="n"/>
-      <c r="U56" s="10" t="n"/>
-      <c r="V56" s="10" t="n"/>
-      <c r="W56" s="10" t="n"/>
-      <c r="X56" s="10" t="n"/>
-      <c r="Y56" s="10" t="n"/>
-      <c r="Z56" s="10" t="n"/>
-      <c r="AA56" s="10" t="n"/>
-      <c r="AB56" s="10" t="n"/>
-      <c r="AC56" s="10" t="n"/>
-      <c r="AD56" s="10" t="n"/>
-      <c r="AE56" s="10" t="n"/>
-      <c r="AF56" s="10" t="n"/>
-      <c r="AG56" s="10" t="n"/>
-      <c r="AH56" s="10" t="n"/>
-      <c r="AI56" s="10" t="n"/>
-      <c r="AJ56" s="10" t="n"/>
-      <c r="AK56" s="11" t="n"/>
-    </row>
-    <row r="58" ht="19.5" customHeight="1">
-      <c r="B58" s="40" t="inlineStr">
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="10" t="n"/>
+      <c r="J58" s="10" t="n"/>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="10" t="n"/>
+      <c r="Q58" s="10" t="n"/>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="10" t="n"/>
+      <c r="X58" s="10" t="n"/>
+      <c r="Y58" s="10" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="10" t="n"/>
+      <c r="AE58" s="10" t="n"/>
+      <c r="AF58" s="10" t="n"/>
+      <c r="AG58" s="10" t="n"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="10" t="n"/>
+      <c r="AJ58" s="10" t="n"/>
+      <c r="AK58" s="11" t="n"/>
+    </row>
+    <row r="60" ht="19.5" customHeight="1">
+      <c r="B60" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="72" customHeight="1">
-      <c r="C59" s="19" t="inlineStr">
+    <row r="61" ht="72" customHeight="1">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -5449,149 +5571,149 @@
 }</t>
         </is>
       </c>
-      <c r="D59" s="10" t="n"/>
-      <c r="E59" s="10" t="n"/>
-      <c r="F59" s="10" t="n"/>
-      <c r="G59" s="10" t="n"/>
-      <c r="H59" s="10" t="n"/>
-      <c r="I59" s="10" t="n"/>
-      <c r="J59" s="10" t="n"/>
-      <c r="K59" s="10" t="n"/>
-      <c r="L59" s="10" t="n"/>
-      <c r="M59" s="10" t="n"/>
-      <c r="N59" s="10" t="n"/>
-      <c r="O59" s="10" t="n"/>
-      <c r="P59" s="10" t="n"/>
-      <c r="Q59" s="10" t="n"/>
-      <c r="R59" s="10" t="n"/>
-      <c r="S59" s="10" t="n"/>
-      <c r="T59" s="10" t="n"/>
-      <c r="U59" s="10" t="n"/>
-      <c r="V59" s="10" t="n"/>
-      <c r="W59" s="10" t="n"/>
-      <c r="X59" s="10" t="n"/>
-      <c r="Y59" s="10" t="n"/>
-      <c r="Z59" s="10" t="n"/>
-      <c r="AA59" s="10" t="n"/>
-      <c r="AB59" s="10" t="n"/>
-      <c r="AC59" s="10" t="n"/>
-      <c r="AD59" s="10" t="n"/>
-      <c r="AE59" s="10" t="n"/>
-      <c r="AF59" s="10" t="n"/>
-      <c r="AG59" s="10" t="n"/>
-      <c r="AH59" s="10" t="n"/>
-      <c r="AI59" s="10" t="n"/>
-      <c r="AJ59" s="10" t="n"/>
-      <c r="AK59" s="11" t="n"/>
-    </row>
-    <row r="61" ht="19.5" customHeight="1"/>
-    <row r="62" ht="19.5" customHeight="1">
-      <c r="A62" s="27" t="inlineStr">
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="10" t="n"/>
+      <c r="J61" s="10" t="n"/>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="10" t="n"/>
+      <c r="Q61" s="10" t="n"/>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="10" t="n"/>
+      <c r="X61" s="10" t="n"/>
+      <c r="Y61" s="10" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="10" t="n"/>
+      <c r="AD61" s="10" t="n"/>
+      <c r="AE61" s="10" t="n"/>
+      <c r="AF61" s="10" t="n"/>
+      <c r="AG61" s="10" t="n"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="10" t="n"/>
+      <c r="AJ61" s="10" t="n"/>
+      <c r="AK61" s="11" t="n"/>
+    </row>
+    <row r="63" ht="19.5" customHeight="1"/>
+    <row r="64" ht="19.5" customHeight="1">
+      <c r="A64" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="B63" s="27" t="inlineStr">
+    <row r="65" ht="18" customHeight="1">
+      <c r="B65" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="C64" s="41" t="inlineStr">
-        <is>
-          <t>パスパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="D65" s="41" t="inlineStr">
-        <is>
-          <t>tanka_id：数値型チェック、必須チェック</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="C66" s="41" t="inlineStr">
         <is>
-          <t>不正なパラメータが存在する場合：</t>
+          <t>パスパラメータの検証：</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="D67" s="41" t="inlineStr">
         <is>
+          <t>tanka_id：数値型チェック、必須チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="C68" s="41" t="inlineStr">
+        <is>
+          <t>不正なパラメータが存在する場合：</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="D69" s="41" t="inlineStr">
+        <is>
           <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="B68" s="27" t="inlineStr">
+    <row r="70" ht="18" customHeight="1">
+      <c r="B70" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="C69" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="C70" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="C71" s="41" t="inlineStr">
         <is>
-          <t>権限チェック：`tanka.view` を保持しているか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="36" customHeight="1">
-      <c r="D72" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="C72" s="41" t="inlineStr">
+        <is>
+          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="C73" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="B74" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得</t>
+          <t>権限チェック：`tanka.view` を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="36" customHeight="1">
+      <c r="D74" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="C75" s="41" t="inlineStr">
         <is>
+          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="B76" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="C77" s="41" t="inlineStr">
+        <is>
           <t>ログインユーザーのスコープを取得する（ja_id）。</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="C76" s="41" t="inlineStr">
+    <row r="78" ht="18" customHeight="1">
+      <c r="C78" s="41" t="inlineStr">
         <is>
           <t>以下の条件でデータを取得する。</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="126" customHeight="1">
-      <c r="C77" s="42" t="inlineStr">
+    <row r="79" ht="126" customHeight="1">
+      <c r="C79" s="42" t="inlineStr">
         <is>
           <t>SELECT tanka_id, ja_id, tanka_type, tanka_code, tanka_name,
        kingaku_zeikomi, kingaku_zeinuki, tax_rate,
@@ -5602,92 +5724,92 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D77" s="10" t="n"/>
-      <c r="E77" s="10" t="n"/>
-      <c r="F77" s="10" t="n"/>
-      <c r="G77" s="10" t="n"/>
-      <c r="H77" s="10" t="n"/>
-      <c r="I77" s="10" t="n"/>
-      <c r="J77" s="10" t="n"/>
-      <c r="K77" s="10" t="n"/>
-      <c r="L77" s="10" t="n"/>
-      <c r="M77" s="10" t="n"/>
-      <c r="N77" s="10" t="n"/>
-      <c r="O77" s="10" t="n"/>
-      <c r="P77" s="10" t="n"/>
-      <c r="Q77" s="10" t="n"/>
-      <c r="R77" s="10" t="n"/>
-      <c r="S77" s="10" t="n"/>
-      <c r="T77" s="10" t="n"/>
-      <c r="U77" s="10" t="n"/>
-      <c r="V77" s="10" t="n"/>
-      <c r="W77" s="10" t="n"/>
-      <c r="X77" s="10" t="n"/>
-      <c r="Y77" s="10" t="n"/>
-      <c r="Z77" s="10" t="n"/>
-      <c r="AA77" s="10" t="n"/>
-      <c r="AB77" s="10" t="n"/>
-      <c r="AC77" s="10" t="n"/>
-      <c r="AD77" s="10" t="n"/>
-      <c r="AE77" s="10" t="n"/>
-      <c r="AF77" s="10" t="n"/>
-      <c r="AG77" s="10" t="n"/>
-      <c r="AH77" s="10" t="n"/>
-      <c r="AI77" s="10" t="n"/>
-      <c r="AJ77" s="10" t="n"/>
-      <c r="AK77" s="11" t="n"/>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="C78" s="41" t="inlineStr">
-        <is>
-          <t>レコードが存在しない場合：HTTP 404 (`TANKA_NOT_FOUND`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="C79" s="41" t="inlineStr">
-        <is>
-          <t>ja_id が一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
-        </is>
-      </c>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="10" t="n"/>
+      <c r="J79" s="10" t="n"/>
+      <c r="K79" s="10" t="n"/>
+      <c r="L79" s="10" t="n"/>
+      <c r="M79" s="10" t="n"/>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="10" t="n"/>
+      <c r="Q79" s="10" t="n"/>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="10" t="n"/>
+      <c r="T79" s="10" t="n"/>
+      <c r="U79" s="10" t="n"/>
+      <c r="V79" s="10" t="n"/>
+      <c r="W79" s="10" t="n"/>
+      <c r="X79" s="10" t="n"/>
+      <c r="Y79" s="10" t="n"/>
+      <c r="Z79" s="10" t="n"/>
+      <c r="AA79" s="10" t="n"/>
+      <c r="AB79" s="10" t="n"/>
+      <c r="AC79" s="10" t="n"/>
+      <c r="AD79" s="10" t="n"/>
+      <c r="AE79" s="10" t="n"/>
+      <c r="AF79" s="10" t="n"/>
+      <c r="AG79" s="10" t="n"/>
+      <c r="AH79" s="10" t="n"/>
+      <c r="AI79" s="10" t="n"/>
+      <c r="AJ79" s="10" t="n"/>
+      <c r="AK79" s="11" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="B80" s="27" t="inlineStr">
-        <is>
-          <t>4.4 レスポンス生成</t>
+      <c r="C80" s="41" t="inlineStr">
+        <is>
+          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="C81" s="41" t="inlineStr">
         <is>
+          <t>ja_id が一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="B82" s="27" t="inlineStr">
+        <is>
+          <t>4.4 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="C83" s="41" t="inlineStr">
+        <is>
           <t>tanka_type 値をラベルにマッピング（1 → 新聞購読料, 2 → 配達手数料）</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="C82" s="41" t="inlineStr">
-        <is>
-          <t>data オブジェクトを含むJSONを返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="B83" s="27" t="inlineStr">
-        <is>
-          <t>4.5 例外処理</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="C84" s="41" t="inlineStr">
         <is>
+          <t>data オブジェクトを含むJSONを返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="B85" s="27" t="inlineStr">
+        <is>
+          <t>4.5 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="C86" s="41" t="inlineStr">
+        <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="182">
+  <mergeCells count="194">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y27:AE27"/>
@@ -5695,9 +5817,9 @@
     <mergeCell ref="Q23:S23"/>
     <mergeCell ref="Y36:AE36"/>
     <mergeCell ref="C66:AK66"/>
+    <mergeCell ref="B54:I54"/>
     <mergeCell ref="T33:X33"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="C53:AK53"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M32:P32"/>
     <mergeCell ref="C77:AK77"/>
@@ -5705,27 +5827,35 @@
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
+    <mergeCell ref="C68:AK68"/>
+    <mergeCell ref="C86:AK86"/>
     <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
+    <mergeCell ref="M43:P43"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="D33:L33"/>
     <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="C44:AK44"/>
+    <mergeCell ref="D42:L42"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C75:AK75"/>
+    <mergeCell ref="B65:AK65"/>
     <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="D35:L35"/>
+    <mergeCell ref="Q43:S43"/>
+    <mergeCell ref="C46:AK46"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="T22:X22"/>
-    <mergeCell ref="B63:AK63"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
     <mergeCell ref="AF34:AK34"/>
@@ -5733,17 +5863,18 @@
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="T34:X34"/>
+    <mergeCell ref="Q42:S42"/>
     <mergeCell ref="Y40:AE40"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="C70:AK70"/>
     <mergeCell ref="T37:X37"/>
+    <mergeCell ref="B45:I45"/>
     <mergeCell ref="D36:L36"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="T30:X30"/>
-    <mergeCell ref="D72:AK72"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="T38:X38"/>
-    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="C29:C43"/>
+    <mergeCell ref="C49:AK49"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="Y33:AE33"/>
@@ -5761,6 +5892,7 @@
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="D29:L29"/>
+    <mergeCell ref="C55:AK55"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="D38:L38"/>
     <mergeCell ref="T40:X40"/>
@@ -5768,63 +5900,63 @@
     <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="D65:AK65"/>
-    <mergeCell ref="B49:I49"/>
     <mergeCell ref="Y29:AE29"/>
-    <mergeCell ref="C59:AK59"/>
     <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="A25:AK25"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="C52:AK52"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="Y31:AE31"/>
+    <mergeCell ref="C61:AK61"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="M37:P37"/>
+    <mergeCell ref="C72:AK72"/>
     <mergeCell ref="M36:P36"/>
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="C81:AK81"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="C29:C41"/>
     <mergeCell ref="C78:AK78"/>
     <mergeCell ref="T32:X32"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="T42:X42"/>
     <mergeCell ref="C28:L28"/>
     <mergeCell ref="Y41:AE41"/>
-    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="A20:AK20"/>
     <mergeCell ref="B11:I11"/>
+    <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="C64:AK64"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M34:P34"/>
     <mergeCell ref="C79:AK79"/>
+    <mergeCell ref="Y43:AE43"/>
     <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="AF31:AK31"/>
     <mergeCell ref="D30:L30"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="M39:P39"/>
-    <mergeCell ref="C50:AK50"/>
+    <mergeCell ref="A64:AK64"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="C56:AK56"/>
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="B80:AK80"/>
     <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="M40:P40"/>
-    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="T43:X43"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
@@ -5835,40 +5967,42 @@
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M41:P41"/>
+    <mergeCell ref="B70:AK70"/>
     <mergeCell ref="D32:L32"/>
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="C69:AK69"/>
     <mergeCell ref="M38:P38"/>
+    <mergeCell ref="C83:AK83"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="B43:I43"/>
-    <mergeCell ref="B58:I58"/>
-    <mergeCell ref="B52:I52"/>
+    <mergeCell ref="D74:AK74"/>
     <mergeCell ref="Y32:AE32"/>
-    <mergeCell ref="A62:AK62"/>
+    <mergeCell ref="D43:L43"/>
+    <mergeCell ref="Y42:AE42"/>
+    <mergeCell ref="B82:AK82"/>
     <mergeCell ref="D67:AK67"/>
+    <mergeCell ref="B60:I60"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="C47:AK47"/>
-    <mergeCell ref="B74:AK74"/>
-    <mergeCell ref="B68:AK68"/>
-    <mergeCell ref="B83:AK83"/>
+    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="D69:AK69"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="B76:AK76"/>
     <mergeCell ref="AF39:AK39"/>
+    <mergeCell ref="B85:AK85"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="C71:AK71"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="M22:P22"/>
-    <mergeCell ref="C76:AK76"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="D31:L31"/>
     <mergeCell ref="Y34:AE34"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="M28:P28"/>
+    <mergeCell ref="M42:P42"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5881,7 +6015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK109"/>
+  <dimension ref="A1:AK115"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -6042,7 +6176,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6392,7 +6526,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -6589,7 +6723,7 @@
       <c r="B18" s="35" t="n"/>
       <c r="I18" s="36" t="n"/>
       <c r="J18" s="17" t="n">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="K18" s="10" t="n"/>
       <c r="L18" s="10" t="n"/>
@@ -7149,7 +7283,7 @@
       <c r="S30" s="11" t="n"/>
       <c r="T30" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="U30" s="10" t="n"/>
@@ -7165,7 +7299,7 @@
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>適用開始日（YYYY-MM-DD）。空欄の場合は現在日付</t>
+          <t>適用開始日（YYYY-MM-DD）。必須</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -7209,7 +7343,7 @@
       <c r="S31" s="11" t="n"/>
       <c r="T31" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="U31" s="10" t="n"/>
@@ -7225,7 +7359,7 @@
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>適用終了日（YYYY-MM-DD）。空欄の場合は無期限</t>
+          <t>適用終了日（YYYY-MM-DD）。必須、開始日以降</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -7234,211 +7368,207 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="19.5" customHeight="1"/>
-    <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="27" t="inlineStr">
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>biko</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="11" t="n"/>
+      <c r="Q32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="11" t="n"/>
+      <c r="T32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="11" t="n"/>
+      <c r="Y32" s="17" t="inlineStr"/>
+      <c r="Z32" s="10" t="n"/>
+      <c r="AA32" s="10" t="n"/>
+      <c r="AB32" s="11" t="n"/>
+      <c r="AC32" s="17" t="inlineStr"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="11" t="n"/>
+      <c r="AF32" s="19" t="inlineStr">
+        <is>
+          <t>備考。空欄可（空文字「""」として保存）</t>
+        </is>
+      </c>
+      <c r="AG32" s="10" t="n"/>
+      <c r="AH32" s="10" t="n"/>
+      <c r="AI32" s="10" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
+      <c r="AK32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>active_flg</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="n"/>
+      <c r="J33" s="10" t="n"/>
+      <c r="K33" s="10" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="n"/>
+      <c r="O33" s="10" t="n"/>
+      <c r="P33" s="11" t="n"/>
+      <c r="Q33" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" s="10" t="n"/>
+      <c r="S33" s="11" t="n"/>
+      <c r="T33" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U33" s="10" t="n"/>
+      <c r="V33" s="10" t="n"/>
+      <c r="W33" s="10" t="n"/>
+      <c r="X33" s="11" t="n"/>
+      <c r="Y33" s="17" t="inlineStr"/>
+      <c r="Z33" s="10" t="n"/>
+      <c r="AA33" s="10" t="n"/>
+      <c r="AB33" s="11" t="n"/>
+      <c r="AC33" s="17" t="inlineStr"/>
+      <c r="AD33" s="10" t="n"/>
+      <c r="AE33" s="11" t="n"/>
+      <c r="AF33" s="19" t="inlineStr">
+        <is>
+          <t>運用上の有効フラグ。省略時は TRUE</t>
+        </is>
+      </c>
+      <c r="AG33" s="10" t="n"/>
+      <c r="AH33" s="10" t="n"/>
+      <c r="AI33" s="10" t="n"/>
+      <c r="AJ33" s="10" t="n"/>
+      <c r="AK33" s="11" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>campaign_flg</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="10" t="n"/>
+      <c r="J34" s="10" t="n"/>
+      <c r="K34" s="10" t="n"/>
+      <c r="L34" s="11" t="n"/>
+      <c r="M34" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N34" s="10" t="n"/>
+      <c r="O34" s="10" t="n"/>
+      <c r="P34" s="11" t="n"/>
+      <c r="Q34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R34" s="10" t="n"/>
+      <c r="S34" s="11" t="n"/>
+      <c r="T34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U34" s="10" t="n"/>
+      <c r="V34" s="10" t="n"/>
+      <c r="W34" s="10" t="n"/>
+      <c r="X34" s="11" t="n"/>
+      <c r="Y34" s="17" t="inlineStr"/>
+      <c r="Z34" s="10" t="n"/>
+      <c r="AA34" s="10" t="n"/>
+      <c r="AB34" s="11" t="n"/>
+      <c r="AC34" s="17" t="inlineStr"/>
+      <c r="AD34" s="10" t="n"/>
+      <c r="AE34" s="11" t="n"/>
+      <c r="AF34" s="19" t="inlineStr">
+        <is>
+          <t>キャンペーンフラグ。省略時は FALSE</t>
+        </is>
+      </c>
+      <c r="AG34" s="10" t="n"/>
+      <c r="AH34" s="10" t="n"/>
+      <c r="AI34" s="10" t="n"/>
+      <c r="AJ34" s="10" t="n"/>
+      <c r="AK34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="19.5" customHeight="1"/>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="19.5" customHeight="1"/>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="B35" s="30" t="inlineStr">
+    <row r="37" ht="19.5" customHeight="1"/>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
         </is>
       </c>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
-      <c r="H35" s="10" t="n"/>
-      <c r="I35" s="10" t="n"/>
-      <c r="J35" s="10" t="n"/>
-      <c r="K35" s="10" t="n"/>
-      <c r="L35" s="11" t="n"/>
-      <c r="M35" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N35" s="10" t="n"/>
-      <c r="O35" s="10" t="n"/>
-      <c r="P35" s="11" t="n"/>
-      <c r="Q35" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R35" s="10" t="n"/>
-      <c r="S35" s="11" t="n"/>
-      <c r="T35" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
-      <c r="U35" s="10" t="n"/>
-      <c r="V35" s="10" t="n"/>
-      <c r="W35" s="10" t="n"/>
-      <c r="X35" s="11" t="n"/>
-      <c r="Y35" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="Z35" s="10" t="n"/>
-      <c r="AA35" s="10" t="n"/>
-      <c r="AB35" s="10" t="n"/>
-      <c r="AC35" s="10" t="n"/>
-      <c r="AD35" s="10" t="n"/>
-      <c r="AE35" s="11" t="n"/>
-      <c r="AF35" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG35" s="10" t="n"/>
-      <c r="AH35" s="10" t="n"/>
-      <c r="AI35" s="10" t="n"/>
-      <c r="AJ35" s="10" t="n"/>
-      <c r="AK35" s="11" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="10" t="n"/>
-      <c r="H36" s="10" t="n"/>
-      <c r="I36" s="10" t="n"/>
-      <c r="J36" s="10" t="n"/>
-      <c r="K36" s="10" t="n"/>
-      <c r="L36" s="11" t="n"/>
-      <c r="M36" s="17" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="N36" s="10" t="n"/>
-      <c r="O36" s="10" t="n"/>
-      <c r="P36" s="11" t="n"/>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R36" s="10" t="n"/>
-      <c r="S36" s="11" t="n"/>
-      <c r="T36" s="17" t="inlineStr"/>
-      <c r="U36" s="10" t="n"/>
-      <c r="V36" s="10" t="n"/>
-      <c r="W36" s="10" t="n"/>
-      <c r="X36" s="11" t="n"/>
-      <c r="Y36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z36" s="10" t="n"/>
-      <c r="AA36" s="10" t="n"/>
-      <c r="AB36" s="10" t="n"/>
-      <c r="AC36" s="10" t="n"/>
-      <c r="AD36" s="10" t="n"/>
-      <c r="AE36" s="11" t="n"/>
-      <c r="AF36" s="19" t="inlineStr">
-        <is>
-          <t>登録された単価データ</t>
-        </is>
-      </c>
-      <c r="AG36" s="10" t="n"/>
-      <c r="AH36" s="10" t="n"/>
-      <c r="AI36" s="10" t="n"/>
-      <c r="AJ36" s="10" t="n"/>
-      <c r="AK36" s="11" t="n"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" s="37" t="n"/>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>tanka_id</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="10" t="n"/>
-      <c r="K37" s="10" t="n"/>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N37" s="10" t="n"/>
-      <c r="O37" s="10" t="n"/>
-      <c r="P37" s="11" t="n"/>
-      <c r="Q37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R37" s="10" t="n"/>
-      <c r="S37" s="11" t="n"/>
-      <c r="T37" s="17" t="inlineStr"/>
-      <c r="U37" s="10" t="n"/>
-      <c r="V37" s="10" t="n"/>
-      <c r="W37" s="10" t="n"/>
-      <c r="X37" s="11" t="n"/>
-      <c r="Y37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z37" s="10" t="n"/>
-      <c r="AA37" s="10" t="n"/>
-      <c r="AB37" s="10" t="n"/>
-      <c r="AC37" s="10" t="n"/>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="11" t="n"/>
-      <c r="AF37" s="19" t="inlineStr">
-        <is>
-          <t>単価ID</t>
-        </is>
-      </c>
-      <c r="AG37" s="10" t="n"/>
-      <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="10" t="n"/>
-      <c r="AJ37" s="10" t="n"/>
-      <c r="AK37" s="11" t="n"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="B38" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C38" s="38" t="n"/>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>ja_id</t>
-        </is>
-      </c>
+      <c r="D38" s="10" t="n"/>
       <c r="E38" s="10" t="n"/>
       <c r="F38" s="10" t="n"/>
       <c r="G38" s="10" t="n"/>
@@ -7447,29 +7577,33 @@
       <c r="J38" s="10" t="n"/>
       <c r="K38" s="10" t="n"/>
       <c r="L38" s="11" t="n"/>
-      <c r="M38" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N38" s="10" t="n"/>
       <c r="O38" s="10" t="n"/>
       <c r="P38" s="11" t="n"/>
-      <c r="Q38" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q38" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R38" s="10" t="n"/>
       <c r="S38" s="11" t="n"/>
-      <c r="T38" s="17" t="inlineStr"/>
+      <c r="T38" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U38" s="10" t="n"/>
       <c r="V38" s="10" t="n"/>
       <c r="W38" s="10" t="n"/>
       <c r="X38" s="11" t="n"/>
-      <c r="Y38" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y38" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z38" s="10" t="n"/>
@@ -7478,9 +7612,9 @@
       <c r="AC38" s="10" t="n"/>
       <c r="AD38" s="10" t="n"/>
       <c r="AE38" s="11" t="n"/>
-      <c r="AF38" s="19" t="inlineStr">
-        <is>
-          <t>JA ID</t>
+      <c r="AF38" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -7491,14 +7625,14 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C39" s="38" t="n"/>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>tanka_type</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n"/>
       <c r="E39" s="10" t="n"/>
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="10" t="n"/>
@@ -7509,7 +7643,7 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
@@ -7540,7 +7674,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>1: 購読料, 2: 配達手数料</t>
+          <t>登録された単価データ</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -7551,12 +7685,12 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C40" s="38" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C40" s="37" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>tanka_type_label</t>
+          <t>tanka_id</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -7569,7 +7703,7 @@
       <c r="L40" s="11" t="n"/>
       <c r="M40" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N40" s="10" t="n"/>
@@ -7600,7 +7734,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>tanka_typeのラベル</t>
+          <t>単価ID</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -7611,12 +7745,12 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>tanka_code</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -7629,7 +7763,7 @@
       <c r="L41" s="11" t="n"/>
       <c r="M41" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N41" s="10" t="n"/>
@@ -7660,7 +7794,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>単価コード</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -7671,12 +7805,12 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>tanka_name</t>
+          <t>tanka_type</t>
         </is>
       </c>
       <c r="E42" s="10" t="n"/>
@@ -7689,7 +7823,7 @@
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N42" s="10" t="n"/>
@@ -7720,7 +7854,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>単価名</t>
+          <t>1: 購読料, 2: 配達手数料</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -7731,12 +7865,12 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>kingaku_zeikomi</t>
+          <t>tanka_code</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -7749,7 +7883,7 @@
       <c r="L43" s="11" t="n"/>
       <c r="M43" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N43" s="10" t="n"/>
@@ -7769,7 +7903,7 @@
       <c r="X43" s="11" t="n"/>
       <c r="Y43" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z43" s="10" t="n"/>
@@ -7780,7 +7914,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>税込金額（円）</t>
+          <t>単価コード</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -7791,12 +7925,12 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>kingaku_zeinuki</t>
+          <t>tanka_name</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -7809,7 +7943,7 @@
       <c r="L44" s="11" t="n"/>
       <c r="M44" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N44" s="10" t="n"/>
@@ -7829,7 +7963,7 @@
       <c r="X44" s="11" t="n"/>
       <c r="Y44" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z44" s="10" t="n"/>
@@ -7840,7 +7974,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>税抜金額（円）</t>
+          <t>単価名</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -7851,12 +7985,12 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>tax_rate</t>
+          <t>kingaku_zeikomi</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
@@ -7882,11 +8016,7 @@
       </c>
       <c r="R45" s="10" t="n"/>
       <c r="S45" s="11" t="n"/>
-      <c r="T45" s="17" t="inlineStr">
-        <is>
-          <t>##.##</t>
-        </is>
-      </c>
+      <c r="T45" s="17" t="inlineStr"/>
       <c r="U45" s="10" t="n"/>
       <c r="V45" s="10" t="n"/>
       <c r="W45" s="10" t="n"/>
@@ -7904,7 +8034,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>税率（%）</t>
+          <t>税込金額（円）</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -7915,12 +8045,12 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>tekiyo_start_date</t>
+          <t>kingaku_zeinuki</t>
         </is>
       </c>
       <c r="E46" s="10" t="n"/>
@@ -7933,7 +8063,7 @@
       <c r="L46" s="11" t="n"/>
       <c r="M46" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N46" s="10" t="n"/>
@@ -7946,11 +8076,7 @@
       </c>
       <c r="R46" s="10" t="n"/>
       <c r="S46" s="11" t="n"/>
-      <c r="T46" s="17" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
+      <c r="T46" s="17" t="inlineStr"/>
       <c r="U46" s="10" t="n"/>
       <c r="V46" s="10" t="n"/>
       <c r="W46" s="10" t="n"/>
@@ -7968,7 +8094,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>適用開始日</t>
+          <t>税抜金額（円）</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -7979,12 +8105,12 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C47" s="38" t="n"/>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>tekiyo_end_date</t>
+          <t>tax_rate</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -7997,7 +8123,7 @@
       <c r="L47" s="11" t="n"/>
       <c r="M47" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N47" s="10" t="n"/>
@@ -8012,7 +8138,7 @@
       <c r="S47" s="11" t="n"/>
       <c r="T47" s="17" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>##.##</t>
         </is>
       </c>
       <c r="U47" s="10" t="n"/>
@@ -8032,7 +8158,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>適用終了日</t>
+          <t>税率（%）</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -8043,12 +8169,12 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C48" s="38" t="n"/>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>tekiyo_start_date</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
@@ -8076,7 +8202,7 @@
       <c r="S48" s="11" t="n"/>
       <c r="T48" s="17" t="inlineStr">
         <is>
-          <t>ISO8601</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="U48" s="10" t="n"/>
@@ -8085,7 +8211,7 @@
       <c r="X48" s="11" t="n"/>
       <c r="Y48" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z48" s="10" t="n"/>
@@ -8096,7 +8222,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>適用開始日</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -8107,12 +8233,12 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>14</v>
-      </c>
-      <c r="C49" s="39" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="C49" s="38" t="n"/>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>tekiyo_end_date</t>
         </is>
       </c>
       <c r="E49" s="10" t="n"/>
@@ -8140,7 +8266,7 @@
       <c r="S49" s="11" t="n"/>
       <c r="T49" s="17" t="inlineStr">
         <is>
-          <t>ISO8601</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="U49" s="10" t="n"/>
@@ -8160,7 +8286,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>適用終了日</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -8169,16 +8295,324 @@
       <c r="AJ49" s="10" t="n"/>
       <c r="AK49" s="11" t="n"/>
     </row>
-    <row r="50" ht="19.5" customHeight="1"/>
-    <row r="51" ht="19.5" customHeight="1">
-      <c r="B51" s="40" t="inlineStr">
+    <row r="50" ht="36" customHeight="1">
+      <c r="B50" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="C50" s="38" t="n"/>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>active_flg</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="n"/>
+      <c r="J50" s="10" t="n"/>
+      <c r="K50" s="10" t="n"/>
+      <c r="L50" s="11" t="n"/>
+      <c r="M50" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N50" s="10" t="n"/>
+      <c r="O50" s="10" t="n"/>
+      <c r="P50" s="11" t="n"/>
+      <c r="Q50" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="11" t="n"/>
+      <c r="T50" s="17" t="inlineStr"/>
+      <c r="U50" s="10" t="n"/>
+      <c r="V50" s="10" t="n"/>
+      <c r="W50" s="10" t="n"/>
+      <c r="X50" s="11" t="n"/>
+      <c r="Y50" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z50" s="10" t="n"/>
+      <c r="AA50" s="10" t="n"/>
+      <c r="AB50" s="10" t="n"/>
+      <c r="AC50" s="10" t="n"/>
+      <c r="AD50" s="10" t="n"/>
+      <c r="AE50" s="11" t="n"/>
+      <c r="AF50" s="19" t="inlineStr">
+        <is>
+          <t>運用上の有効フラグ（FALSE時は新規割当不可。適用期間とは独立）</t>
+        </is>
+      </c>
+      <c r="AG50" s="10" t="n"/>
+      <c r="AH50" s="10" t="n"/>
+      <c r="AI50" s="10" t="n"/>
+      <c r="AJ50" s="10" t="n"/>
+      <c r="AK50" s="11" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="C51" s="38" t="n"/>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>campaign_flg</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="10" t="n"/>
+      <c r="J51" s="10" t="n"/>
+      <c r="K51" s="10" t="n"/>
+      <c r="L51" s="11" t="n"/>
+      <c r="M51" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="10" t="n"/>
+      <c r="P51" s="11" t="n"/>
+      <c r="Q51" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="11" t="n"/>
+      <c r="T51" s="17" t="inlineStr"/>
+      <c r="U51" s="10" t="n"/>
+      <c r="V51" s="10" t="n"/>
+      <c r="W51" s="10" t="n"/>
+      <c r="X51" s="11" t="n"/>
+      <c r="Y51" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z51" s="10" t="n"/>
+      <c r="AA51" s="10" t="n"/>
+      <c r="AB51" s="10" t="n"/>
+      <c r="AC51" s="10" t="n"/>
+      <c r="AD51" s="10" t="n"/>
+      <c r="AE51" s="11" t="n"/>
+      <c r="AF51" s="19" t="inlineStr">
+        <is>
+          <t>キャンペーンフラグ（TRUE: 有効, FALSE: 無効）</t>
+        </is>
+      </c>
+      <c r="AG51" s="10" t="n"/>
+      <c r="AH51" s="10" t="n"/>
+      <c r="AI51" s="10" t="n"/>
+      <c r="AJ51" s="10" t="n"/>
+      <c r="AK51" s="11" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="19" t="inlineStr">
+        <is>
+          <t>biko</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="10" t="n"/>
+      <c r="J52" s="10" t="n"/>
+      <c r="K52" s="10" t="n"/>
+      <c r="L52" s="11" t="n"/>
+      <c r="M52" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N52" s="10" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="11" t="n"/>
+      <c r="Q52" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="11" t="n"/>
+      <c r="T52" s="17" t="inlineStr"/>
+      <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
+      <c r="W52" s="10" t="n"/>
+      <c r="X52" s="11" t="n"/>
+      <c r="Y52" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z52" s="10" t="n"/>
+      <c r="AA52" s="10" t="n"/>
+      <c r="AB52" s="10" t="n"/>
+      <c r="AC52" s="10" t="n"/>
+      <c r="AD52" s="10" t="n"/>
+      <c r="AE52" s="11" t="n"/>
+      <c r="AF52" s="19" t="inlineStr">
+        <is>
+          <t>備考（NOT NULL、空欄は `""`）</t>
+        </is>
+      </c>
+      <c r="AG52" s="10" t="n"/>
+      <c r="AH52" s="10" t="n"/>
+      <c r="AI52" s="10" t="n"/>
+      <c r="AJ52" s="10" t="n"/>
+      <c r="AK52" s="11" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="C53" s="38" t="n"/>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="10" t="n"/>
+      <c r="J53" s="10" t="n"/>
+      <c r="K53" s="10" t="n"/>
+      <c r="L53" s="11" t="n"/>
+      <c r="M53" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N53" s="10" t="n"/>
+      <c r="O53" s="10" t="n"/>
+      <c r="P53" s="11" t="n"/>
+      <c r="Q53" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="11" t="n"/>
+      <c r="T53" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U53" s="10" t="n"/>
+      <c r="V53" s="10" t="n"/>
+      <c r="W53" s="10" t="n"/>
+      <c r="X53" s="11" t="n"/>
+      <c r="Y53" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z53" s="10" t="n"/>
+      <c r="AA53" s="10" t="n"/>
+      <c r="AB53" s="10" t="n"/>
+      <c r="AC53" s="10" t="n"/>
+      <c r="AD53" s="10" t="n"/>
+      <c r="AE53" s="11" t="n"/>
+      <c r="AF53" s="19" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="AG53" s="10" t="n"/>
+      <c r="AH53" s="10" t="n"/>
+      <c r="AI53" s="10" t="n"/>
+      <c r="AJ53" s="10" t="n"/>
+      <c r="AK53" s="11" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="C54" s="39" t="n"/>
+      <c r="D54" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="n"/>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="11" t="n"/>
+      <c r="M54" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="11" t="n"/>
+      <c r="Q54" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="11" t="n"/>
+      <c r="T54" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="11" t="n"/>
+      <c r="Y54" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+      <c r="AC54" s="10" t="n"/>
+      <c r="AD54" s="10" t="n"/>
+      <c r="AE54" s="11" t="n"/>
+      <c r="AF54" s="19" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AG54" s="10" t="n"/>
+      <c r="AH54" s="10" t="n"/>
+      <c r="AI54" s="10" t="n"/>
+      <c r="AJ54" s="10" t="n"/>
+      <c r="AK54" s="11" t="n"/>
+    </row>
+    <row r="55" ht="19.5" customHeight="1"/>
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="B56" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="234" customHeight="1">
-      <c r="C52" s="19" t="inlineStr">
+    <row r="57" ht="288" customHeight="1">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>POST /api/v1/tanka
 Content-Type: application/json
@@ -8190,61 +8624,63 @@
   "kingaku_zeikomi": 4900,
   "kingaku_zeinuki": 4455,
   "tekiyo_start_date": "2026-04-01",
-  "tekiyo_end_date": null
+  "tekiyo_end_date": null,
+  "active_flg": true,
+  "campaign_flg": false,
+  "biko": ""
 }</t>
         </is>
       </c>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
-      <c r="F52" s="10" t="n"/>
-      <c r="G52" s="10" t="n"/>
-      <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n"/>
-      <c r="J52" s="10" t="n"/>
-      <c r="K52" s="10" t="n"/>
-      <c r="L52" s="10" t="n"/>
-      <c r="M52" s="10" t="n"/>
-      <c r="N52" s="10" t="n"/>
-      <c r="O52" s="10" t="n"/>
-      <c r="P52" s="10" t="n"/>
-      <c r="Q52" s="10" t="n"/>
-      <c r="R52" s="10" t="n"/>
-      <c r="S52" s="10" t="n"/>
-      <c r="T52" s="10" t="n"/>
-      <c r="U52" s="10" t="n"/>
-      <c r="V52" s="10" t="n"/>
-      <c r="W52" s="10" t="n"/>
-      <c r="X52" s="10" t="n"/>
-      <c r="Y52" s="10" t="n"/>
-      <c r="Z52" s="10" t="n"/>
-      <c r="AA52" s="10" t="n"/>
-      <c r="AB52" s="10" t="n"/>
-      <c r="AC52" s="10" t="n"/>
-      <c r="AD52" s="10" t="n"/>
-      <c r="AE52" s="10" t="n"/>
-      <c r="AF52" s="10" t="n"/>
-      <c r="AG52" s="10" t="n"/>
-      <c r="AH52" s="10" t="n"/>
-      <c r="AI52" s="10" t="n"/>
-      <c r="AJ52" s="10" t="n"/>
-      <c r="AK52" s="11" t="n"/>
-    </row>
-    <row r="54" ht="19.5" customHeight="1">
-      <c r="B54" s="40" t="inlineStr">
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="10" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="10" t="n"/>
+      <c r="X57" s="10" t="n"/>
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="10" t="n"/>
+      <c r="AE57" s="10" t="n"/>
+      <c r="AF57" s="10" t="n"/>
+      <c r="AG57" s="10" t="n"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="10" t="n"/>
+      <c r="AJ57" s="10" t="n"/>
+      <c r="AK57" s="11" t="n"/>
+    </row>
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="B59" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="306" customHeight="1">
-      <c r="C55" s="19" t="inlineStr">
+    <row r="60" ht="342" customHeight="1">
+      <c r="C60" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
     "tanka_id": 10,
     "ja_id": 1,
     "tanka_type": 1,
-    "tanka_type_label": "新聞購読料",
     "tanka_code": "T001",
     "tanka_name": "基本購読料（月額）",
     "kingaku_zeikomi": 4900,
@@ -8252,56 +8688,59 @@
     "tax_rate": 10.0,
     "tekiyo_start_date": "2026-04-01",
     "tekiyo_end_date": null,
+    "active_flg": true,
+    "campaign_flg": false,
+    "biko": "",
     "created_at": "2026-04-09T10:00:00Z",
     "updated_at": null
   }
 }</t>
         </is>
       </c>
-      <c r="D55" s="10" t="n"/>
-      <c r="E55" s="10" t="n"/>
-      <c r="F55" s="10" t="n"/>
-      <c r="G55" s="10" t="n"/>
-      <c r="H55" s="10" t="n"/>
-      <c r="I55" s="10" t="n"/>
-      <c r="J55" s="10" t="n"/>
-      <c r="K55" s="10" t="n"/>
-      <c r="L55" s="10" t="n"/>
-      <c r="M55" s="10" t="n"/>
-      <c r="N55" s="10" t="n"/>
-      <c r="O55" s="10" t="n"/>
-      <c r="P55" s="10" t="n"/>
-      <c r="Q55" s="10" t="n"/>
-      <c r="R55" s="10" t="n"/>
-      <c r="S55" s="10" t="n"/>
-      <c r="T55" s="10" t="n"/>
-      <c r="U55" s="10" t="n"/>
-      <c r="V55" s="10" t="n"/>
-      <c r="W55" s="10" t="n"/>
-      <c r="X55" s="10" t="n"/>
-      <c r="Y55" s="10" t="n"/>
-      <c r="Z55" s="10" t="n"/>
-      <c r="AA55" s="10" t="n"/>
-      <c r="AB55" s="10" t="n"/>
-      <c r="AC55" s="10" t="n"/>
-      <c r="AD55" s="10" t="n"/>
-      <c r="AE55" s="10" t="n"/>
-      <c r="AF55" s="10" t="n"/>
-      <c r="AG55" s="10" t="n"/>
-      <c r="AH55" s="10" t="n"/>
-      <c r="AI55" s="10" t="n"/>
-      <c r="AJ55" s="10" t="n"/>
-      <c r="AK55" s="11" t="n"/>
-    </row>
-    <row r="57" ht="19.5" customHeight="1">
-      <c r="B57" s="40" t="inlineStr">
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="10" t="n"/>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="10" t="n"/>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="10" t="n"/>
+      <c r="X60" s="10" t="n"/>
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="10" t="n"/>
+      <c r="AE60" s="10" t="n"/>
+      <c r="AF60" s="10" t="n"/>
+      <c r="AG60" s="10" t="n"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="10" t="n"/>
+      <c r="AJ60" s="10" t="n"/>
+      <c r="AK60" s="11" t="n"/>
+    </row>
+    <row r="62" ht="19.5" customHeight="1">
+      <c r="B62" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request）</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="144" customHeight="1">
-      <c r="C58" s="19" t="inlineStr">
+    <row r="63" ht="144" customHeight="1">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
@@ -8313,50 +8752,50 @@
 }</t>
         </is>
       </c>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
-      <c r="F58" s="10" t="n"/>
-      <c r="G58" s="10" t="n"/>
-      <c r="H58" s="10" t="n"/>
-      <c r="I58" s="10" t="n"/>
-      <c r="J58" s="10" t="n"/>
-      <c r="K58" s="10" t="n"/>
-      <c r="L58" s="10" t="n"/>
-      <c r="M58" s="10" t="n"/>
-      <c r="N58" s="10" t="n"/>
-      <c r="O58" s="10" t="n"/>
-      <c r="P58" s="10" t="n"/>
-      <c r="Q58" s="10" t="n"/>
-      <c r="R58" s="10" t="n"/>
-      <c r="S58" s="10" t="n"/>
-      <c r="T58" s="10" t="n"/>
-      <c r="U58" s="10" t="n"/>
-      <c r="V58" s="10" t="n"/>
-      <c r="W58" s="10" t="n"/>
-      <c r="X58" s="10" t="n"/>
-      <c r="Y58" s="10" t="n"/>
-      <c r="Z58" s="10" t="n"/>
-      <c r="AA58" s="10" t="n"/>
-      <c r="AB58" s="10" t="n"/>
-      <c r="AC58" s="10" t="n"/>
-      <c r="AD58" s="10" t="n"/>
-      <c r="AE58" s="10" t="n"/>
-      <c r="AF58" s="10" t="n"/>
-      <c r="AG58" s="10" t="n"/>
-      <c r="AH58" s="10" t="n"/>
-      <c r="AI58" s="10" t="n"/>
-      <c r="AJ58" s="10" t="n"/>
-      <c r="AK58" s="11" t="n"/>
-    </row>
-    <row r="60" ht="19.5" customHeight="1">
-      <c r="B60" s="40" t="inlineStr">
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="10" t="n"/>
+      <c r="J63" s="10" t="n"/>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="10" t="n"/>
+      <c r="Q63" s="10" t="n"/>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="10" t="n"/>
+      <c r="X63" s="10" t="n"/>
+      <c r="Y63" s="10" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="10" t="n"/>
+      <c r="AE63" s="10" t="n"/>
+      <c r="AF63" s="10" t="n"/>
+      <c r="AG63" s="10" t="n"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="10" t="n"/>
+      <c r="AJ63" s="10" t="n"/>
+      <c r="AK63" s="11" t="n"/>
+    </row>
+    <row r="65" ht="19.5" customHeight="1">
+      <c r="B65" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="72" customHeight="1">
-      <c r="C61" s="19" t="inlineStr">
+    <row r="66" ht="72" customHeight="1">
+      <c r="C66" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -8364,50 +8803,50 @@
 }</t>
         </is>
       </c>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="10" t="n"/>
-      <c r="F61" s="10" t="n"/>
-      <c r="G61" s="10" t="n"/>
-      <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="n"/>
-      <c r="J61" s="10" t="n"/>
-      <c r="K61" s="10" t="n"/>
-      <c r="L61" s="10" t="n"/>
-      <c r="M61" s="10" t="n"/>
-      <c r="N61" s="10" t="n"/>
-      <c r="O61" s="10" t="n"/>
-      <c r="P61" s="10" t="n"/>
-      <c r="Q61" s="10" t="n"/>
-      <c r="R61" s="10" t="n"/>
-      <c r="S61" s="10" t="n"/>
-      <c r="T61" s="10" t="n"/>
-      <c r="U61" s="10" t="n"/>
-      <c r="V61" s="10" t="n"/>
-      <c r="W61" s="10" t="n"/>
-      <c r="X61" s="10" t="n"/>
-      <c r="Y61" s="10" t="n"/>
-      <c r="Z61" s="10" t="n"/>
-      <c r="AA61" s="10" t="n"/>
-      <c r="AB61" s="10" t="n"/>
-      <c r="AC61" s="10" t="n"/>
-      <c r="AD61" s="10" t="n"/>
-      <c r="AE61" s="10" t="n"/>
-      <c r="AF61" s="10" t="n"/>
-      <c r="AG61" s="10" t="n"/>
-      <c r="AH61" s="10" t="n"/>
-      <c r="AI61" s="10" t="n"/>
-      <c r="AJ61" s="10" t="n"/>
-      <c r="AK61" s="11" t="n"/>
-    </row>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="B63" s="40" t="inlineStr">
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="10" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="10" t="n"/>
+      <c r="J66" s="10" t="n"/>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="10" t="n"/>
+      <c r="Q66" s="10" t="n"/>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="10" t="n"/>
+      <c r="X66" s="10" t="n"/>
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="10" t="n"/>
+      <c r="AD66" s="10" t="n"/>
+      <c r="AE66" s="10" t="n"/>
+      <c r="AF66" s="10" t="n"/>
+      <c r="AG66" s="10" t="n"/>
+      <c r="AH66" s="10" t="n"/>
+      <c r="AI66" s="10" t="n"/>
+      <c r="AJ66" s="10" t="n"/>
+      <c r="AK66" s="11" t="n"/>
+    </row>
+    <row r="68" ht="19.5" customHeight="1">
+      <c r="B68" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="72" customHeight="1">
-      <c r="C64" s="19" t="inlineStr">
+    <row r="69" ht="72" customHeight="1">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -8415,50 +8854,50 @@
 }</t>
         </is>
       </c>
-      <c r="D64" s="10" t="n"/>
-      <c r="E64" s="10" t="n"/>
-      <c r="F64" s="10" t="n"/>
-      <c r="G64" s="10" t="n"/>
-      <c r="H64" s="10" t="n"/>
-      <c r="I64" s="10" t="n"/>
-      <c r="J64" s="10" t="n"/>
-      <c r="K64" s="10" t="n"/>
-      <c r="L64" s="10" t="n"/>
-      <c r="M64" s="10" t="n"/>
-      <c r="N64" s="10" t="n"/>
-      <c r="O64" s="10" t="n"/>
-      <c r="P64" s="10" t="n"/>
-      <c r="Q64" s="10" t="n"/>
-      <c r="R64" s="10" t="n"/>
-      <c r="S64" s="10" t="n"/>
-      <c r="T64" s="10" t="n"/>
-      <c r="U64" s="10" t="n"/>
-      <c r="V64" s="10" t="n"/>
-      <c r="W64" s="10" t="n"/>
-      <c r="X64" s="10" t="n"/>
-      <c r="Y64" s="10" t="n"/>
-      <c r="Z64" s="10" t="n"/>
-      <c r="AA64" s="10" t="n"/>
-      <c r="AB64" s="10" t="n"/>
-      <c r="AC64" s="10" t="n"/>
-      <c r="AD64" s="10" t="n"/>
-      <c r="AE64" s="10" t="n"/>
-      <c r="AF64" s="10" t="n"/>
-      <c r="AG64" s="10" t="n"/>
-      <c r="AH64" s="10" t="n"/>
-      <c r="AI64" s="10" t="n"/>
-      <c r="AJ64" s="10" t="n"/>
-      <c r="AK64" s="11" t="n"/>
-    </row>
-    <row r="66" ht="19.5" customHeight="1">
-      <c r="B66" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（失敗 409 Conflict）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="72" customHeight="1">
-      <c r="C67" s="19" t="inlineStr">
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="10" t="n"/>
+      <c r="J69" s="10" t="n"/>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="10" t="n"/>
+      <c r="Q69" s="10" t="n"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="10" t="n"/>
+      <c r="X69" s="10" t="n"/>
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="10" t="n"/>
+      <c r="AD69" s="10" t="n"/>
+      <c r="AE69" s="10" t="n"/>
+      <c r="AF69" s="10" t="n"/>
+      <c r="AG69" s="10" t="n"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="10" t="n"/>
+      <c r="AJ69" s="10" t="n"/>
+      <c r="AK69" s="11" t="n"/>
+    </row>
+    <row r="71" ht="19.5" customHeight="1">
+      <c r="B71" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 400 Bad Request（重複））</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="72" customHeight="1">
+      <c r="C72" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "DUPLICATE_CODE",
@@ -8466,50 +8905,50 @@
 }</t>
         </is>
       </c>
-      <c r="D67" s="10" t="n"/>
-      <c r="E67" s="10" t="n"/>
-      <c r="F67" s="10" t="n"/>
-      <c r="G67" s="10" t="n"/>
-      <c r="H67" s="10" t="n"/>
-      <c r="I67" s="10" t="n"/>
-      <c r="J67" s="10" t="n"/>
-      <c r="K67" s="10" t="n"/>
-      <c r="L67" s="10" t="n"/>
-      <c r="M67" s="10" t="n"/>
-      <c r="N67" s="10" t="n"/>
-      <c r="O67" s="10" t="n"/>
-      <c r="P67" s="10" t="n"/>
-      <c r="Q67" s="10" t="n"/>
-      <c r="R67" s="10" t="n"/>
-      <c r="S67" s="10" t="n"/>
-      <c r="T67" s="10" t="n"/>
-      <c r="U67" s="10" t="n"/>
-      <c r="V67" s="10" t="n"/>
-      <c r="W67" s="10" t="n"/>
-      <c r="X67" s="10" t="n"/>
-      <c r="Y67" s="10" t="n"/>
-      <c r="Z67" s="10" t="n"/>
-      <c r="AA67" s="10" t="n"/>
-      <c r="AB67" s="10" t="n"/>
-      <c r="AC67" s="10" t="n"/>
-      <c r="AD67" s="10" t="n"/>
-      <c r="AE67" s="10" t="n"/>
-      <c r="AF67" s="10" t="n"/>
-      <c r="AG67" s="10" t="n"/>
-      <c r="AH67" s="10" t="n"/>
-      <c r="AI67" s="10" t="n"/>
-      <c r="AJ67" s="10" t="n"/>
-      <c r="AK67" s="11" t="n"/>
-    </row>
-    <row r="69" ht="19.5" customHeight="1">
-      <c r="B69" s="40" t="inlineStr">
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="10" t="n"/>
+      <c r="J72" s="10" t="n"/>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="10" t="n"/>
+      <c r="Q72" s="10" t="n"/>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="10" t="n"/>
+      <c r="X72" s="10" t="n"/>
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="10" t="n"/>
+      <c r="AD72" s="10" t="n"/>
+      <c r="AE72" s="10" t="n"/>
+      <c r="AF72" s="10" t="n"/>
+      <c r="AG72" s="10" t="n"/>
+      <c r="AH72" s="10" t="n"/>
+      <c r="AI72" s="10" t="n"/>
+      <c r="AJ72" s="10" t="n"/>
+      <c r="AK72" s="11" t="n"/>
+    </row>
+    <row r="74" ht="19.5" customHeight="1">
+      <c r="B74" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="72" customHeight="1">
-      <c r="C70" s="19" t="inlineStr">
+    <row r="75" ht="72" customHeight="1">
+      <c r="C75" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -8517,272 +8956,232 @@
 }</t>
         </is>
       </c>
-      <c r="D70" s="10" t="n"/>
-      <c r="E70" s="10" t="n"/>
-      <c r="F70" s="10" t="n"/>
-      <c r="G70" s="10" t="n"/>
-      <c r="H70" s="10" t="n"/>
-      <c r="I70" s="10" t="n"/>
-      <c r="J70" s="10" t="n"/>
-      <c r="K70" s="10" t="n"/>
-      <c r="L70" s="10" t="n"/>
-      <c r="M70" s="10" t="n"/>
-      <c r="N70" s="10" t="n"/>
-      <c r="O70" s="10" t="n"/>
-      <c r="P70" s="10" t="n"/>
-      <c r="Q70" s="10" t="n"/>
-      <c r="R70" s="10" t="n"/>
-      <c r="S70" s="10" t="n"/>
-      <c r="T70" s="10" t="n"/>
-      <c r="U70" s="10" t="n"/>
-      <c r="V70" s="10" t="n"/>
-      <c r="W70" s="10" t="n"/>
-      <c r="X70" s="10" t="n"/>
-      <c r="Y70" s="10" t="n"/>
-      <c r="Z70" s="10" t="n"/>
-      <c r="AA70" s="10" t="n"/>
-      <c r="AB70" s="10" t="n"/>
-      <c r="AC70" s="10" t="n"/>
-      <c r="AD70" s="10" t="n"/>
-      <c r="AE70" s="10" t="n"/>
-      <c r="AF70" s="10" t="n"/>
-      <c r="AG70" s="10" t="n"/>
-      <c r="AH70" s="10" t="n"/>
-      <c r="AI70" s="10" t="n"/>
-      <c r="AJ70" s="10" t="n"/>
-      <c r="AK70" s="11" t="n"/>
-    </row>
-    <row r="72" ht="19.5" customHeight="1"/>
-    <row r="73" ht="19.5" customHeight="1">
-      <c r="A73" s="27" t="inlineStr">
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="10" t="n"/>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="10" t="n"/>
+      <c r="J75" s="10" t="n"/>
+      <c r="K75" s="10" t="n"/>
+      <c r="L75" s="10" t="n"/>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="10" t="n"/>
+      <c r="Q75" s="10" t="n"/>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
+      <c r="T75" s="10" t="n"/>
+      <c r="U75" s="10" t="n"/>
+      <c r="V75" s="10" t="n"/>
+      <c r="W75" s="10" t="n"/>
+      <c r="X75" s="10" t="n"/>
+      <c r="Y75" s="10" t="n"/>
+      <c r="Z75" s="10" t="n"/>
+      <c r="AA75" s="10" t="n"/>
+      <c r="AB75" s="10" t="n"/>
+      <c r="AC75" s="10" t="n"/>
+      <c r="AD75" s="10" t="n"/>
+      <c r="AE75" s="10" t="n"/>
+      <c r="AF75" s="10" t="n"/>
+      <c r="AG75" s="10" t="n"/>
+      <c r="AH75" s="10" t="n"/>
+      <c r="AI75" s="10" t="n"/>
+      <c r="AJ75" s="10" t="n"/>
+      <c r="AK75" s="11" t="n"/>
+    </row>
+    <row r="77" ht="19.5" customHeight="1"/>
+    <row r="78" ht="19.5" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="B74" s="27" t="inlineStr">
+    <row r="79" ht="54" customHeight="1">
+      <c r="B79" s="42" t="inlineStr">
+        <is>
+          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="10" t="n"/>
+      <c r="J79" s="10" t="n"/>
+      <c r="K79" s="10" t="n"/>
+      <c r="L79" s="10" t="n"/>
+      <c r="M79" s="10" t="n"/>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="10" t="n"/>
+      <c r="Q79" s="10" t="n"/>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="10" t="n"/>
+      <c r="T79" s="10" t="n"/>
+      <c r="U79" s="10" t="n"/>
+      <c r="V79" s="10" t="n"/>
+      <c r="W79" s="10" t="n"/>
+      <c r="X79" s="10" t="n"/>
+      <c r="Y79" s="10" t="n"/>
+      <c r="Z79" s="10" t="n"/>
+      <c r="AA79" s="10" t="n"/>
+      <c r="AB79" s="10" t="n"/>
+      <c r="AC79" s="10" t="n"/>
+      <c r="AD79" s="10" t="n"/>
+      <c r="AE79" s="10" t="n"/>
+      <c r="AF79" s="10" t="n"/>
+      <c r="AG79" s="10" t="n"/>
+      <c r="AH79" s="10" t="n"/>
+      <c r="AI79" s="10" t="n"/>
+      <c r="AJ79" s="10" t="n"/>
+      <c r="AK79" s="11" t="n"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="B80" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="C75" s="41" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="C81" s="41" t="inlineStr">
         <is>
           <t>リクエストボディの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="D76" s="41" t="inlineStr">
-        <is>
-          <t>tanka_type：必須、1 または 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="D77" s="41" t="inlineStr">
-        <is>
-          <t>tanka_code：必須、最大10桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="D78" s="41" t="inlineStr">
-        <is>
-          <t>tanka_name：必須、最大100桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="D79" s="41" t="inlineStr">
-        <is>
-          <t>tax_rate：0〜100、小数点以下2桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="D80" s="41" t="inlineStr">
-        <is>
-          <t>kingaku_zeikomi：≧ 0、数値</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="D81" s="41" t="inlineStr">
-        <is>
-          <t>kingaku_zeinuki：≧ 0、数値</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="D82" s="41" t="inlineStr">
         <is>
-          <t>tekiyo_start_date：有効な日付形式（YYYY-MM-DD）、新規登録時は過去日不可</t>
+          <t>tanka_type：必須、1 または 2</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="D83" s="41" t="inlineStr">
         <is>
-          <t>tekiyo_end_date：有効な日付形式、tekiyo_start_date 以降</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="36" customHeight="1">
-      <c r="C84" s="41" t="inlineStr">
-        <is>
-          <t>バリデーションエラーの場合：HTTP 422 (`VALIDATION_ERROR`) + errors配列</t>
+          <t>tanka_code：必須、最大10桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="D84" s="41" t="inlineStr">
+        <is>
+          <t>tanka_name：必須、最大100桁</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="B85" s="27" t="inlineStr">
+      <c r="D85" s="41" t="inlineStr">
+        <is>
+          <t>tax_rate：0〜100、小数点以下2桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="D86" s="41" t="inlineStr">
+        <is>
+          <t>kingaku_zeikomi：≧ 0、数値</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="D87" s="41" t="inlineStr">
+        <is>
+          <t>kingaku_zeinuki：≧ 0、数値</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="D88" s="41" t="inlineStr">
+        <is>
+          <t>tekiyo_start_date：有効な日付形式（YYYY-MM-DD）、新規登録時は過去日不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
+      <c r="C89" s="41" t="inlineStr">
+        <is>
+          <t>バリデーションエラーの場合：HTTP 400 (`VALIDATION_ERROR`) + errors配列</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="B90" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="C86" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="C87" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="C88" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：`tanka.create` を保持しているか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="36" customHeight="1">
-      <c r="D89" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="C90" s="41" t="inlineStr">
-        <is>
-          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="B91" s="27" t="inlineStr">
-        <is>
-          <t>4.3 重複チェック</t>
+      <c r="C91" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="C92" s="41" t="inlineStr">
         <is>
-          <t>ログインユーザーのスコープを取得する（ja_id）。</t>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="C93" s="41" t="inlineStr">
         <is>
-          <t>以下の条件で重複を確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="54" customHeight="1">
-      <c r="C94" s="42" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) FROM m_tanka
-WHERE tanka_code = :tanka_code
-  AND deleted_at IS NULL</t>
-        </is>
-      </c>
-      <c r="D94" s="10" t="n"/>
-      <c r="E94" s="10" t="n"/>
-      <c r="F94" s="10" t="n"/>
-      <c r="G94" s="10" t="n"/>
-      <c r="H94" s="10" t="n"/>
-      <c r="I94" s="10" t="n"/>
-      <c r="J94" s="10" t="n"/>
-      <c r="K94" s="10" t="n"/>
-      <c r="L94" s="10" t="n"/>
-      <c r="M94" s="10" t="n"/>
-      <c r="N94" s="10" t="n"/>
-      <c r="O94" s="10" t="n"/>
-      <c r="P94" s="10" t="n"/>
-      <c r="Q94" s="10" t="n"/>
-      <c r="R94" s="10" t="n"/>
-      <c r="S94" s="10" t="n"/>
-      <c r="T94" s="10" t="n"/>
-      <c r="U94" s="10" t="n"/>
-      <c r="V94" s="10" t="n"/>
-      <c r="W94" s="10" t="n"/>
-      <c r="X94" s="10" t="n"/>
-      <c r="Y94" s="10" t="n"/>
-      <c r="Z94" s="10" t="n"/>
-      <c r="AA94" s="10" t="n"/>
-      <c r="AB94" s="10" t="n"/>
-      <c r="AC94" s="10" t="n"/>
-      <c r="AD94" s="10" t="n"/>
-      <c r="AE94" s="10" t="n"/>
-      <c r="AF94" s="10" t="n"/>
-      <c r="AG94" s="10" t="n"/>
-      <c r="AH94" s="10" t="n"/>
-      <c r="AI94" s="10" t="n"/>
-      <c r="AJ94" s="10" t="n"/>
-      <c r="AK94" s="11" t="n"/>
+          <t>権限チェック：`tanka.create` を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="36" customHeight="1">
+      <c r="D94" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="C95" s="41" t="inlineStr">
         <is>
-          <t>重複がある場合：HTTP 409 (`DUPLICATE_CODE`)</t>
+          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="B96" s="27" t="inlineStr">
         <is>
-          <t>4.4 データ登録</t>
+          <t>4.3 重複チェック</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="C97" s="41" t="inlineStr">
         <is>
-          <t>tekiyo_start_date が空の場合、CURRENT_DATE を設定する。</t>
+          <t>ログインユーザーのスコープを取得する（ja_id）。</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="C98" s="41" t="inlineStr">
         <is>
-          <t>以下のSQLを実行して登録する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="162" customHeight="1">
+          <t>以下の条件で重複を確認する。**単価コードの一意性は JA 単位**（DB の</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="54" customHeight="1">
       <c r="C99" s="42" t="inlineStr">
         <is>
-          <t>INSERT INTO m_tanka (ja_id, tanka_type, tanka_code, tanka_name,
-                     kingaku_zeikomi, kingaku_zeinuki, tax_rate,
-                     tekiyo_start_date, tekiyo_end_date,
-                     created_at, created_by, updated_at, updated_by)
-VALUES (:ja_id, :tanka_type, :tanka_code, :tanka_name,
-        :kingaku_zeikomi, :kingaku_zeinuki, :tax_rate,
-        :tekiyo_start_date, :tekiyo_end_date,
-        NOW(), :user_account_id, NOW(), :user_account_id)
-RETURNING *</t>
+          <t>SELECT COUNT(*) FROM m_tanka
+WHERE ja_id = :ja_id
+  AND tanka_code = :tanka_code</t>
         </is>
       </c>
       <c r="D99" s="10" t="n"/>
@@ -8820,22 +9219,106 @@
       <c r="AJ99" s="10" t="n"/>
       <c r="AK99" s="11" t="n"/>
     </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="B100" s="27" t="inlineStr">
-        <is>
-          <t>4.5 操作ログ記録</t>
+    <row r="100" ht="36" customHeight="1">
+      <c r="C100" s="41" t="inlineStr">
+        <is>
+          <t>`deleted_at` では絞らない。DB の UNIQUE INDEX に `deleted_at` の条件が無く、</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="C101" s="41" t="inlineStr">
         <is>
+          <t>重複がある場合：HTTP 400 (`DUPLICATE_CODE`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="B102" s="27" t="inlineStr">
+        <is>
+          <t>4.4 データ登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="C103" s="41" t="inlineStr">
+        <is>
+          <t>tekiyo_start_date が空の場合、CURRENT_DATE を設定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="C104" s="41" t="inlineStr">
+        <is>
+          <t>以下のSQLを実行して登録する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="162" customHeight="1">
+      <c r="C105" s="42" t="inlineStr">
+        <is>
+          <t>INSERT INTO m_tanka (ja_id, tanka_type, tanka_code, tanka_name,
+                     kingaku_zeikomi, kingaku_zeinuki, tax_rate,
+                     tekiyo_start_date, tekiyo_end_date,
+                     created_at, created_by, updated_at, updated_by)
+VALUES (:ja_id, :tanka_type, :tanka_code, :tanka_name,
+        :kingaku_zeikomi, :kingaku_zeinuki, :tax_rate,
+        :tekiyo_start_date, :tekiyo_end_date,
+        NOW(), :user_account_id, NOW(), :user_account_id)
+RETURNING *</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="n"/>
+      <c r="E105" s="10" t="n"/>
+      <c r="F105" s="10" t="n"/>
+      <c r="G105" s="10" t="n"/>
+      <c r="H105" s="10" t="n"/>
+      <c r="I105" s="10" t="n"/>
+      <c r="J105" s="10" t="n"/>
+      <c r="K105" s="10" t="n"/>
+      <c r="L105" s="10" t="n"/>
+      <c r="M105" s="10" t="n"/>
+      <c r="N105" s="10" t="n"/>
+      <c r="O105" s="10" t="n"/>
+      <c r="P105" s="10" t="n"/>
+      <c r="Q105" s="10" t="n"/>
+      <c r="R105" s="10" t="n"/>
+      <c r="S105" s="10" t="n"/>
+      <c r="T105" s="10" t="n"/>
+      <c r="U105" s="10" t="n"/>
+      <c r="V105" s="10" t="n"/>
+      <c r="W105" s="10" t="n"/>
+      <c r="X105" s="10" t="n"/>
+      <c r="Y105" s="10" t="n"/>
+      <c r="Z105" s="10" t="n"/>
+      <c r="AA105" s="10" t="n"/>
+      <c r="AB105" s="10" t="n"/>
+      <c r="AC105" s="10" t="n"/>
+      <c r="AD105" s="10" t="n"/>
+      <c r="AE105" s="10" t="n"/>
+      <c r="AF105" s="10" t="n"/>
+      <c r="AG105" s="10" t="n"/>
+      <c r="AH105" s="10" t="n"/>
+      <c r="AI105" s="10" t="n"/>
+      <c r="AJ105" s="10" t="n"/>
+      <c r="AK105" s="11" t="n"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="B106" s="27" t="inlineStr">
+        <is>
+          <t>4.5 操作ログ記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="C107" s="41" t="inlineStr">
+        <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="216" customHeight="1">
-      <c r="C102" s="42" t="inlineStr">
+    <row r="108" ht="216" customHeight="1">
+      <c r="C108" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -8851,43 +9334,43 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D102" s="10" t="n"/>
-      <c r="E102" s="10" t="n"/>
-      <c r="F102" s="10" t="n"/>
-      <c r="G102" s="10" t="n"/>
-      <c r="H102" s="10" t="n"/>
-      <c r="I102" s="10" t="n"/>
-      <c r="J102" s="10" t="n"/>
-      <c r="K102" s="10" t="n"/>
-      <c r="L102" s="10" t="n"/>
-      <c r="M102" s="10" t="n"/>
-      <c r="N102" s="10" t="n"/>
-      <c r="O102" s="10" t="n"/>
-      <c r="P102" s="10" t="n"/>
-      <c r="Q102" s="10" t="n"/>
-      <c r="R102" s="10" t="n"/>
-      <c r="S102" s="10" t="n"/>
-      <c r="T102" s="10" t="n"/>
-      <c r="U102" s="10" t="n"/>
-      <c r="V102" s="10" t="n"/>
-      <c r="W102" s="10" t="n"/>
-      <c r="X102" s="10" t="n"/>
-      <c r="Y102" s="10" t="n"/>
-      <c r="Z102" s="10" t="n"/>
-      <c r="AA102" s="10" t="n"/>
-      <c r="AB102" s="10" t="n"/>
-      <c r="AC102" s="10" t="n"/>
-      <c r="AD102" s="10" t="n"/>
-      <c r="AE102" s="10" t="n"/>
-      <c r="AF102" s="10" t="n"/>
-      <c r="AG102" s="10" t="n"/>
-      <c r="AH102" s="10" t="n"/>
-      <c r="AI102" s="10" t="n"/>
-      <c r="AJ102" s="10" t="n"/>
-      <c r="AK102" s="11" t="n"/>
-    </row>
-    <row r="103" ht="270" customHeight="1">
-      <c r="C103" s="42" t="inlineStr">
+      <c r="D108" s="10" t="n"/>
+      <c r="E108" s="10" t="n"/>
+      <c r="F108" s="10" t="n"/>
+      <c r="G108" s="10" t="n"/>
+      <c r="H108" s="10" t="n"/>
+      <c r="I108" s="10" t="n"/>
+      <c r="J108" s="10" t="n"/>
+      <c r="K108" s="10" t="n"/>
+      <c r="L108" s="10" t="n"/>
+      <c r="M108" s="10" t="n"/>
+      <c r="N108" s="10" t="n"/>
+      <c r="O108" s="10" t="n"/>
+      <c r="P108" s="10" t="n"/>
+      <c r="Q108" s="10" t="n"/>
+      <c r="R108" s="10" t="n"/>
+      <c r="S108" s="10" t="n"/>
+      <c r="T108" s="10" t="n"/>
+      <c r="U108" s="10" t="n"/>
+      <c r="V108" s="10" t="n"/>
+      <c r="W108" s="10" t="n"/>
+      <c r="X108" s="10" t="n"/>
+      <c r="Y108" s="10" t="n"/>
+      <c r="Z108" s="10" t="n"/>
+      <c r="AA108" s="10" t="n"/>
+      <c r="AB108" s="10" t="n"/>
+      <c r="AC108" s="10" t="n"/>
+      <c r="AD108" s="10" t="n"/>
+      <c r="AE108" s="10" t="n"/>
+      <c r="AF108" s="10" t="n"/>
+      <c r="AG108" s="10" t="n"/>
+      <c r="AH108" s="10" t="n"/>
+      <c r="AI108" s="10" t="n"/>
+      <c r="AJ108" s="10" t="n"/>
+      <c r="AK108" s="11" t="n"/>
+    </row>
+    <row r="109" ht="324" customHeight="1">
+      <c r="C109" s="42" t="inlineStr">
         <is>
           <t>`before_value`：INSERT のため空文字列を設定する。
 `after_value`：登録されたデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
@@ -8901,95 +9384,11 @@
   "kingaku_zeinuki": 4455,
   "tax_rate": 10.0,
   "tekiyo_start_date": "2026-04-01",
-  "tekiyo_end_date": null
+  "tekiyo_end_date": null,
+  "active_flg": true,
+  "campaign_flg": false,
+  "biko": ""
 }</t>
-        </is>
-      </c>
-      <c r="D103" s="10" t="n"/>
-      <c r="E103" s="10" t="n"/>
-      <c r="F103" s="10" t="n"/>
-      <c r="G103" s="10" t="n"/>
-      <c r="H103" s="10" t="n"/>
-      <c r="I103" s="10" t="n"/>
-      <c r="J103" s="10" t="n"/>
-      <c r="K103" s="10" t="n"/>
-      <c r="L103" s="10" t="n"/>
-      <c r="M103" s="10" t="n"/>
-      <c r="N103" s="10" t="n"/>
-      <c r="O103" s="10" t="n"/>
-      <c r="P103" s="10" t="n"/>
-      <c r="Q103" s="10" t="n"/>
-      <c r="R103" s="10" t="n"/>
-      <c r="S103" s="10" t="n"/>
-      <c r="T103" s="10" t="n"/>
-      <c r="U103" s="10" t="n"/>
-      <c r="V103" s="10" t="n"/>
-      <c r="W103" s="10" t="n"/>
-      <c r="X103" s="10" t="n"/>
-      <c r="Y103" s="10" t="n"/>
-      <c r="Z103" s="10" t="n"/>
-      <c r="AA103" s="10" t="n"/>
-      <c r="AB103" s="10" t="n"/>
-      <c r="AC103" s="10" t="n"/>
-      <c r="AD103" s="10" t="n"/>
-      <c r="AE103" s="10" t="n"/>
-      <c r="AF103" s="10" t="n"/>
-      <c r="AG103" s="10" t="n"/>
-      <c r="AH103" s="10" t="n"/>
-      <c r="AI103" s="10" t="n"/>
-      <c r="AJ103" s="10" t="n"/>
-      <c r="AK103" s="11" t="n"/>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="B104" s="27" t="inlineStr">
-        <is>
-          <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="C105" s="41" t="inlineStr">
-        <is>
-          <t>登録されたデータをdata オブジェクトとして返却する。HTTP 201。</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="B106" s="27" t="inlineStr">
-        <is>
-          <t>4.7 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="C107" s="41" t="inlineStr">
-        <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="C108" s="41" t="inlineStr">
-        <is>
-          <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="216" customHeight="1">
-      <c r="C109" s="42" t="inlineStr">
-        <is>
-          <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
-                   gamen_name, operation, result_status,
-                   target_id, target_table,
-                   before_value, after_value,
-                   error_message, stack_trace,
-                   ip_address, user_agent)
-VALUES (3, NOW(), :account_id, :ja_id,
-        '単価マスタ登録画面 (ACSMS-SCR-003)', 'CREATE', 2,
-        NULL, 'm_tanka',
-        '', '',
-        :error_message, :stack_trace,
-        :ip_address, :user_agent)</t>
         </is>
       </c>
       <c r="D109" s="10" t="n"/>
@@ -9027,210 +9426,326 @@
       <c r="AJ109" s="10" t="n"/>
       <c r="AK109" s="11" t="n"/>
     </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="B110" s="27" t="inlineStr">
+        <is>
+          <t>4.6 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="C111" s="41" t="inlineStr">
+        <is>
+          <t>登録されたデータをdata オブジェクトとして返却する。HTTP 201。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="B112" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="C113" s="41" t="inlineStr">
+        <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="C114" s="41" t="inlineStr">
+        <is>
+          <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="216" customHeight="1">
+      <c r="C115" s="42" t="inlineStr">
+        <is>
+          <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
+                   gamen_name, operation, result_status,
+                   target_id, target_table,
+                   before_value, after_value,
+                   error_message, stack_trace,
+                   ip_address, user_agent)
+VALUES (3, NOW(), :account_id, :ja_id,
+        '単価マスタ登録画面 (ACSMS-SCR-003)', 'CREATE', 2,
+        NULL, 'm_tanka',
+        '', '',
+        :error_message, :stack_trace,
+        :ip_address, :user_agent)</t>
+        </is>
+      </c>
+      <c r="D115" s="10" t="n"/>
+      <c r="E115" s="10" t="n"/>
+      <c r="F115" s="10" t="n"/>
+      <c r="G115" s="10" t="n"/>
+      <c r="H115" s="10" t="n"/>
+      <c r="I115" s="10" t="n"/>
+      <c r="J115" s="10" t="n"/>
+      <c r="K115" s="10" t="n"/>
+      <c r="L115" s="10" t="n"/>
+      <c r="M115" s="10" t="n"/>
+      <c r="N115" s="10" t="n"/>
+      <c r="O115" s="10" t="n"/>
+      <c r="P115" s="10" t="n"/>
+      <c r="Q115" s="10" t="n"/>
+      <c r="R115" s="10" t="n"/>
+      <c r="S115" s="10" t="n"/>
+      <c r="T115" s="10" t="n"/>
+      <c r="U115" s="10" t="n"/>
+      <c r="V115" s="10" t="n"/>
+      <c r="W115" s="10" t="n"/>
+      <c r="X115" s="10" t="n"/>
+      <c r="Y115" s="10" t="n"/>
+      <c r="Z115" s="10" t="n"/>
+      <c r="AA115" s="10" t="n"/>
+      <c r="AB115" s="10" t="n"/>
+      <c r="AC115" s="10" t="n"/>
+      <c r="AD115" s="10" t="n"/>
+      <c r="AE115" s="10" t="n"/>
+      <c r="AF115" s="10" t="n"/>
+      <c r="AG115" s="10" t="n"/>
+      <c r="AH115" s="10" t="n"/>
+      <c r="AI115" s="10" t="n"/>
+      <c r="AJ115" s="10" t="n"/>
+      <c r="AK115" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="249">
+  <mergeCells count="283">
+    <mergeCell ref="B102:AK102"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="D78:AK78"/>
-    <mergeCell ref="Y36:AE36"/>
+    <mergeCell ref="C57:AK57"/>
+    <mergeCell ref="B62:I62"/>
     <mergeCell ref="T24:X24"/>
-    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="C66:AK66"/>
+    <mergeCell ref="D87:AK87"/>
     <mergeCell ref="Y45:AE45"/>
+    <mergeCell ref="T33:X33"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="C102:AK102"/>
     <mergeCell ref="D48:L48"/>
     <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M32:P32"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="C86:AK86"/>
-    <mergeCell ref="C108:AK108"/>
+    <mergeCell ref="Y32:AB32"/>
+    <mergeCell ref="T53:X53"/>
+    <mergeCell ref="B56:I56"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="M46:P46"/>
-    <mergeCell ref="C58:AK58"/>
+    <mergeCell ref="C108:AK108"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="D82:AK82"/>
     <mergeCell ref="M43:P43"/>
+    <mergeCell ref="Y52:AE52"/>
     <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="AF50:AK50"/>
+    <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
+    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C94:AK94"/>
+    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="C109:AK109"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
+    <mergeCell ref="D51:L51"/>
+    <mergeCell ref="AF52:AK52"/>
+    <mergeCell ref="Q1:U1"/>
     <mergeCell ref="C75:AK75"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C84:AK84"/>
+    <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="M35:P35"/>
-    <mergeCell ref="AF36:AK36"/>
+    <mergeCell ref="C114:AK114"/>
+    <mergeCell ref="A36:AK36"/>
     <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="M54:P54"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="J2:P3"/>
+    <mergeCell ref="B65:I65"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
-    <mergeCell ref="C37:C49"/>
+    <mergeCell ref="AF34:AK34"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="A78:AK78"/>
     <mergeCell ref="C95:AK95"/>
-    <mergeCell ref="D77:AK77"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="Y40:AE40"/>
+    <mergeCell ref="Y34:AB34"/>
     <mergeCell ref="AF49:AK49"/>
-    <mergeCell ref="C70:AK70"/>
-    <mergeCell ref="T37:X37"/>
-    <mergeCell ref="B91:AK91"/>
     <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="M33:P33"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="A21:AK21"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="AF44:AK44"/>
+    <mergeCell ref="B59:I59"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="M47:P47"/>
-    <mergeCell ref="C101:AK101"/>
+    <mergeCell ref="C32:L32"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="C38:L38"/>
+    <mergeCell ref="D53:L53"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="D47:L47"/>
     <mergeCell ref="AC29:AE29"/>
+    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="D37:L37"/>
+    <mergeCell ref="C104:AK104"/>
     <mergeCell ref="Q46:S46"/>
-    <mergeCell ref="C88:AK88"/>
-    <mergeCell ref="D89:AK89"/>
+    <mergeCell ref="AF51:AK51"/>
+    <mergeCell ref="T54:X54"/>
+    <mergeCell ref="Y53:AE53"/>
     <mergeCell ref="AC31:AE31"/>
+    <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="C24:L24"/>
-    <mergeCell ref="AF35:AK35"/>
-    <mergeCell ref="D39:L39"/>
+    <mergeCell ref="M44:P44"/>
+    <mergeCell ref="B112:AK112"/>
     <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="M44:P44"/>
+    <mergeCell ref="C33:L33"/>
     <mergeCell ref="Q48:S48"/>
-    <mergeCell ref="D79:AK79"/>
+    <mergeCell ref="D88:AK88"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="C103:AK103"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
-    <mergeCell ref="C55:AK55"/>
     <mergeCell ref="C99:AK99"/>
-    <mergeCell ref="D38:L38"/>
+    <mergeCell ref="Q32:S32"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="C26:L26"/>
-    <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y39:AE39"/>
-    <mergeCell ref="C35:L35"/>
+    <mergeCell ref="M51:P51"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="B104:AK104"/>
     <mergeCell ref="C25:L25"/>
-    <mergeCell ref="AF37:AK37"/>
+    <mergeCell ref="C115:AK115"/>
     <mergeCell ref="A2:I3"/>
+    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="C52:AK52"/>
     <mergeCell ref="B106:AK106"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="C61:AK61"/>
-    <mergeCell ref="D76:AK76"/>
     <mergeCell ref="T46:X46"/>
-    <mergeCell ref="B63:I63"/>
-    <mergeCell ref="C36:L36"/>
+    <mergeCell ref="B90:AK90"/>
+    <mergeCell ref="AF53:AK53"/>
+    <mergeCell ref="Q51:S51"/>
     <mergeCell ref="M27:P27"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="M36:P36"/>
-    <mergeCell ref="Y37:AE37"/>
+    <mergeCell ref="D52:L52"/>
+    <mergeCell ref="C72:AK72"/>
+    <mergeCell ref="AC33:AE33"/>
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="D49:L49"/>
+    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="B66:I66"/>
-    <mergeCell ref="C87:AK87"/>
+    <mergeCell ref="Q50:S50"/>
+    <mergeCell ref="T32:X32"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="Y33:AB33"/>
     <mergeCell ref="AF30:AK30"/>
+    <mergeCell ref="Q34:S34"/>
     <mergeCell ref="T42:X42"/>
+    <mergeCell ref="C28:L28"/>
     <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="C28:L28"/>
     <mergeCell ref="Y41:AE41"/>
     <mergeCell ref="T47:X47"/>
+    <mergeCell ref="M53:P53"/>
+    <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="AC34:AE34"/>
+    <mergeCell ref="M50:P50"/>
     <mergeCell ref="C98:AK98"/>
-    <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="C107:AK107"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="Q49:S49"/>
-    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="T50:X50"/>
+    <mergeCell ref="C89:AK89"/>
     <mergeCell ref="T44:X44"/>
-    <mergeCell ref="C64:AK64"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="M34:P34"/>
     <mergeCell ref="Y43:AE43"/>
+    <mergeCell ref="D94:AK94"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="C40:C54"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="M49:P49"/>
+    <mergeCell ref="C63:AK63"/>
     <mergeCell ref="M39:P39"/>
     <mergeCell ref="M48:P48"/>
+    <mergeCell ref="T51:X51"/>
+    <mergeCell ref="T26:X26"/>
     <mergeCell ref="C93:AK93"/>
-    <mergeCell ref="T26:X26"/>
-    <mergeCell ref="B69:I69"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="Y30:AB30"/>
-    <mergeCell ref="A73:AK73"/>
     <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="D54:L54"/>
     <mergeCell ref="T41:X41"/>
-    <mergeCell ref="Y35:AE35"/>
+    <mergeCell ref="C105:AK105"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="Y44:AE44"/>
-    <mergeCell ref="D80:AK80"/>
+    <mergeCell ref="B80:AK80"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AF43:AK43"/>
-    <mergeCell ref="C105:AK105"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="M31:P31"/>
+    <mergeCell ref="AC32:AE32"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="T43:X43"/>
     <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="D46:L46"/>
+    <mergeCell ref="T52:X52"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="T36:X36"/>
+    <mergeCell ref="Q54:S54"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="C67:AK67"/>
     <mergeCell ref="Y46:AE46"/>
     <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="M41:P41"/>
     <mergeCell ref="B96:AK96"/>
-    <mergeCell ref="A33:AK33"/>
+    <mergeCell ref="C111:AK111"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="B14:I19"/>
@@ -9239,8 +9754,9 @@
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="Y48:AE48"/>
+    <mergeCell ref="C69:AK69"/>
     <mergeCell ref="AC26:AE26"/>
-    <mergeCell ref="T35:X35"/>
+    <mergeCell ref="B71:I71"/>
     <mergeCell ref="C92:AK92"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="D43:L43"/>
@@ -9249,29 +9765,33 @@
     <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="C97:AK97"/>
     <mergeCell ref="Y47:AE47"/>
-    <mergeCell ref="B60:I60"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="D85:AK85"/>
     <mergeCell ref="AF47:AK47"/>
+    <mergeCell ref="M52:P52"/>
     <mergeCell ref="AC27:AE27"/>
-    <mergeCell ref="B74:AK74"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
+    <mergeCell ref="D50:L50"/>
+    <mergeCell ref="D84:AK84"/>
     <mergeCell ref="D44:L44"/>
+    <mergeCell ref="Q53:S53"/>
     <mergeCell ref="J15:M15"/>
+    <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="C90:AK90"/>
     <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="B85:AK85"/>
+    <mergeCell ref="C60:AK60"/>
+    <mergeCell ref="B110:AK110"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="C31:L31"/>
-    <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="D86:AK86"/>
+    <mergeCell ref="Y50:AE50"/>
     <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="M30:P30"/>
-    <mergeCell ref="B100:AK100"/>
+    <mergeCell ref="Q52:S52"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="D45:L45"/>
     <mergeCell ref="M28:P28"/>
@@ -9289,7 +9809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK108"/>
+  <dimension ref="A1:AK113"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -9450,7 +9970,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -9804,7 +10324,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -9856,7 +10376,7 @@
       <c r="M14" s="11" t="n"/>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>正常に単価を更新しました</t>
+          <t>更新しました</t>
         </is>
       </c>
       <c r="O14" s="10" t="n"/>
@@ -10557,7 +11077,7 @@
       <c r="S30" s="11" t="n"/>
       <c r="T30" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="U30" s="10" t="n"/>
@@ -10573,7 +11093,7 @@
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>適用開始日（YYYY-MM-DD）</t>
+          <t>適用開始日（YYYY-MM-DD）。必須</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -10617,7 +11137,7 @@
       <c r="S31" s="11" t="n"/>
       <c r="T31" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="U31" s="10" t="n"/>
@@ -10633,7 +11153,7 @@
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>適用終了日（YYYY-MM-DD）</t>
+          <t>適用終了日（YYYY-MM-DD）。必須、開始日以降</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -10642,211 +11162,207 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="19.5" customHeight="1"/>
-    <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="27" t="inlineStr">
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>biko</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="11" t="n"/>
+      <c r="Q32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="11" t="n"/>
+      <c r="T32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="11" t="n"/>
+      <c r="Y32" s="17" t="inlineStr"/>
+      <c r="Z32" s="10" t="n"/>
+      <c r="AA32" s="10" t="n"/>
+      <c r="AB32" s="11" t="n"/>
+      <c r="AC32" s="17" t="inlineStr"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="11" t="n"/>
+      <c r="AF32" s="19" t="inlineStr">
+        <is>
+          <t>備考。空欄可</t>
+        </is>
+      </c>
+      <c r="AG32" s="10" t="n"/>
+      <c r="AH32" s="10" t="n"/>
+      <c r="AI32" s="10" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
+      <c r="AK32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>active_flg</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="n"/>
+      <c r="J33" s="10" t="n"/>
+      <c r="K33" s="10" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="n"/>
+      <c r="O33" s="10" t="n"/>
+      <c r="P33" s="11" t="n"/>
+      <c r="Q33" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" s="10" t="n"/>
+      <c r="S33" s="11" t="n"/>
+      <c r="T33" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U33" s="10" t="n"/>
+      <c r="V33" s="10" t="n"/>
+      <c r="W33" s="10" t="n"/>
+      <c r="X33" s="11" t="n"/>
+      <c r="Y33" s="17" t="inlineStr"/>
+      <c r="Z33" s="10" t="n"/>
+      <c r="AA33" s="10" t="n"/>
+      <c r="AB33" s="11" t="n"/>
+      <c r="AC33" s="17" t="inlineStr"/>
+      <c r="AD33" s="10" t="n"/>
+      <c r="AE33" s="11" t="n"/>
+      <c r="AF33" s="19" t="inlineStr">
+        <is>
+          <t>運用上の有効フラグ</t>
+        </is>
+      </c>
+      <c r="AG33" s="10" t="n"/>
+      <c r="AH33" s="10" t="n"/>
+      <c r="AI33" s="10" t="n"/>
+      <c r="AJ33" s="10" t="n"/>
+      <c r="AK33" s="11" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>campaign_flg</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="10" t="n"/>
+      <c r="J34" s="10" t="n"/>
+      <c r="K34" s="10" t="n"/>
+      <c r="L34" s="11" t="n"/>
+      <c r="M34" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N34" s="10" t="n"/>
+      <c r="O34" s="10" t="n"/>
+      <c r="P34" s="11" t="n"/>
+      <c r="Q34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R34" s="10" t="n"/>
+      <c r="S34" s="11" t="n"/>
+      <c r="T34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U34" s="10" t="n"/>
+      <c r="V34" s="10" t="n"/>
+      <c r="W34" s="10" t="n"/>
+      <c r="X34" s="11" t="n"/>
+      <c r="Y34" s="17" t="inlineStr"/>
+      <c r="Z34" s="10" t="n"/>
+      <c r="AA34" s="10" t="n"/>
+      <c r="AB34" s="11" t="n"/>
+      <c r="AC34" s="17" t="inlineStr"/>
+      <c r="AD34" s="10" t="n"/>
+      <c r="AE34" s="11" t="n"/>
+      <c r="AF34" s="19" t="inlineStr">
+        <is>
+          <t>キャンペーンフラグ</t>
+        </is>
+      </c>
+      <c r="AG34" s="10" t="n"/>
+      <c r="AH34" s="10" t="n"/>
+      <c r="AI34" s="10" t="n"/>
+      <c r="AJ34" s="10" t="n"/>
+      <c r="AK34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="19.5" customHeight="1"/>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="19.5" customHeight="1"/>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="B35" s="30" t="inlineStr">
+    <row r="37" ht="19.5" customHeight="1"/>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
         </is>
       </c>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
-      <c r="H35" s="10" t="n"/>
-      <c r="I35" s="10" t="n"/>
-      <c r="J35" s="10" t="n"/>
-      <c r="K35" s="10" t="n"/>
-      <c r="L35" s="11" t="n"/>
-      <c r="M35" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N35" s="10" t="n"/>
-      <c r="O35" s="10" t="n"/>
-      <c r="P35" s="11" t="n"/>
-      <c r="Q35" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R35" s="10" t="n"/>
-      <c r="S35" s="11" t="n"/>
-      <c r="T35" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
-      <c r="U35" s="10" t="n"/>
-      <c r="V35" s="10" t="n"/>
-      <c r="W35" s="10" t="n"/>
-      <c r="X35" s="11" t="n"/>
-      <c r="Y35" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="Z35" s="10" t="n"/>
-      <c r="AA35" s="10" t="n"/>
-      <c r="AB35" s="10" t="n"/>
-      <c r="AC35" s="10" t="n"/>
-      <c r="AD35" s="10" t="n"/>
-      <c r="AE35" s="11" t="n"/>
-      <c r="AF35" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG35" s="10" t="n"/>
-      <c r="AH35" s="10" t="n"/>
-      <c r="AI35" s="10" t="n"/>
-      <c r="AJ35" s="10" t="n"/>
-      <c r="AK35" s="11" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="10" t="n"/>
-      <c r="H36" s="10" t="n"/>
-      <c r="I36" s="10" t="n"/>
-      <c r="J36" s="10" t="n"/>
-      <c r="K36" s="10" t="n"/>
-      <c r="L36" s="11" t="n"/>
-      <c r="M36" s="17" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="N36" s="10" t="n"/>
-      <c r="O36" s="10" t="n"/>
-      <c r="P36" s="11" t="n"/>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R36" s="10" t="n"/>
-      <c r="S36" s="11" t="n"/>
-      <c r="T36" s="17" t="inlineStr"/>
-      <c r="U36" s="10" t="n"/>
-      <c r="V36" s="10" t="n"/>
-      <c r="W36" s="10" t="n"/>
-      <c r="X36" s="11" t="n"/>
-      <c r="Y36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z36" s="10" t="n"/>
-      <c r="AA36" s="10" t="n"/>
-      <c r="AB36" s="10" t="n"/>
-      <c r="AC36" s="10" t="n"/>
-      <c r="AD36" s="10" t="n"/>
-      <c r="AE36" s="11" t="n"/>
-      <c r="AF36" s="19" t="inlineStr">
-        <is>
-          <t>更新された単価データ</t>
-        </is>
-      </c>
-      <c r="AG36" s="10" t="n"/>
-      <c r="AH36" s="10" t="n"/>
-      <c r="AI36" s="10" t="n"/>
-      <c r="AJ36" s="10" t="n"/>
-      <c r="AK36" s="11" t="n"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" s="37" t="n"/>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>tanka_id</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="10" t="n"/>
-      <c r="K37" s="10" t="n"/>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N37" s="10" t="n"/>
-      <c r="O37" s="10" t="n"/>
-      <c r="P37" s="11" t="n"/>
-      <c r="Q37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R37" s="10" t="n"/>
-      <c r="S37" s="11" t="n"/>
-      <c r="T37" s="17" t="inlineStr"/>
-      <c r="U37" s="10" t="n"/>
-      <c r="V37" s="10" t="n"/>
-      <c r="W37" s="10" t="n"/>
-      <c r="X37" s="11" t="n"/>
-      <c r="Y37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z37" s="10" t="n"/>
-      <c r="AA37" s="10" t="n"/>
-      <c r="AB37" s="10" t="n"/>
-      <c r="AC37" s="10" t="n"/>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="11" t="n"/>
-      <c r="AF37" s="19" t="inlineStr">
-        <is>
-          <t>単価ID</t>
-        </is>
-      </c>
-      <c r="AG37" s="10" t="n"/>
-      <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="10" t="n"/>
-      <c r="AJ37" s="10" t="n"/>
-      <c r="AK37" s="11" t="n"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="B38" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C38" s="38" t="n"/>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>ja_id</t>
-        </is>
-      </c>
+      <c r="D38" s="10" t="n"/>
       <c r="E38" s="10" t="n"/>
       <c r="F38" s="10" t="n"/>
       <c r="G38" s="10" t="n"/>
@@ -10855,29 +11371,33 @@
       <c r="J38" s="10" t="n"/>
       <c r="K38" s="10" t="n"/>
       <c r="L38" s="11" t="n"/>
-      <c r="M38" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N38" s="10" t="n"/>
       <c r="O38" s="10" t="n"/>
       <c r="P38" s="11" t="n"/>
-      <c r="Q38" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q38" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R38" s="10" t="n"/>
       <c r="S38" s="11" t="n"/>
-      <c r="T38" s="17" t="inlineStr"/>
+      <c r="T38" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U38" s="10" t="n"/>
       <c r="V38" s="10" t="n"/>
       <c r="W38" s="10" t="n"/>
       <c r="X38" s="11" t="n"/>
-      <c r="Y38" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y38" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z38" s="10" t="n"/>
@@ -10886,9 +11406,9 @@
       <c r="AC38" s="10" t="n"/>
       <c r="AD38" s="10" t="n"/>
       <c r="AE38" s="11" t="n"/>
-      <c r="AF38" s="19" t="inlineStr">
-        <is>
-          <t>JA ID</t>
+      <c r="AF38" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -10899,14 +11419,14 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C39" s="38" t="n"/>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>tanka_type</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n"/>
       <c r="E39" s="10" t="n"/>
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="10" t="n"/>
@@ -10917,7 +11437,7 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
@@ -10948,7 +11468,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>1: 購読料, 2: 配達手数料</t>
+          <t>更新された単価データ</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -10959,12 +11479,12 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C40" s="38" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C40" s="37" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>tanka_type_label</t>
+          <t>tanka_id</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -10977,7 +11497,7 @@
       <c r="L40" s="11" t="n"/>
       <c r="M40" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N40" s="10" t="n"/>
@@ -11008,7 +11528,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>tanka_typeのラベル</t>
+          <t>単価ID</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -11019,12 +11539,12 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>tanka_code</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -11037,7 +11557,7 @@
       <c r="L41" s="11" t="n"/>
       <c r="M41" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N41" s="10" t="n"/>
@@ -11068,7 +11588,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>単価コード , 編集しないでください。</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -11079,12 +11599,12 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>tanka_name</t>
+          <t>tanka_type</t>
         </is>
       </c>
       <c r="E42" s="10" t="n"/>
@@ -11097,7 +11617,7 @@
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N42" s="10" t="n"/>
@@ -11128,7 +11648,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>単価名</t>
+          <t>1: 購読料, 2: 配達手数料</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -11139,12 +11659,12 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>kingaku_zeikomi</t>
+          <t>tanka_code</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -11157,7 +11677,7 @@
       <c r="L43" s="11" t="n"/>
       <c r="M43" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N43" s="10" t="n"/>
@@ -11177,7 +11697,7 @@
       <c r="X43" s="11" t="n"/>
       <c r="Y43" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z43" s="10" t="n"/>
@@ -11188,7 +11708,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>税込金額（円）</t>
+          <t>単価コード , 編集しないでください。</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -11199,12 +11719,12 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>kingaku_zeinuki</t>
+          <t>tanka_name</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -11217,7 +11737,7 @@
       <c r="L44" s="11" t="n"/>
       <c r="M44" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N44" s="10" t="n"/>
@@ -11237,7 +11757,7 @@
       <c r="X44" s="11" t="n"/>
       <c r="Y44" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z44" s="10" t="n"/>
@@ -11248,7 +11768,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>税抜金額（円）</t>
+          <t>単価名</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -11259,12 +11779,12 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>tax_rate</t>
+          <t>kingaku_zeikomi</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
@@ -11290,11 +11810,7 @@
       </c>
       <c r="R45" s="10" t="n"/>
       <c r="S45" s="11" t="n"/>
-      <c r="T45" s="17" t="inlineStr">
-        <is>
-          <t>##.##</t>
-        </is>
-      </c>
+      <c r="T45" s="17" t="inlineStr"/>
       <c r="U45" s="10" t="n"/>
       <c r="V45" s="10" t="n"/>
       <c r="W45" s="10" t="n"/>
@@ -11312,7 +11828,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>税率（%）</t>
+          <t>税込金額（円）</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -11323,12 +11839,12 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>tekiyo_start_date</t>
+          <t>kingaku_zeinuki</t>
         </is>
       </c>
       <c r="E46" s="10" t="n"/>
@@ -11341,7 +11857,7 @@
       <c r="L46" s="11" t="n"/>
       <c r="M46" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N46" s="10" t="n"/>
@@ -11354,11 +11870,7 @@
       </c>
       <c r="R46" s="10" t="n"/>
       <c r="S46" s="11" t="n"/>
-      <c r="T46" s="17" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
+      <c r="T46" s="17" t="inlineStr"/>
       <c r="U46" s="10" t="n"/>
       <c r="V46" s="10" t="n"/>
       <c r="W46" s="10" t="n"/>
@@ -11376,7 +11888,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>適用開始日</t>
+          <t>税抜金額（円）</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -11387,12 +11899,12 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C47" s="38" t="n"/>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>tekiyo_end_date</t>
+          <t>tax_rate</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -11405,7 +11917,7 @@
       <c r="L47" s="11" t="n"/>
       <c r="M47" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N47" s="10" t="n"/>
@@ -11420,7 +11932,7 @@
       <c r="S47" s="11" t="n"/>
       <c r="T47" s="17" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>##.##</t>
         </is>
       </c>
       <c r="U47" s="10" t="n"/>
@@ -11440,7 +11952,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>適用終了日</t>
+          <t>税率（%）</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -11451,12 +11963,12 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C48" s="38" t="n"/>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>tekiyo_start_date</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
@@ -11484,7 +11996,7 @@
       <c r="S48" s="11" t="n"/>
       <c r="T48" s="17" t="inlineStr">
         <is>
-          <t>ISO8601</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="U48" s="10" t="n"/>
@@ -11493,7 +12005,7 @@
       <c r="X48" s="11" t="n"/>
       <c r="Y48" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z48" s="10" t="n"/>
@@ -11504,7 +12016,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>適用開始日</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -11515,12 +12027,12 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>14</v>
-      </c>
-      <c r="C49" s="39" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="C49" s="38" t="n"/>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>tekiyo_end_date</t>
         </is>
       </c>
       <c r="E49" s="10" t="n"/>
@@ -11548,7 +12060,7 @@
       <c r="S49" s="11" t="n"/>
       <c r="T49" s="17" t="inlineStr">
         <is>
-          <t>ISO8601</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="U49" s="10" t="n"/>
@@ -11568,7 +12080,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>適用終了日</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -11577,16 +12089,324 @@
       <c r="AJ49" s="10" t="n"/>
       <c r="AK49" s="11" t="n"/>
     </row>
-    <row r="50" ht="19.5" customHeight="1"/>
-    <row r="51" ht="19.5" customHeight="1">
-      <c r="B51" s="40" t="inlineStr">
+    <row r="50" ht="36" customHeight="1">
+      <c r="B50" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="C50" s="38" t="n"/>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>active_flg</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="n"/>
+      <c r="J50" s="10" t="n"/>
+      <c r="K50" s="10" t="n"/>
+      <c r="L50" s="11" t="n"/>
+      <c r="M50" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N50" s="10" t="n"/>
+      <c r="O50" s="10" t="n"/>
+      <c r="P50" s="11" t="n"/>
+      <c r="Q50" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="11" t="n"/>
+      <c r="T50" s="17" t="inlineStr"/>
+      <c r="U50" s="10" t="n"/>
+      <c r="V50" s="10" t="n"/>
+      <c r="W50" s="10" t="n"/>
+      <c r="X50" s="11" t="n"/>
+      <c r="Y50" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z50" s="10" t="n"/>
+      <c r="AA50" s="10" t="n"/>
+      <c r="AB50" s="10" t="n"/>
+      <c r="AC50" s="10" t="n"/>
+      <c r="AD50" s="10" t="n"/>
+      <c r="AE50" s="11" t="n"/>
+      <c r="AF50" s="19" t="inlineStr">
+        <is>
+          <t>運用上の有効フラグ（FALSE時は新規割当不可。適用期間とは独立）</t>
+        </is>
+      </c>
+      <c r="AG50" s="10" t="n"/>
+      <c r="AH50" s="10" t="n"/>
+      <c r="AI50" s="10" t="n"/>
+      <c r="AJ50" s="10" t="n"/>
+      <c r="AK50" s="11" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="C51" s="38" t="n"/>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>campaign_flg</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="10" t="n"/>
+      <c r="J51" s="10" t="n"/>
+      <c r="K51" s="10" t="n"/>
+      <c r="L51" s="11" t="n"/>
+      <c r="M51" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="10" t="n"/>
+      <c r="P51" s="11" t="n"/>
+      <c r="Q51" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="11" t="n"/>
+      <c r="T51" s="17" t="inlineStr"/>
+      <c r="U51" s="10" t="n"/>
+      <c r="V51" s="10" t="n"/>
+      <c r="W51" s="10" t="n"/>
+      <c r="X51" s="11" t="n"/>
+      <c r="Y51" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z51" s="10" t="n"/>
+      <c r="AA51" s="10" t="n"/>
+      <c r="AB51" s="10" t="n"/>
+      <c r="AC51" s="10" t="n"/>
+      <c r="AD51" s="10" t="n"/>
+      <c r="AE51" s="11" t="n"/>
+      <c r="AF51" s="19" t="inlineStr">
+        <is>
+          <t>キャンペーンフラグ（TRUE: 有効, FALSE: 無効）</t>
+        </is>
+      </c>
+      <c r="AG51" s="10" t="n"/>
+      <c r="AH51" s="10" t="n"/>
+      <c r="AI51" s="10" t="n"/>
+      <c r="AJ51" s="10" t="n"/>
+      <c r="AK51" s="11" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="19" t="inlineStr">
+        <is>
+          <t>biko</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="10" t="n"/>
+      <c r="J52" s="10" t="n"/>
+      <c r="K52" s="10" t="n"/>
+      <c r="L52" s="11" t="n"/>
+      <c r="M52" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N52" s="10" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="11" t="n"/>
+      <c r="Q52" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="11" t="n"/>
+      <c r="T52" s="17" t="inlineStr"/>
+      <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
+      <c r="W52" s="10" t="n"/>
+      <c r="X52" s="11" t="n"/>
+      <c r="Y52" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z52" s="10" t="n"/>
+      <c r="AA52" s="10" t="n"/>
+      <c r="AB52" s="10" t="n"/>
+      <c r="AC52" s="10" t="n"/>
+      <c r="AD52" s="10" t="n"/>
+      <c r="AE52" s="11" t="n"/>
+      <c r="AF52" s="19" t="inlineStr">
+        <is>
+          <t>備考（NOT NULL、空欄は `""`）</t>
+        </is>
+      </c>
+      <c r="AG52" s="10" t="n"/>
+      <c r="AH52" s="10" t="n"/>
+      <c r="AI52" s="10" t="n"/>
+      <c r="AJ52" s="10" t="n"/>
+      <c r="AK52" s="11" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="C53" s="38" t="n"/>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="10" t="n"/>
+      <c r="J53" s="10" t="n"/>
+      <c r="K53" s="10" t="n"/>
+      <c r="L53" s="11" t="n"/>
+      <c r="M53" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N53" s="10" t="n"/>
+      <c r="O53" s="10" t="n"/>
+      <c r="P53" s="11" t="n"/>
+      <c r="Q53" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="11" t="n"/>
+      <c r="T53" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U53" s="10" t="n"/>
+      <c r="V53" s="10" t="n"/>
+      <c r="W53" s="10" t="n"/>
+      <c r="X53" s="11" t="n"/>
+      <c r="Y53" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z53" s="10" t="n"/>
+      <c r="AA53" s="10" t="n"/>
+      <c r="AB53" s="10" t="n"/>
+      <c r="AC53" s="10" t="n"/>
+      <c r="AD53" s="10" t="n"/>
+      <c r="AE53" s="11" t="n"/>
+      <c r="AF53" s="19" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="AG53" s="10" t="n"/>
+      <c r="AH53" s="10" t="n"/>
+      <c r="AI53" s="10" t="n"/>
+      <c r="AJ53" s="10" t="n"/>
+      <c r="AK53" s="11" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="C54" s="39" t="n"/>
+      <c r="D54" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="n"/>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="11" t="n"/>
+      <c r="M54" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="11" t="n"/>
+      <c r="Q54" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="11" t="n"/>
+      <c r="T54" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="11" t="n"/>
+      <c r="Y54" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+      <c r="AC54" s="10" t="n"/>
+      <c r="AD54" s="10" t="n"/>
+      <c r="AE54" s="11" t="n"/>
+      <c r="AF54" s="19" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AG54" s="10" t="n"/>
+      <c r="AH54" s="10" t="n"/>
+      <c r="AI54" s="10" t="n"/>
+      <c r="AJ54" s="10" t="n"/>
+      <c r="AK54" s="11" t="n"/>
+    </row>
+    <row r="55" ht="19.5" customHeight="1"/>
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="B56" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="216" customHeight="1">
-      <c r="C52" s="19" t="inlineStr">
+    <row r="57" ht="270" customHeight="1">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>PUT /api/v1/tanka/1
 Content-Type: application/json
@@ -11597,61 +12417,63 @@
   "kingaku_zeikomi": 5200,
   "kingaku_zeinuki": 4727,
   "tekiyo_start_date": "2026-04-01",
-  "tekiyo_end_date": null
+  "tekiyo_end_date": null,
+  "active_flg": true,
+  "campaign_flg": false,
+  "biko": ""
 }</t>
         </is>
       </c>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
-      <c r="F52" s="10" t="n"/>
-      <c r="G52" s="10" t="n"/>
-      <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n"/>
-      <c r="J52" s="10" t="n"/>
-      <c r="K52" s="10" t="n"/>
-      <c r="L52" s="10" t="n"/>
-      <c r="M52" s="10" t="n"/>
-      <c r="N52" s="10" t="n"/>
-      <c r="O52" s="10" t="n"/>
-      <c r="P52" s="10" t="n"/>
-      <c r="Q52" s="10" t="n"/>
-      <c r="R52" s="10" t="n"/>
-      <c r="S52" s="10" t="n"/>
-      <c r="T52" s="10" t="n"/>
-      <c r="U52" s="10" t="n"/>
-      <c r="V52" s="10" t="n"/>
-      <c r="W52" s="10" t="n"/>
-      <c r="X52" s="10" t="n"/>
-      <c r="Y52" s="10" t="n"/>
-      <c r="Z52" s="10" t="n"/>
-      <c r="AA52" s="10" t="n"/>
-      <c r="AB52" s="10" t="n"/>
-      <c r="AC52" s="10" t="n"/>
-      <c r="AD52" s="10" t="n"/>
-      <c r="AE52" s="10" t="n"/>
-      <c r="AF52" s="10" t="n"/>
-      <c r="AG52" s="10" t="n"/>
-      <c r="AH52" s="10" t="n"/>
-      <c r="AI52" s="10" t="n"/>
-      <c r="AJ52" s="10" t="n"/>
-      <c r="AK52" s="11" t="n"/>
-    </row>
-    <row r="54" ht="19.5" customHeight="1">
-      <c r="B54" s="40" t="inlineStr">
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="10" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="10" t="n"/>
+      <c r="X57" s="10" t="n"/>
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="10" t="n"/>
+      <c r="AE57" s="10" t="n"/>
+      <c r="AF57" s="10" t="n"/>
+      <c r="AG57" s="10" t="n"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="10" t="n"/>
+      <c r="AJ57" s="10" t="n"/>
+      <c r="AK57" s="11" t="n"/>
+    </row>
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="B59" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="306" customHeight="1">
-      <c r="C55" s="19" t="inlineStr">
+    <row r="60" ht="342" customHeight="1">
+      <c r="C60" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
     "tanka_id": 1,
     "ja_id": 1,
     "tanka_type": 1,
-    "tanka_type_label": "新聞購読料",
     "tanka_code": "T001",
     "tanka_name": "基本購読料（月額）改定",
     "kingaku_zeikomi": 5200,
@@ -11659,56 +12481,59 @@
     "tax_rate": 10.0,
     "tekiyo_start_date": "2026-04-01",
     "tekiyo_end_date": null,
+    "active_flg": true,
+    "campaign_flg": false,
+    "biko": "",
     "created_at": "2026-01-15T10:00:00Z",
     "updated_at": "2026-04-09T14:30:00Z"
   }
 }</t>
         </is>
       </c>
-      <c r="D55" s="10" t="n"/>
-      <c r="E55" s="10" t="n"/>
-      <c r="F55" s="10" t="n"/>
-      <c r="G55" s="10" t="n"/>
-      <c r="H55" s="10" t="n"/>
-      <c r="I55" s="10" t="n"/>
-      <c r="J55" s="10" t="n"/>
-      <c r="K55" s="10" t="n"/>
-      <c r="L55" s="10" t="n"/>
-      <c r="M55" s="10" t="n"/>
-      <c r="N55" s="10" t="n"/>
-      <c r="O55" s="10" t="n"/>
-      <c r="P55" s="10" t="n"/>
-      <c r="Q55" s="10" t="n"/>
-      <c r="R55" s="10" t="n"/>
-      <c r="S55" s="10" t="n"/>
-      <c r="T55" s="10" t="n"/>
-      <c r="U55" s="10" t="n"/>
-      <c r="V55" s="10" t="n"/>
-      <c r="W55" s="10" t="n"/>
-      <c r="X55" s="10" t="n"/>
-      <c r="Y55" s="10" t="n"/>
-      <c r="Z55" s="10" t="n"/>
-      <c r="AA55" s="10" t="n"/>
-      <c r="AB55" s="10" t="n"/>
-      <c r="AC55" s="10" t="n"/>
-      <c r="AD55" s="10" t="n"/>
-      <c r="AE55" s="10" t="n"/>
-      <c r="AF55" s="10" t="n"/>
-      <c r="AG55" s="10" t="n"/>
-      <c r="AH55" s="10" t="n"/>
-      <c r="AI55" s="10" t="n"/>
-      <c r="AJ55" s="10" t="n"/>
-      <c r="AK55" s="11" t="n"/>
-    </row>
-    <row r="57" ht="19.5" customHeight="1">
-      <c r="B57" s="40" t="inlineStr">
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="10" t="n"/>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="10" t="n"/>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="10" t="n"/>
+      <c r="X60" s="10" t="n"/>
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="10" t="n"/>
+      <c r="AE60" s="10" t="n"/>
+      <c r="AF60" s="10" t="n"/>
+      <c r="AG60" s="10" t="n"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="10" t="n"/>
+      <c r="AJ60" s="10" t="n"/>
+      <c r="AK60" s="11" t="n"/>
+    </row>
+    <row r="62" ht="19.5" customHeight="1">
+      <c r="B62" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request）</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="90" customHeight="1">
-      <c r="C58" s="19" t="inlineStr">
+    <row r="63" ht="90" customHeight="1">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
@@ -11717,50 +12542,50 @@
 }</t>
         </is>
       </c>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
-      <c r="F58" s="10" t="n"/>
-      <c r="G58" s="10" t="n"/>
-      <c r="H58" s="10" t="n"/>
-      <c r="I58" s="10" t="n"/>
-      <c r="J58" s="10" t="n"/>
-      <c r="K58" s="10" t="n"/>
-      <c r="L58" s="10" t="n"/>
-      <c r="M58" s="10" t="n"/>
-      <c r="N58" s="10" t="n"/>
-      <c r="O58" s="10" t="n"/>
-      <c r="P58" s="10" t="n"/>
-      <c r="Q58" s="10" t="n"/>
-      <c r="R58" s="10" t="n"/>
-      <c r="S58" s="10" t="n"/>
-      <c r="T58" s="10" t="n"/>
-      <c r="U58" s="10" t="n"/>
-      <c r="V58" s="10" t="n"/>
-      <c r="W58" s="10" t="n"/>
-      <c r="X58" s="10" t="n"/>
-      <c r="Y58" s="10" t="n"/>
-      <c r="Z58" s="10" t="n"/>
-      <c r="AA58" s="10" t="n"/>
-      <c r="AB58" s="10" t="n"/>
-      <c r="AC58" s="10" t="n"/>
-      <c r="AD58" s="10" t="n"/>
-      <c r="AE58" s="10" t="n"/>
-      <c r="AF58" s="10" t="n"/>
-      <c r="AG58" s="10" t="n"/>
-      <c r="AH58" s="10" t="n"/>
-      <c r="AI58" s="10" t="n"/>
-      <c r="AJ58" s="10" t="n"/>
-      <c r="AK58" s="11" t="n"/>
-    </row>
-    <row r="60" ht="19.5" customHeight="1">
-      <c r="B60" s="40" t="inlineStr">
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="10" t="n"/>
+      <c r="J63" s="10" t="n"/>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="10" t="n"/>
+      <c r="Q63" s="10" t="n"/>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="10" t="n"/>
+      <c r="X63" s="10" t="n"/>
+      <c r="Y63" s="10" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="10" t="n"/>
+      <c r="AE63" s="10" t="n"/>
+      <c r="AF63" s="10" t="n"/>
+      <c r="AG63" s="10" t="n"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="10" t="n"/>
+      <c r="AJ63" s="10" t="n"/>
+      <c r="AK63" s="11" t="n"/>
+    </row>
+    <row r="65" ht="19.5" customHeight="1">
+      <c r="B65" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="72" customHeight="1">
-      <c r="C61" s="19" t="inlineStr">
+    <row r="66" ht="72" customHeight="1">
+      <c r="C66" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -11768,50 +12593,50 @@
 }</t>
         </is>
       </c>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="10" t="n"/>
-      <c r="F61" s="10" t="n"/>
-      <c r="G61" s="10" t="n"/>
-      <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="n"/>
-      <c r="J61" s="10" t="n"/>
-      <c r="K61" s="10" t="n"/>
-      <c r="L61" s="10" t="n"/>
-      <c r="M61" s="10" t="n"/>
-      <c r="N61" s="10" t="n"/>
-      <c r="O61" s="10" t="n"/>
-      <c r="P61" s="10" t="n"/>
-      <c r="Q61" s="10" t="n"/>
-      <c r="R61" s="10" t="n"/>
-      <c r="S61" s="10" t="n"/>
-      <c r="T61" s="10" t="n"/>
-      <c r="U61" s="10" t="n"/>
-      <c r="V61" s="10" t="n"/>
-      <c r="W61" s="10" t="n"/>
-      <c r="X61" s="10" t="n"/>
-      <c r="Y61" s="10" t="n"/>
-      <c r="Z61" s="10" t="n"/>
-      <c r="AA61" s="10" t="n"/>
-      <c r="AB61" s="10" t="n"/>
-      <c r="AC61" s="10" t="n"/>
-      <c r="AD61" s="10" t="n"/>
-      <c r="AE61" s="10" t="n"/>
-      <c r="AF61" s="10" t="n"/>
-      <c r="AG61" s="10" t="n"/>
-      <c r="AH61" s="10" t="n"/>
-      <c r="AI61" s="10" t="n"/>
-      <c r="AJ61" s="10" t="n"/>
-      <c r="AK61" s="11" t="n"/>
-    </row>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="B63" s="40" t="inlineStr">
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="10" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="10" t="n"/>
+      <c r="J66" s="10" t="n"/>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="10" t="n"/>
+      <c r="Q66" s="10" t="n"/>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="10" t="n"/>
+      <c r="X66" s="10" t="n"/>
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="10" t="n"/>
+      <c r="AD66" s="10" t="n"/>
+      <c r="AE66" s="10" t="n"/>
+      <c r="AF66" s="10" t="n"/>
+      <c r="AG66" s="10" t="n"/>
+      <c r="AH66" s="10" t="n"/>
+      <c r="AI66" s="10" t="n"/>
+      <c r="AJ66" s="10" t="n"/>
+      <c r="AK66" s="11" t="n"/>
+    </row>
+    <row r="68" ht="19.5" customHeight="1">
+      <c r="B68" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="72" customHeight="1">
-      <c r="C64" s="19" t="inlineStr">
+    <row r="69" ht="72" customHeight="1">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -11819,101 +12644,101 @@
 }</t>
         </is>
       </c>
-      <c r="D64" s="10" t="n"/>
-      <c r="E64" s="10" t="n"/>
-      <c r="F64" s="10" t="n"/>
-      <c r="G64" s="10" t="n"/>
-      <c r="H64" s="10" t="n"/>
-      <c r="I64" s="10" t="n"/>
-      <c r="J64" s="10" t="n"/>
-      <c r="K64" s="10" t="n"/>
-      <c r="L64" s="10" t="n"/>
-      <c r="M64" s="10" t="n"/>
-      <c r="N64" s="10" t="n"/>
-      <c r="O64" s="10" t="n"/>
-      <c r="P64" s="10" t="n"/>
-      <c r="Q64" s="10" t="n"/>
-      <c r="R64" s="10" t="n"/>
-      <c r="S64" s="10" t="n"/>
-      <c r="T64" s="10" t="n"/>
-      <c r="U64" s="10" t="n"/>
-      <c r="V64" s="10" t="n"/>
-      <c r="W64" s="10" t="n"/>
-      <c r="X64" s="10" t="n"/>
-      <c r="Y64" s="10" t="n"/>
-      <c r="Z64" s="10" t="n"/>
-      <c r="AA64" s="10" t="n"/>
-      <c r="AB64" s="10" t="n"/>
-      <c r="AC64" s="10" t="n"/>
-      <c r="AD64" s="10" t="n"/>
-      <c r="AE64" s="10" t="n"/>
-      <c r="AF64" s="10" t="n"/>
-      <c r="AG64" s="10" t="n"/>
-      <c r="AH64" s="10" t="n"/>
-      <c r="AI64" s="10" t="n"/>
-      <c r="AJ64" s="10" t="n"/>
-      <c r="AK64" s="11" t="n"/>
-    </row>
-    <row r="66" ht="19.5" customHeight="1">
-      <c r="B66" s="40" t="inlineStr">
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="10" t="n"/>
+      <c r="J69" s="10" t="n"/>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="10" t="n"/>
+      <c r="Q69" s="10" t="n"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="10" t="n"/>
+      <c r="X69" s="10" t="n"/>
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="10" t="n"/>
+      <c r="AD69" s="10" t="n"/>
+      <c r="AE69" s="10" t="n"/>
+      <c r="AF69" s="10" t="n"/>
+      <c r="AG69" s="10" t="n"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="10" t="n"/>
+      <c r="AJ69" s="10" t="n"/>
+      <c r="AK69" s="11" t="n"/>
+    </row>
+    <row r="71" ht="19.5" customHeight="1">
+      <c r="B71" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 404 Not Found）</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="72" customHeight="1">
-      <c r="C67" s="19" t="inlineStr">
+    <row r="72" ht="72" customHeight="1">
+      <c r="C72" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "TANKA_NOT_FOUND",
+  "error_code": "NOT_FOUND",
   "message": "指定された単価が見つかりません"
 }</t>
         </is>
       </c>
-      <c r="D67" s="10" t="n"/>
-      <c r="E67" s="10" t="n"/>
-      <c r="F67" s="10" t="n"/>
-      <c r="G67" s="10" t="n"/>
-      <c r="H67" s="10" t="n"/>
-      <c r="I67" s="10" t="n"/>
-      <c r="J67" s="10" t="n"/>
-      <c r="K67" s="10" t="n"/>
-      <c r="L67" s="10" t="n"/>
-      <c r="M67" s="10" t="n"/>
-      <c r="N67" s="10" t="n"/>
-      <c r="O67" s="10" t="n"/>
-      <c r="P67" s="10" t="n"/>
-      <c r="Q67" s="10" t="n"/>
-      <c r="R67" s="10" t="n"/>
-      <c r="S67" s="10" t="n"/>
-      <c r="T67" s="10" t="n"/>
-      <c r="U67" s="10" t="n"/>
-      <c r="V67" s="10" t="n"/>
-      <c r="W67" s="10" t="n"/>
-      <c r="X67" s="10" t="n"/>
-      <c r="Y67" s="10" t="n"/>
-      <c r="Z67" s="10" t="n"/>
-      <c r="AA67" s="10" t="n"/>
-      <c r="AB67" s="10" t="n"/>
-      <c r="AC67" s="10" t="n"/>
-      <c r="AD67" s="10" t="n"/>
-      <c r="AE67" s="10" t="n"/>
-      <c r="AF67" s="10" t="n"/>
-      <c r="AG67" s="10" t="n"/>
-      <c r="AH67" s="10" t="n"/>
-      <c r="AI67" s="10" t="n"/>
-      <c r="AJ67" s="10" t="n"/>
-      <c r="AK67" s="11" t="n"/>
-    </row>
-    <row r="69" ht="19.5" customHeight="1">
-      <c r="B69" s="40" t="inlineStr">
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="10" t="n"/>
+      <c r="J72" s="10" t="n"/>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="10" t="n"/>
+      <c r="Q72" s="10" t="n"/>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="10" t="n"/>
+      <c r="X72" s="10" t="n"/>
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="10" t="n"/>
+      <c r="AD72" s="10" t="n"/>
+      <c r="AE72" s="10" t="n"/>
+      <c r="AF72" s="10" t="n"/>
+      <c r="AG72" s="10" t="n"/>
+      <c r="AH72" s="10" t="n"/>
+      <c r="AI72" s="10" t="n"/>
+      <c r="AJ72" s="10" t="n"/>
+      <c r="AK72" s="11" t="n"/>
+    </row>
+    <row r="74" ht="19.5" customHeight="1">
+      <c r="B74" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="72" customHeight="1">
-      <c r="C70" s="19" t="inlineStr">
+    <row r="75" ht="72" customHeight="1">
+      <c r="C75" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -11921,177 +12746,214 @@
 }</t>
         </is>
       </c>
-      <c r="D70" s="10" t="n"/>
-      <c r="E70" s="10" t="n"/>
-      <c r="F70" s="10" t="n"/>
-      <c r="G70" s="10" t="n"/>
-      <c r="H70" s="10" t="n"/>
-      <c r="I70" s="10" t="n"/>
-      <c r="J70" s="10" t="n"/>
-      <c r="K70" s="10" t="n"/>
-      <c r="L70" s="10" t="n"/>
-      <c r="M70" s="10" t="n"/>
-      <c r="N70" s="10" t="n"/>
-      <c r="O70" s="10" t="n"/>
-      <c r="P70" s="10" t="n"/>
-      <c r="Q70" s="10" t="n"/>
-      <c r="R70" s="10" t="n"/>
-      <c r="S70" s="10" t="n"/>
-      <c r="T70" s="10" t="n"/>
-      <c r="U70" s="10" t="n"/>
-      <c r="V70" s="10" t="n"/>
-      <c r="W70" s="10" t="n"/>
-      <c r="X70" s="10" t="n"/>
-      <c r="Y70" s="10" t="n"/>
-      <c r="Z70" s="10" t="n"/>
-      <c r="AA70" s="10" t="n"/>
-      <c r="AB70" s="10" t="n"/>
-      <c r="AC70" s="10" t="n"/>
-      <c r="AD70" s="10" t="n"/>
-      <c r="AE70" s="10" t="n"/>
-      <c r="AF70" s="10" t="n"/>
-      <c r="AG70" s="10" t="n"/>
-      <c r="AH70" s="10" t="n"/>
-      <c r="AI70" s="10" t="n"/>
-      <c r="AJ70" s="10" t="n"/>
-      <c r="AK70" s="11" t="n"/>
-    </row>
-    <row r="72" ht="19.5" customHeight="1"/>
-    <row r="73" ht="19.5" customHeight="1">
-      <c r="A73" s="27" t="inlineStr">
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="10" t="n"/>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="10" t="n"/>
+      <c r="J75" s="10" t="n"/>
+      <c r="K75" s="10" t="n"/>
+      <c r="L75" s="10" t="n"/>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="10" t="n"/>
+      <c r="Q75" s="10" t="n"/>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
+      <c r="T75" s="10" t="n"/>
+      <c r="U75" s="10" t="n"/>
+      <c r="V75" s="10" t="n"/>
+      <c r="W75" s="10" t="n"/>
+      <c r="X75" s="10" t="n"/>
+      <c r="Y75" s="10" t="n"/>
+      <c r="Z75" s="10" t="n"/>
+      <c r="AA75" s="10" t="n"/>
+      <c r="AB75" s="10" t="n"/>
+      <c r="AC75" s="10" t="n"/>
+      <c r="AD75" s="10" t="n"/>
+      <c r="AE75" s="10" t="n"/>
+      <c r="AF75" s="10" t="n"/>
+      <c r="AG75" s="10" t="n"/>
+      <c r="AH75" s="10" t="n"/>
+      <c r="AI75" s="10" t="n"/>
+      <c r="AJ75" s="10" t="n"/>
+      <c r="AK75" s="11" t="n"/>
+    </row>
+    <row r="77" ht="19.5" customHeight="1"/>
+    <row r="78" ht="19.5" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="B74" s="27" t="inlineStr">
+    <row r="79" ht="54" customHeight="1">
+      <c r="B79" s="42" t="inlineStr">
+        <is>
+          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="10" t="n"/>
+      <c r="J79" s="10" t="n"/>
+      <c r="K79" s="10" t="n"/>
+      <c r="L79" s="10" t="n"/>
+      <c r="M79" s="10" t="n"/>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="10" t="n"/>
+      <c r="Q79" s="10" t="n"/>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="10" t="n"/>
+      <c r="T79" s="10" t="n"/>
+      <c r="U79" s="10" t="n"/>
+      <c r="V79" s="10" t="n"/>
+      <c r="W79" s="10" t="n"/>
+      <c r="X79" s="10" t="n"/>
+      <c r="Y79" s="10" t="n"/>
+      <c r="Z79" s="10" t="n"/>
+      <c r="AA79" s="10" t="n"/>
+      <c r="AB79" s="10" t="n"/>
+      <c r="AC79" s="10" t="n"/>
+      <c r="AD79" s="10" t="n"/>
+      <c r="AE79" s="10" t="n"/>
+      <c r="AF79" s="10" t="n"/>
+      <c r="AG79" s="10" t="n"/>
+      <c r="AH79" s="10" t="n"/>
+      <c r="AI79" s="10" t="n"/>
+      <c r="AJ79" s="10" t="n"/>
+      <c r="AK79" s="11" t="n"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="B80" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="C75" s="41" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="C81" s="41" t="inlineStr">
         <is>
           <t>パスパラメータ：tanka_id 数値型チェック、必須</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="C76" s="41" t="inlineStr">
+    <row r="82" ht="18" customHeight="1">
+      <c r="C82" s="41" t="inlineStr">
         <is>
           <t>リクエストボディ：</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="D77" s="41" t="inlineStr">
+    <row r="83" ht="18" customHeight="1">
+      <c r="D83" s="41" t="inlineStr">
         <is>
           <t>tanka_type：必須、1 または 2</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="D78" s="41" t="inlineStr">
+    <row r="84" ht="18" customHeight="1">
+      <c r="D84" s="41" t="inlineStr">
         <is>
           <t>tanka_name：必須、最大100桁</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="D79" s="41" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="D85" s="41" t="inlineStr">
         <is>
           <t>tax_rate：0〜100、小数点以下2桁</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="D80" s="41" t="inlineStr">
+    <row r="86" ht="18" customHeight="1">
+      <c r="D86" s="41" t="inlineStr">
         <is>
           <t>kingaku_zeikomi：≧ 0、数値</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="D81" s="41" t="inlineStr">
+    <row r="87" ht="18" customHeight="1">
+      <c r="D87" s="41" t="inlineStr">
         <is>
           <t>kingaku_zeinuki：≧ 0、数値</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="D82" s="41" t="inlineStr">
+    <row r="88" ht="18" customHeight="1">
+      <c r="D88" s="41" t="inlineStr">
         <is>
           <t>tekiyo_start_date：有効な日付形式。過去日の場合は変更不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="36" customHeight="1">
-      <c r="D83" s="41" t="inlineStr">
-        <is>
-          <t>tekiyo_end_date：有効な日付形式、tekiyo_start_date 以降。過去日の場合は変更不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="C84" s="41" t="inlineStr">
-        <is>
-          <t>バリデーションエラーの場合：HTTP 400 (`VALIDATION_ERROR`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="B85" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="C86" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="C87" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：`tanka.update` を保持しているか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="36" customHeight="1">
-      <c r="D88" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="C89" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
+          <t>バリデーションエラーの場合：HTTP 400 (`VALIDATION_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="B90" s="27" t="inlineStr">
         <is>
-          <t>4.3 対象レコードの存在確認</t>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="C91" s="41" t="inlineStr">
         <is>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="C92" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：`tanka.update` を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="36" customHeight="1">
+      <c r="D93" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="C94" s="41" t="inlineStr">
+        <is>
+          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="B95" s="27" t="inlineStr">
+        <is>
+          <t>4.3 対象レコードの存在確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="C96" s="41" t="inlineStr">
+        <is>
           <t>ログインユーザーのスコープを取得する（ja_id）。</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="72" customHeight="1">
-      <c r="C92" s="42" t="inlineStr">
+    <row r="97" ht="72" customHeight="1">
+      <c r="C97" s="42" t="inlineStr">
         <is>
           <t>SELECT * FROM m_tanka
 WHERE tanka_id = :tanka_id
@@ -12099,64 +12961,64 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D92" s="10" t="n"/>
-      <c r="E92" s="10" t="n"/>
-      <c r="F92" s="10" t="n"/>
-      <c r="G92" s="10" t="n"/>
-      <c r="H92" s="10" t="n"/>
-      <c r="I92" s="10" t="n"/>
-      <c r="J92" s="10" t="n"/>
-      <c r="K92" s="10" t="n"/>
-      <c r="L92" s="10" t="n"/>
-      <c r="M92" s="10" t="n"/>
-      <c r="N92" s="10" t="n"/>
-      <c r="O92" s="10" t="n"/>
-      <c r="P92" s="10" t="n"/>
-      <c r="Q92" s="10" t="n"/>
-      <c r="R92" s="10" t="n"/>
-      <c r="S92" s="10" t="n"/>
-      <c r="T92" s="10" t="n"/>
-      <c r="U92" s="10" t="n"/>
-      <c r="V92" s="10" t="n"/>
-      <c r="W92" s="10" t="n"/>
-      <c r="X92" s="10" t="n"/>
-      <c r="Y92" s="10" t="n"/>
-      <c r="Z92" s="10" t="n"/>
-      <c r="AA92" s="10" t="n"/>
-      <c r="AB92" s="10" t="n"/>
-      <c r="AC92" s="10" t="n"/>
-      <c r="AD92" s="10" t="n"/>
-      <c r="AE92" s="10" t="n"/>
-      <c r="AF92" s="10" t="n"/>
-      <c r="AG92" s="10" t="n"/>
-      <c r="AH92" s="10" t="n"/>
-      <c r="AI92" s="10" t="n"/>
-      <c r="AJ92" s="10" t="n"/>
-      <c r="AK92" s="11" t="n"/>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="C93" s="41" t="inlineStr">
-        <is>
-          <t>レコードが存在しない場合：HTTP 404 (`TANKA_NOT_FOUND`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="C94" s="41" t="inlineStr">
+      <c r="D97" s="10" t="n"/>
+      <c r="E97" s="10" t="n"/>
+      <c r="F97" s="10" t="n"/>
+      <c r="G97" s="10" t="n"/>
+      <c r="H97" s="10" t="n"/>
+      <c r="I97" s="10" t="n"/>
+      <c r="J97" s="10" t="n"/>
+      <c r="K97" s="10" t="n"/>
+      <c r="L97" s="10" t="n"/>
+      <c r="M97" s="10" t="n"/>
+      <c r="N97" s="10" t="n"/>
+      <c r="O97" s="10" t="n"/>
+      <c r="P97" s="10" t="n"/>
+      <c r="Q97" s="10" t="n"/>
+      <c r="R97" s="10" t="n"/>
+      <c r="S97" s="10" t="n"/>
+      <c r="T97" s="10" t="n"/>
+      <c r="U97" s="10" t="n"/>
+      <c r="V97" s="10" t="n"/>
+      <c r="W97" s="10" t="n"/>
+      <c r="X97" s="10" t="n"/>
+      <c r="Y97" s="10" t="n"/>
+      <c r="Z97" s="10" t="n"/>
+      <c r="AA97" s="10" t="n"/>
+      <c r="AB97" s="10" t="n"/>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="10" t="n"/>
+      <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="10" t="n"/>
+      <c r="AK97" s="11" t="n"/>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="C98" s="41" t="inlineStr">
+        <is>
+          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="C99" s="41" t="inlineStr">
         <is>
           <t>ja_id が一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="B95" s="27" t="inlineStr">
+    <row r="100" ht="18" customHeight="1">
+      <c r="B100" s="27" t="inlineStr">
         <is>
           <t>4.4 データ更新</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="252" customHeight="1">
-      <c r="C96" s="42" t="inlineStr">
+    <row r="101" ht="252" customHeight="1">
+      <c r="C101" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_tanka
 SET tanka_type = :tanka_type,
@@ -12172,132 +13034,6 @@
   AND ja_id = :ja_id
   AND deleted_at IS NULL
 RETURNING *</t>
-        </is>
-      </c>
-      <c r="D96" s="10" t="n"/>
-      <c r="E96" s="10" t="n"/>
-      <c r="F96" s="10" t="n"/>
-      <c r="G96" s="10" t="n"/>
-      <c r="H96" s="10" t="n"/>
-      <c r="I96" s="10" t="n"/>
-      <c r="J96" s="10" t="n"/>
-      <c r="K96" s="10" t="n"/>
-      <c r="L96" s="10" t="n"/>
-      <c r="M96" s="10" t="n"/>
-      <c r="N96" s="10" t="n"/>
-      <c r="O96" s="10" t="n"/>
-      <c r="P96" s="10" t="n"/>
-      <c r="Q96" s="10" t="n"/>
-      <c r="R96" s="10" t="n"/>
-      <c r="S96" s="10" t="n"/>
-      <c r="T96" s="10" t="n"/>
-      <c r="U96" s="10" t="n"/>
-      <c r="V96" s="10" t="n"/>
-      <c r="W96" s="10" t="n"/>
-      <c r="X96" s="10" t="n"/>
-      <c r="Y96" s="10" t="n"/>
-      <c r="Z96" s="10" t="n"/>
-      <c r="AA96" s="10" t="n"/>
-      <c r="AB96" s="10" t="n"/>
-      <c r="AC96" s="10" t="n"/>
-      <c r="AD96" s="10" t="n"/>
-      <c r="AE96" s="10" t="n"/>
-      <c r="AF96" s="10" t="n"/>
-      <c r="AG96" s="10" t="n"/>
-      <c r="AH96" s="10" t="n"/>
-      <c r="AI96" s="10" t="n"/>
-      <c r="AJ96" s="10" t="n"/>
-      <c r="AK96" s="11" t="n"/>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="B97" s="27" t="inlineStr">
-        <is>
-          <t>4.5 操作ログ記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="C98" s="41" t="inlineStr">
-        <is>
-          <t>更新前データを取得（4.3 のSELECT結果）し、`before_value` に格納する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="C99" s="41" t="inlineStr">
-        <is>
-          <t>以下のSQLを実行して操作ログを記録する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="216" customHeight="1">
-      <c r="C100" s="42" t="inlineStr">
-        <is>
-          <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
-                   gamen_name, operation, result_status,
-                   target_id, target_table,
-                   before_value, after_value,
-                   error_message, stack_trace,
-                   ip_address, user_agent)
-VALUES (1, NOW(), :account_id, :ja_id,
-        '単価マスタ登録画面 (ACSMS-SCR-003)', 'UPDATE', 1,
-        :tanka_id, 'm_tanka',
-        :before_value_json, :after_value_json,
-        '', '',
-        :ip_address, :user_agent)</t>
-        </is>
-      </c>
-      <c r="D100" s="10" t="n"/>
-      <c r="E100" s="10" t="n"/>
-      <c r="F100" s="10" t="n"/>
-      <c r="G100" s="10" t="n"/>
-      <c r="H100" s="10" t="n"/>
-      <c r="I100" s="10" t="n"/>
-      <c r="J100" s="10" t="n"/>
-      <c r="K100" s="10" t="n"/>
-      <c r="L100" s="10" t="n"/>
-      <c r="M100" s="10" t="n"/>
-      <c r="N100" s="10" t="n"/>
-      <c r="O100" s="10" t="n"/>
-      <c r="P100" s="10" t="n"/>
-      <c r="Q100" s="10" t="n"/>
-      <c r="R100" s="10" t="n"/>
-      <c r="S100" s="10" t="n"/>
-      <c r="T100" s="10" t="n"/>
-      <c r="U100" s="10" t="n"/>
-      <c r="V100" s="10" t="n"/>
-      <c r="W100" s="10" t="n"/>
-      <c r="X100" s="10" t="n"/>
-      <c r="Y100" s="10" t="n"/>
-      <c r="Z100" s="10" t="n"/>
-      <c r="AA100" s="10" t="n"/>
-      <c r="AB100" s="10" t="n"/>
-      <c r="AC100" s="10" t="n"/>
-      <c r="AD100" s="10" t="n"/>
-      <c r="AE100" s="10" t="n"/>
-      <c r="AF100" s="10" t="n"/>
-      <c r="AG100" s="10" t="n"/>
-      <c r="AH100" s="10" t="n"/>
-      <c r="AI100" s="10" t="n"/>
-      <c r="AJ100" s="10" t="n"/>
-      <c r="AK100" s="11" t="n"/>
-    </row>
-    <row r="101" ht="252" customHeight="1">
-      <c r="C101" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：更新前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
-{
-  "tanka_id": 1,
-  "ja_id": 1,
-  "tanka_type": 1,
-  "tanka_code": "T001",
-  "tanka_name": "基本購読料（月額）",
-  "kingaku_zeikomi": 4900,
-  "kingaku_zeinuki": 4455,
-  "tax_rate": 10.0,
-  "tekiyo_start_date": "2026-01-01",
-  "tekiyo_end_date": null
-}</t>
         </is>
       </c>
       <c r="D101" s="10" t="n"/>
@@ -12335,8 +13071,137 @@
       <c r="AJ101" s="10" t="n"/>
       <c r="AK101" s="11" t="n"/>
     </row>
-    <row r="102" ht="252" customHeight="1">
-      <c r="C102" s="42" t="inlineStr">
+    <row r="102" ht="18" customHeight="1">
+      <c r="B102" s="27" t="inlineStr">
+        <is>
+          <t>4.5 操作ログ記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="C103" s="41" t="inlineStr">
+        <is>
+          <t>更新前データを取得（4.3 のSELECT結果）し、`before_value` に格納する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="C104" s="41" t="inlineStr">
+        <is>
+          <t>以下のSQLを実行して操作ログを記録する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="216" customHeight="1">
+      <c r="C105" s="42" t="inlineStr">
+        <is>
+          <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
+                   gamen_name, operation, result_status,
+                   target_id, target_table,
+                   before_value, after_value,
+                   error_message, stack_trace,
+                   ip_address, user_agent)
+VALUES (1, NOW(), :account_id, :ja_id,
+        '単価マスタ登録画面 (ACSMS-SCR-003)', 'UPDATE', 1,
+        :tanka_id, 'm_tanka',
+        :before_value_json, :after_value_json,
+        '', '',
+        :ip_address, :user_agent)</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="n"/>
+      <c r="E105" s="10" t="n"/>
+      <c r="F105" s="10" t="n"/>
+      <c r="G105" s="10" t="n"/>
+      <c r="H105" s="10" t="n"/>
+      <c r="I105" s="10" t="n"/>
+      <c r="J105" s="10" t="n"/>
+      <c r="K105" s="10" t="n"/>
+      <c r="L105" s="10" t="n"/>
+      <c r="M105" s="10" t="n"/>
+      <c r="N105" s="10" t="n"/>
+      <c r="O105" s="10" t="n"/>
+      <c r="P105" s="10" t="n"/>
+      <c r="Q105" s="10" t="n"/>
+      <c r="R105" s="10" t="n"/>
+      <c r="S105" s="10" t="n"/>
+      <c r="T105" s="10" t="n"/>
+      <c r="U105" s="10" t="n"/>
+      <c r="V105" s="10" t="n"/>
+      <c r="W105" s="10" t="n"/>
+      <c r="X105" s="10" t="n"/>
+      <c r="Y105" s="10" t="n"/>
+      <c r="Z105" s="10" t="n"/>
+      <c r="AA105" s="10" t="n"/>
+      <c r="AB105" s="10" t="n"/>
+      <c r="AC105" s="10" t="n"/>
+      <c r="AD105" s="10" t="n"/>
+      <c r="AE105" s="10" t="n"/>
+      <c r="AF105" s="10" t="n"/>
+      <c r="AG105" s="10" t="n"/>
+      <c r="AH105" s="10" t="n"/>
+      <c r="AI105" s="10" t="n"/>
+      <c r="AJ105" s="10" t="n"/>
+      <c r="AK105" s="11" t="n"/>
+    </row>
+    <row r="106" ht="306" customHeight="1">
+      <c r="C106" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：更新前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+{
+  "tanka_id": 1,
+  "ja_id": 1,
+  "tanka_type": 1,
+  "tanka_code": "T001",
+  "tanka_name": "基本購読料（月額）",
+  "kingaku_zeikomi": 4900,
+  "kingaku_zeinuki": 4455,
+  "tax_rate": 10.0,
+  "tekiyo_start_date": "2026-01-01",
+  "tekiyo_end_date": null,
+  "active_flg": true,
+  "campaign_flg": false,
+  "biko": ""
+}</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="n"/>
+      <c r="E106" s="10" t="n"/>
+      <c r="F106" s="10" t="n"/>
+      <c r="G106" s="10" t="n"/>
+      <c r="H106" s="10" t="n"/>
+      <c r="I106" s="10" t="n"/>
+      <c r="J106" s="10" t="n"/>
+      <c r="K106" s="10" t="n"/>
+      <c r="L106" s="10" t="n"/>
+      <c r="M106" s="10" t="n"/>
+      <c r="N106" s="10" t="n"/>
+      <c r="O106" s="10" t="n"/>
+      <c r="P106" s="10" t="n"/>
+      <c r="Q106" s="10" t="n"/>
+      <c r="R106" s="10" t="n"/>
+      <c r="S106" s="10" t="n"/>
+      <c r="T106" s="10" t="n"/>
+      <c r="U106" s="10" t="n"/>
+      <c r="V106" s="10" t="n"/>
+      <c r="W106" s="10" t="n"/>
+      <c r="X106" s="10" t="n"/>
+      <c r="Y106" s="10" t="n"/>
+      <c r="Z106" s="10" t="n"/>
+      <c r="AA106" s="10" t="n"/>
+      <c r="AB106" s="10" t="n"/>
+      <c r="AC106" s="10" t="n"/>
+      <c r="AD106" s="10" t="n"/>
+      <c r="AE106" s="10" t="n"/>
+      <c r="AF106" s="10" t="n"/>
+      <c r="AG106" s="10" t="n"/>
+      <c r="AH106" s="10" t="n"/>
+      <c r="AI106" s="10" t="n"/>
+      <c r="AJ106" s="10" t="n"/>
+      <c r="AK106" s="11" t="n"/>
+    </row>
+    <row r="107" ht="306" customHeight="1">
+      <c r="C107" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve"> `after_value`：更新後のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
 {
@@ -12349,82 +13214,85 @@
   "kingaku_zeinuki": 4727,
   "tax_rate": 10.0,
   "tekiyo_start_date": "2026-04-01",
-  "tekiyo_end_date": null
+  "tekiyo_end_date": null,
+  "active_flg": true,
+  "campaign_flg": false,
+  "biko": ""
 }</t>
         </is>
       </c>
-      <c r="D102" s="10" t="n"/>
-      <c r="E102" s="10" t="n"/>
-      <c r="F102" s="10" t="n"/>
-      <c r="G102" s="10" t="n"/>
-      <c r="H102" s="10" t="n"/>
-      <c r="I102" s="10" t="n"/>
-      <c r="J102" s="10" t="n"/>
-      <c r="K102" s="10" t="n"/>
-      <c r="L102" s="10" t="n"/>
-      <c r="M102" s="10" t="n"/>
-      <c r="N102" s="10" t="n"/>
-      <c r="O102" s="10" t="n"/>
-      <c r="P102" s="10" t="n"/>
-      <c r="Q102" s="10" t="n"/>
-      <c r="R102" s="10" t="n"/>
-      <c r="S102" s="10" t="n"/>
-      <c r="T102" s="10" t="n"/>
-      <c r="U102" s="10" t="n"/>
-      <c r="V102" s="10" t="n"/>
-      <c r="W102" s="10" t="n"/>
-      <c r="X102" s="10" t="n"/>
-      <c r="Y102" s="10" t="n"/>
-      <c r="Z102" s="10" t="n"/>
-      <c r="AA102" s="10" t="n"/>
-      <c r="AB102" s="10" t="n"/>
-      <c r="AC102" s="10" t="n"/>
-      <c r="AD102" s="10" t="n"/>
-      <c r="AE102" s="10" t="n"/>
-      <c r="AF102" s="10" t="n"/>
-      <c r="AG102" s="10" t="n"/>
-      <c r="AH102" s="10" t="n"/>
-      <c r="AI102" s="10" t="n"/>
-      <c r="AJ102" s="10" t="n"/>
-      <c r="AK102" s="11" t="n"/>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="B103" s="27" t="inlineStr">
+      <c r="D107" s="10" t="n"/>
+      <c r="E107" s="10" t="n"/>
+      <c r="F107" s="10" t="n"/>
+      <c r="G107" s="10" t="n"/>
+      <c r="H107" s="10" t="n"/>
+      <c r="I107" s="10" t="n"/>
+      <c r="J107" s="10" t="n"/>
+      <c r="K107" s="10" t="n"/>
+      <c r="L107" s="10" t="n"/>
+      <c r="M107" s="10" t="n"/>
+      <c r="N107" s="10" t="n"/>
+      <c r="O107" s="10" t="n"/>
+      <c r="P107" s="10" t="n"/>
+      <c r="Q107" s="10" t="n"/>
+      <c r="R107" s="10" t="n"/>
+      <c r="S107" s="10" t="n"/>
+      <c r="T107" s="10" t="n"/>
+      <c r="U107" s="10" t="n"/>
+      <c r="V107" s="10" t="n"/>
+      <c r="W107" s="10" t="n"/>
+      <c r="X107" s="10" t="n"/>
+      <c r="Y107" s="10" t="n"/>
+      <c r="Z107" s="10" t="n"/>
+      <c r="AA107" s="10" t="n"/>
+      <c r="AB107" s="10" t="n"/>
+      <c r="AC107" s="10" t="n"/>
+      <c r="AD107" s="10" t="n"/>
+      <c r="AE107" s="10" t="n"/>
+      <c r="AF107" s="10" t="n"/>
+      <c r="AG107" s="10" t="n"/>
+      <c r="AH107" s="10" t="n"/>
+      <c r="AI107" s="10" t="n"/>
+      <c r="AJ107" s="10" t="n"/>
+      <c r="AK107" s="11" t="n"/>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="B108" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="C104" s="41" t="inlineStr">
+    <row r="109" ht="18" customHeight="1">
+      <c r="C109" s="41" t="inlineStr">
         <is>
           <t>更新されたデータをdata オブジェクトとして返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="B105" s="27" t="inlineStr">
+    <row r="110" ht="18" customHeight="1">
+      <c r="B110" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="C106" s="41" t="inlineStr">
+    <row r="111" ht="18" customHeight="1">
+      <c r="C111" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="C107" s="41" t="inlineStr">
+    <row r="112" ht="18" customHeight="1">
+      <c r="C112" s="41" t="inlineStr">
         <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="216" customHeight="1">
-      <c r="C108" s="42" t="inlineStr">
+    <row r="113" ht="216" customHeight="1">
+      <c r="C113" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -12440,246 +13308,270 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D108" s="10" t="n"/>
-      <c r="E108" s="10" t="n"/>
-      <c r="F108" s="10" t="n"/>
-      <c r="G108" s="10" t="n"/>
-      <c r="H108" s="10" t="n"/>
-      <c r="I108" s="10" t="n"/>
-      <c r="J108" s="10" t="n"/>
-      <c r="K108" s="10" t="n"/>
-      <c r="L108" s="10" t="n"/>
-      <c r="M108" s="10" t="n"/>
-      <c r="N108" s="10" t="n"/>
-      <c r="O108" s="10" t="n"/>
-      <c r="P108" s="10" t="n"/>
-      <c r="Q108" s="10" t="n"/>
-      <c r="R108" s="10" t="n"/>
-      <c r="S108" s="10" t="n"/>
-      <c r="T108" s="10" t="n"/>
-      <c r="U108" s="10" t="n"/>
-      <c r="V108" s="10" t="n"/>
-      <c r="W108" s="10" t="n"/>
-      <c r="X108" s="10" t="n"/>
-      <c r="Y108" s="10" t="n"/>
-      <c r="Z108" s="10" t="n"/>
-      <c r="AA108" s="10" t="n"/>
-      <c r="AB108" s="10" t="n"/>
-      <c r="AC108" s="10" t="n"/>
-      <c r="AD108" s="10" t="n"/>
-      <c r="AE108" s="10" t="n"/>
-      <c r="AF108" s="10" t="n"/>
-      <c r="AG108" s="10" t="n"/>
-      <c r="AH108" s="10" t="n"/>
-      <c r="AI108" s="10" t="n"/>
-      <c r="AJ108" s="10" t="n"/>
-      <c r="AK108" s="11" t="n"/>
+      <c r="D113" s="10" t="n"/>
+      <c r="E113" s="10" t="n"/>
+      <c r="F113" s="10" t="n"/>
+      <c r="G113" s="10" t="n"/>
+      <c r="H113" s="10" t="n"/>
+      <c r="I113" s="10" t="n"/>
+      <c r="J113" s="10" t="n"/>
+      <c r="K113" s="10" t="n"/>
+      <c r="L113" s="10" t="n"/>
+      <c r="M113" s="10" t="n"/>
+      <c r="N113" s="10" t="n"/>
+      <c r="O113" s="10" t="n"/>
+      <c r="P113" s="10" t="n"/>
+      <c r="Q113" s="10" t="n"/>
+      <c r="R113" s="10" t="n"/>
+      <c r="S113" s="10" t="n"/>
+      <c r="T113" s="10" t="n"/>
+      <c r="U113" s="10" t="n"/>
+      <c r="V113" s="10" t="n"/>
+      <c r="W113" s="10" t="n"/>
+      <c r="X113" s="10" t="n"/>
+      <c r="Y113" s="10" t="n"/>
+      <c r="Z113" s="10" t="n"/>
+      <c r="AA113" s="10" t="n"/>
+      <c r="AB113" s="10" t="n"/>
+      <c r="AC113" s="10" t="n"/>
+      <c r="AD113" s="10" t="n"/>
+      <c r="AE113" s="10" t="n"/>
+      <c r="AF113" s="10" t="n"/>
+      <c r="AG113" s="10" t="n"/>
+      <c r="AH113" s="10" t="n"/>
+      <c r="AI113" s="10" t="n"/>
+      <c r="AJ113" s="10" t="n"/>
+      <c r="AK113" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="248">
+  <mergeCells count="281">
+    <mergeCell ref="B102:AK102"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="D78:AK78"/>
-    <mergeCell ref="Y36:AE36"/>
+    <mergeCell ref="C57:AK57"/>
+    <mergeCell ref="B62:I62"/>
     <mergeCell ref="T24:X24"/>
-    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="C66:AK66"/>
+    <mergeCell ref="D87:AK87"/>
     <mergeCell ref="Y45:AE45"/>
+    <mergeCell ref="T33:X33"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="C102:AK102"/>
     <mergeCell ref="D48:L48"/>
     <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M32:P32"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="C86:AK86"/>
-    <mergeCell ref="C108:AK108"/>
+    <mergeCell ref="Y32:AB32"/>
+    <mergeCell ref="T53:X53"/>
+    <mergeCell ref="B56:I56"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="M46:P46"/>
-    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="D82:AK82"/>
     <mergeCell ref="M43:P43"/>
+    <mergeCell ref="Y52:AE52"/>
     <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="AF50:AK50"/>
+    <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="C100:AK100"/>
+    <mergeCell ref="C112:AK112"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="C91:AK91"/>
     <mergeCell ref="C94:AK94"/>
+    <mergeCell ref="C109:AK109"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
+    <mergeCell ref="D51:L51"/>
+    <mergeCell ref="AF52:AK52"/>
+    <mergeCell ref="Q1:U1"/>
     <mergeCell ref="C75:AK75"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C84:AK84"/>
+    <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="M35:P35"/>
-    <mergeCell ref="AF36:AK36"/>
+    <mergeCell ref="A36:AK36"/>
     <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="M54:P54"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="J2:P3"/>
+    <mergeCell ref="B65:I65"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
-    <mergeCell ref="C37:C49"/>
-    <mergeCell ref="D77:AK77"/>
+    <mergeCell ref="AF34:AK34"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="A78:AK78"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="Y40:AE40"/>
+    <mergeCell ref="Y34:AB34"/>
     <mergeCell ref="AF49:AK49"/>
-    <mergeCell ref="C70:AK70"/>
-    <mergeCell ref="T37:X37"/>
     <mergeCell ref="C106:AK106"/>
     <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="M33:P33"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="T30:X30"/>
+    <mergeCell ref="C107:AK107"/>
     <mergeCell ref="A21:AK21"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="AF44:AK44"/>
+    <mergeCell ref="B59:I59"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="M47:P47"/>
-    <mergeCell ref="C101:AK101"/>
+    <mergeCell ref="C32:L32"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="C38:L38"/>
+    <mergeCell ref="D53:L53"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="D47:L47"/>
     <mergeCell ref="AC29:AE29"/>
+    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q44:S44"/>
     <mergeCell ref="C104:AK104"/>
-    <mergeCell ref="D37:L37"/>
     <mergeCell ref="Q46:S46"/>
+    <mergeCell ref="AF51:AK51"/>
+    <mergeCell ref="T54:X54"/>
+    <mergeCell ref="Y53:AE53"/>
     <mergeCell ref="AC31:AE31"/>
-    <mergeCell ref="B103:AK103"/>
+    <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="C24:L24"/>
-    <mergeCell ref="AF35:AK35"/>
-    <mergeCell ref="D39:L39"/>
+    <mergeCell ref="M44:P44"/>
     <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="M44:P44"/>
+    <mergeCell ref="C33:L33"/>
     <mergeCell ref="Q48:S48"/>
-    <mergeCell ref="D79:AK79"/>
     <mergeCell ref="D88:AK88"/>
     <mergeCell ref="B13:I13"/>
+    <mergeCell ref="C103:AK103"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
-    <mergeCell ref="C55:AK55"/>
     <mergeCell ref="C99:AK99"/>
-    <mergeCell ref="D38:L38"/>
+    <mergeCell ref="Q32:S32"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="C26:L26"/>
-    <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y39:AE39"/>
-    <mergeCell ref="C35:L35"/>
+    <mergeCell ref="M51:P51"/>
     <mergeCell ref="B95:AK95"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
     <mergeCell ref="C25:L25"/>
-    <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="A2:I3"/>
+    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Y26:AB26"/>
-    <mergeCell ref="B97:AK97"/>
+    <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="C52:AK52"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="C61:AK61"/>
     <mergeCell ref="T46:X46"/>
-    <mergeCell ref="B63:I63"/>
     <mergeCell ref="B90:AK90"/>
-    <mergeCell ref="C36:L36"/>
+    <mergeCell ref="AF53:AK53"/>
+    <mergeCell ref="Q51:S51"/>
     <mergeCell ref="M27:P27"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="M36:P36"/>
-    <mergeCell ref="Y37:AE37"/>
+    <mergeCell ref="D52:L52"/>
+    <mergeCell ref="C72:AK72"/>
+    <mergeCell ref="AC33:AE33"/>
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="D49:L49"/>
+    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="Q50:S50"/>
     <mergeCell ref="C96:AK96"/>
-    <mergeCell ref="B66:I66"/>
-    <mergeCell ref="C87:AK87"/>
+    <mergeCell ref="T32:X32"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="Y33:AB33"/>
     <mergeCell ref="AF30:AK30"/>
+    <mergeCell ref="Q34:S34"/>
     <mergeCell ref="T42:X42"/>
+    <mergeCell ref="C28:L28"/>
     <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="C28:L28"/>
     <mergeCell ref="Y41:AE41"/>
     <mergeCell ref="T47:X47"/>
+    <mergeCell ref="M53:P53"/>
+    <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="AC34:AE34"/>
+    <mergeCell ref="M50:P50"/>
+    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="C98:AK98"/>
-    <mergeCell ref="AC25:AE25"/>
-    <mergeCell ref="C107:AK107"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="Q49:S49"/>
+    <mergeCell ref="T50:X50"/>
     <mergeCell ref="C89:AK89"/>
-    <mergeCell ref="Q36:S36"/>
     <mergeCell ref="T44:X44"/>
-    <mergeCell ref="C64:AK64"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="M34:P34"/>
     <mergeCell ref="Y43:AE43"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="C40:C54"/>
+    <mergeCell ref="B108:AK108"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="M49:P49"/>
+    <mergeCell ref="C63:AK63"/>
     <mergeCell ref="M39:P39"/>
     <mergeCell ref="M48:P48"/>
-    <mergeCell ref="C93:AK93"/>
+    <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
-    <mergeCell ref="B69:I69"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="Y30:AB30"/>
-    <mergeCell ref="A73:AK73"/>
     <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="D54:L54"/>
     <mergeCell ref="T41:X41"/>
-    <mergeCell ref="Y35:AE35"/>
+    <mergeCell ref="C105:AK105"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="Y44:AE44"/>
-    <mergeCell ref="D80:AK80"/>
+    <mergeCell ref="B80:AK80"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="M31:P31"/>
+    <mergeCell ref="AC32:AE32"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="T43:X43"/>
     <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="D46:L46"/>
+    <mergeCell ref="T52:X52"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="T36:X36"/>
+    <mergeCell ref="Q54:S54"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="C67:AK67"/>
     <mergeCell ref="Y46:AE46"/>
     <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="M41:P41"/>
-    <mergeCell ref="B105:AK105"/>
-    <mergeCell ref="A33:AK33"/>
+    <mergeCell ref="C111:AK111"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="B14:I19"/>
@@ -12688,37 +13580,46 @@
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="Y48:AE48"/>
+    <mergeCell ref="C69:AK69"/>
     <mergeCell ref="AC26:AE26"/>
-    <mergeCell ref="T35:X35"/>
+    <mergeCell ref="B71:I71"/>
     <mergeCell ref="C92:AK92"/>
+    <mergeCell ref="D93:AK93"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="D43:L43"/>
     <mergeCell ref="D83:AK83"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="Y42:AE42"/>
+    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="Y47:AE47"/>
-    <mergeCell ref="B60:I60"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="D85:AK85"/>
     <mergeCell ref="AF47:AK47"/>
+    <mergeCell ref="M52:P52"/>
     <mergeCell ref="AC27:AE27"/>
-    <mergeCell ref="B74:AK74"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
+    <mergeCell ref="D50:L50"/>
+    <mergeCell ref="D84:AK84"/>
     <mergeCell ref="D44:L44"/>
+    <mergeCell ref="Q53:S53"/>
     <mergeCell ref="J15:M15"/>
+    <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="B85:AK85"/>
+    <mergeCell ref="C60:AK60"/>
+    <mergeCell ref="B110:AK110"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="C31:L31"/>
-    <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="D86:AK86"/>
+    <mergeCell ref="Y50:AE50"/>
     <mergeCell ref="AC28:AE28"/>
-    <mergeCell ref="C76:AK76"/>
     <mergeCell ref="M30:P30"/>
+    <mergeCell ref="B100:AK100"/>
+    <mergeCell ref="Q52:S52"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="D45:L45"/>
     <mergeCell ref="M28:P28"/>

--- a/docs/design/ACSMS-SCR-003/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_単価マスタ登録画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-003/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_単価マスタ登録画面_V1.0.xlsx
@@ -1353,7 +1353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG3"/>
+  <dimension ref="A1:AG4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1572,15 +1572,78 @@
       <c r="AF3" s="10" t="n"/>
       <c r="AG3" s="11" t="n"/>
     </row>
+    <row r="4" ht="19.5" customHeight="1">
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="11" t="n"/>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="11" t="n"/>
+      <c r="R4" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件2026-08（バグ報告）：更新APIに「有効(active_flg=true)な単価は適用終了日が無し(無期限)または本日以降でなければならない」バリデーションを追加（4.1）。tanka-expireバッチは失効→無効の一方向のみで無効→有効の復帰はしないため、失効した単価を手動で有効へ戻す際に古い適用終了日を放置できてしまっていた不具合の修正</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="11" t="n"/>
+      <c r="W4" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="11" t="n"/>
+      <c r="AB4" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="28">
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
+    <mergeCell ref="R4:V4"/>
     <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="K4:Q4"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="W4:AA4"/>
     <mergeCell ref="W1:AA1"/>
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="H3:J3"/>
@@ -1591,8 +1654,11 @@
     <mergeCell ref="AB3:AG3"/>
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="H1:J1"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="H4:J4"/>
     <mergeCell ref="R2:V2"/>
+    <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="C3:G3"/>
   </mergeCells>
@@ -1767,7 +1833,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2193,7 +2259,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2761,7 +2827,7 @@
       <c r="U14" s="11" t="n"/>
       <c r="V14" s="19" t="inlineStr">
         <is>
-          <t>同一の単価コードが既に登録されています。</t>
+          <t>単価コード「{tanka_code}」はすでに登録されています。</t>
         </is>
       </c>
       <c r="W14" s="10" t="n"/>
@@ -3008,7 +3074,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3506,7 +3572,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4707,7 +4773,7 @@
       <c r="X34" s="11" t="n"/>
       <c r="Y34" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z34" s="10" t="n"/>
@@ -4767,7 +4833,7 @@
       <c r="X35" s="11" t="n"/>
       <c r="Y35" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z35" s="10" t="n"/>
@@ -4831,7 +4897,7 @@
       <c r="X36" s="11" t="n"/>
       <c r="Y36" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z36" s="10" t="n"/>
@@ -5766,10 +5832,10 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
+    <row r="81" ht="54" customHeight="1">
       <c r="C81" s="41" t="inlineStr">
         <is>
-          <t>ja_id が一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
+          <t>ja_id が一致しない場合：HTTP 404 (`NOT_FOUND`)（存在秘匿のため 403 DATA_SCOPE_VIOLATION ではなく NOT_FOUND を返す。`assertJaScope` 実装準拠）</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6242,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6730,7 +6796,7 @@
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>同一の単価コードが既に登録されています</t>
+          <t>単価コードが既に登録されています</t>
         </is>
       </c>
       <c r="O18" s="10" t="n"/>
@@ -7179,7 +7245,7 @@
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>税込金額（円）≧0。デフォルト: 0</t>
+          <t>税込金額（円）0〜9,999,999,999。デフォルト: 0</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -7239,7 +7305,7 @@
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>税抜金額（円）≧0。デフォルト: 0</t>
+          <t>税抜金額（円）0〜9,999,999,999。デフォルト: 0</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -8023,7 +8089,7 @@
       <c r="X45" s="11" t="n"/>
       <c r="Y45" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z45" s="10" t="n"/>
@@ -8083,7 +8149,7 @@
       <c r="X46" s="11" t="n"/>
       <c r="Y46" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z46" s="10" t="n"/>
@@ -8147,7 +8213,7 @@
       <c r="X47" s="11" t="n"/>
       <c r="Y47" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z47" s="10" t="n"/>
@@ -8673,7 +8739,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="342" customHeight="1">
+    <row r="60" ht="360" customHeight="1">
       <c r="C60" s="19" t="inlineStr">
         <is>
           <t>{
@@ -8693,7 +8759,8 @@
     "biko": "",
     "created_at": "2026-04-09T10:00:00Z",
     "updated_at": null
-  }
+  },
+  "message": "登録しました。"
 }</t>
         </is>
       </c>
@@ -8746,8 +8813,8 @@
   "error_code": "VALIDATION_ERROR",
   "message": "入力値が不正です。詳細はerrorsフィールドを確認してください",
   "errors": [
-    { "field": "tanka_code", "message": "単価コードは必須です" },
-    { "field": "tanka_name", "message": "単価名は必須です" }
+    { "field": "tanka_code", "message": "単価コードを入力してください。" },
+    { "field": "tanka_name", "message": "単価名を入力してください。" }
   ]
 }</t>
         </is>
@@ -8901,7 +8968,7 @@
         <is>
           <t>{
   "error_code": "DUPLICATE_CODE",
-  "message": "同一の単価コードが既に登録されています"
+  "message": "単価コード「T001」はすでに登録されています。"
 }</t>
         </is>
       </c>
@@ -9809,7 +9876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK113"/>
+  <dimension ref="A1:AK114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -9970,7 +10037,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -10973,7 +11040,7 @@
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>税込金額（円）</t>
+          <t>税込金額（円）0〜9,999,999,999</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -11033,7 +11100,7 @@
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>税抜金額（円）</t>
+          <t>税抜金額（円）0〜9,999,999,999</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -11817,7 +11884,7 @@
       <c r="X45" s="11" t="n"/>
       <c r="Y45" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z45" s="10" t="n"/>
@@ -11877,7 +11944,7 @@
       <c r="X46" s="11" t="n"/>
       <c r="Y46" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z46" s="10" t="n"/>
@@ -11941,7 +12008,7 @@
       <c r="X47" s="11" t="n"/>
       <c r="Y47" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z47" s="10" t="n"/>
@@ -12466,7 +12533,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="342" customHeight="1">
+    <row r="60" ht="360" customHeight="1">
       <c r="C60" s="19" t="inlineStr">
         <is>
           <t>{
@@ -12486,7 +12553,8 @@
     "biko": "",
     "created_at": "2026-01-15T10:00:00Z",
     "updated_at": "2026-04-09T14:30:00Z"
-  }
+  },
+  "message": "更新しました。"
 }</t>
         </is>
       </c>
@@ -12538,7 +12606,7 @@
           <t>{
   "error_code": "VALIDATION_ERROR",
   "message": "入力値が不正です。詳細はerrorsフィールドを確認してください",
-  "errors": [{ "field": "tanka_name", "message": "単価名は必須です" }]
+  "errors": [{ "field": "tanka_name", "message": "単価名を入力してください。" }]
 }</t>
         </is>
       </c>
@@ -12896,64 +12964,71 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="C89" s="41" t="inlineStr">
+    <row r="89" ht="36" customHeight="1">
+      <c r="D89" s="41" t="inlineStr">
+        <is>
+          <t>tekiyo_end_date：`active_flg`（有効）と組み合わせる場合、無し（無期限）または</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="C90" s="41" t="inlineStr">
         <is>
           <t>バリデーションエラーの場合：HTTP 400 (`VALIDATION_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="B90" s="27" t="inlineStr">
+    <row r="91" ht="18" customHeight="1">
+      <c r="B91" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="C91" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="C92" s="41" t="inlineStr">
         <is>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="C93" s="41" t="inlineStr">
+        <is>
           <t>権限チェック：`tanka.update` を保持しているか確認する。</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="36" customHeight="1">
-      <c r="D93" s="41" t="inlineStr">
+    <row r="94" ht="36" customHeight="1">
+      <c r="D94" s="41" t="inlineStr">
         <is>
           <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="C94" s="41" t="inlineStr">
+    <row r="95" ht="18" customHeight="1">
+      <c r="C95" s="41" t="inlineStr">
         <is>
           <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="B95" s="27" t="inlineStr">
+    <row r="96" ht="18" customHeight="1">
+      <c r="B96" s="27" t="inlineStr">
         <is>
           <t>4.3 対象レコードの存在確認</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="C96" s="41" t="inlineStr">
+    <row r="97" ht="18" customHeight="1">
+      <c r="C97" s="41" t="inlineStr">
         <is>
           <t>ログインユーザーのスコープを取得する（ja_id）。</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="72" customHeight="1">
-      <c r="C97" s="42" t="inlineStr">
+    <row r="98" ht="72" customHeight="1">
+      <c r="C98" s="42" t="inlineStr">
         <is>
           <t>SELECT * FROM m_tanka
 WHERE tanka_id = :tanka_id
@@ -12961,64 +13036,64 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D97" s="10" t="n"/>
-      <c r="E97" s="10" t="n"/>
-      <c r="F97" s="10" t="n"/>
-      <c r="G97" s="10" t="n"/>
-      <c r="H97" s="10" t="n"/>
-      <c r="I97" s="10" t="n"/>
-      <c r="J97" s="10" t="n"/>
-      <c r="K97" s="10" t="n"/>
-      <c r="L97" s="10" t="n"/>
-      <c r="M97" s="10" t="n"/>
-      <c r="N97" s="10" t="n"/>
-      <c r="O97" s="10" t="n"/>
-      <c r="P97" s="10" t="n"/>
-      <c r="Q97" s="10" t="n"/>
-      <c r="R97" s="10" t="n"/>
-      <c r="S97" s="10" t="n"/>
-      <c r="T97" s="10" t="n"/>
-      <c r="U97" s="10" t="n"/>
-      <c r="V97" s="10" t="n"/>
-      <c r="W97" s="10" t="n"/>
-      <c r="X97" s="10" t="n"/>
-      <c r="Y97" s="10" t="n"/>
-      <c r="Z97" s="10" t="n"/>
-      <c r="AA97" s="10" t="n"/>
-      <c r="AB97" s="10" t="n"/>
-      <c r="AC97" s="10" t="n"/>
-      <c r="AD97" s="10" t="n"/>
-      <c r="AE97" s="10" t="n"/>
-      <c r="AF97" s="10" t="n"/>
-      <c r="AG97" s="10" t="n"/>
-      <c r="AH97" s="10" t="n"/>
-      <c r="AI97" s="10" t="n"/>
-      <c r="AJ97" s="10" t="n"/>
-      <c r="AK97" s="11" t="n"/>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="C98" s="41" t="inlineStr">
-        <is>
-          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
-        </is>
-      </c>
+      <c r="D98" s="10" t="n"/>
+      <c r="E98" s="10" t="n"/>
+      <c r="F98" s="10" t="n"/>
+      <c r="G98" s="10" t="n"/>
+      <c r="H98" s="10" t="n"/>
+      <c r="I98" s="10" t="n"/>
+      <c r="J98" s="10" t="n"/>
+      <c r="K98" s="10" t="n"/>
+      <c r="L98" s="10" t="n"/>
+      <c r="M98" s="10" t="n"/>
+      <c r="N98" s="10" t="n"/>
+      <c r="O98" s="10" t="n"/>
+      <c r="P98" s="10" t="n"/>
+      <c r="Q98" s="10" t="n"/>
+      <c r="R98" s="10" t="n"/>
+      <c r="S98" s="10" t="n"/>
+      <c r="T98" s="10" t="n"/>
+      <c r="U98" s="10" t="n"/>
+      <c r="V98" s="10" t="n"/>
+      <c r="W98" s="10" t="n"/>
+      <c r="X98" s="10" t="n"/>
+      <c r="Y98" s="10" t="n"/>
+      <c r="Z98" s="10" t="n"/>
+      <c r="AA98" s="10" t="n"/>
+      <c r="AB98" s="10" t="n"/>
+      <c r="AC98" s="10" t="n"/>
+      <c r="AD98" s="10" t="n"/>
+      <c r="AE98" s="10" t="n"/>
+      <c r="AF98" s="10" t="n"/>
+      <c r="AG98" s="10" t="n"/>
+      <c r="AH98" s="10" t="n"/>
+      <c r="AI98" s="10" t="n"/>
+      <c r="AJ98" s="10" t="n"/>
+      <c r="AK98" s="11" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="C99" s="41" t="inlineStr">
         <is>
-          <t>ja_id が一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="B100" s="27" t="inlineStr">
+          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="54" customHeight="1">
+      <c r="C100" s="41" t="inlineStr">
+        <is>
+          <t>ja_id が一致しない場合：HTTP 404 (`NOT_FOUND`)（存在秘匿のため 403 DATA_SCOPE_VIOLATION ではなく NOT_FOUND を返す。`assertJaScope` 実装準拠）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="B101" s="27" t="inlineStr">
         <is>
           <t>4.4 データ更新</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="252" customHeight="1">
-      <c r="C101" s="42" t="inlineStr">
+    <row r="102" ht="252" customHeight="1">
+      <c r="C102" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_tanka
 SET tanka_type = :tanka_type,
@@ -13036,64 +13111,64 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D101" s="10" t="n"/>
-      <c r="E101" s="10" t="n"/>
-      <c r="F101" s="10" t="n"/>
-      <c r="G101" s="10" t="n"/>
-      <c r="H101" s="10" t="n"/>
-      <c r="I101" s="10" t="n"/>
-      <c r="J101" s="10" t="n"/>
-      <c r="K101" s="10" t="n"/>
-      <c r="L101" s="10" t="n"/>
-      <c r="M101" s="10" t="n"/>
-      <c r="N101" s="10" t="n"/>
-      <c r="O101" s="10" t="n"/>
-      <c r="P101" s="10" t="n"/>
-      <c r="Q101" s="10" t="n"/>
-      <c r="R101" s="10" t="n"/>
-      <c r="S101" s="10" t="n"/>
-      <c r="T101" s="10" t="n"/>
-      <c r="U101" s="10" t="n"/>
-      <c r="V101" s="10" t="n"/>
-      <c r="W101" s="10" t="n"/>
-      <c r="X101" s="10" t="n"/>
-      <c r="Y101" s="10" t="n"/>
-      <c r="Z101" s="10" t="n"/>
-      <c r="AA101" s="10" t="n"/>
-      <c r="AB101" s="10" t="n"/>
-      <c r="AC101" s="10" t="n"/>
-      <c r="AD101" s="10" t="n"/>
-      <c r="AE101" s="10" t="n"/>
-      <c r="AF101" s="10" t="n"/>
-      <c r="AG101" s="10" t="n"/>
-      <c r="AH101" s="10" t="n"/>
-      <c r="AI101" s="10" t="n"/>
-      <c r="AJ101" s="10" t="n"/>
-      <c r="AK101" s="11" t="n"/>
-    </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="B102" s="27" t="inlineStr">
+      <c r="D102" s="10" t="n"/>
+      <c r="E102" s="10" t="n"/>
+      <c r="F102" s="10" t="n"/>
+      <c r="G102" s="10" t="n"/>
+      <c r="H102" s="10" t="n"/>
+      <c r="I102" s="10" t="n"/>
+      <c r="J102" s="10" t="n"/>
+      <c r="K102" s="10" t="n"/>
+      <c r="L102" s="10" t="n"/>
+      <c r="M102" s="10" t="n"/>
+      <c r="N102" s="10" t="n"/>
+      <c r="O102" s="10" t="n"/>
+      <c r="P102" s="10" t="n"/>
+      <c r="Q102" s="10" t="n"/>
+      <c r="R102" s="10" t="n"/>
+      <c r="S102" s="10" t="n"/>
+      <c r="T102" s="10" t="n"/>
+      <c r="U102" s="10" t="n"/>
+      <c r="V102" s="10" t="n"/>
+      <c r="W102" s="10" t="n"/>
+      <c r="X102" s="10" t="n"/>
+      <c r="Y102" s="10" t="n"/>
+      <c r="Z102" s="10" t="n"/>
+      <c r="AA102" s="10" t="n"/>
+      <c r="AB102" s="10" t="n"/>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="10" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="10" t="n"/>
+      <c r="AK102" s="11" t="n"/>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="B103" s="27" t="inlineStr">
         <is>
           <t>4.5 操作ログ記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="C103" s="41" t="inlineStr">
-        <is>
-          <t>更新前データを取得（4.3 のSELECT結果）し、`before_value` に格納する。</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="C104" s="41" t="inlineStr">
         <is>
+          <t>更新前データを取得（4.3 のSELECT結果）し、`before_value` に格納する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="C105" s="41" t="inlineStr">
+        <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="216" customHeight="1">
-      <c r="C105" s="42" t="inlineStr">
+    <row r="106" ht="216" customHeight="1">
+      <c r="C106" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -13107,62 +13182,6 @@
         :before_value_json, :after_value_json,
         '', '',
         :ip_address, :user_agent)</t>
-        </is>
-      </c>
-      <c r="D105" s="10" t="n"/>
-      <c r="E105" s="10" t="n"/>
-      <c r="F105" s="10" t="n"/>
-      <c r="G105" s="10" t="n"/>
-      <c r="H105" s="10" t="n"/>
-      <c r="I105" s="10" t="n"/>
-      <c r="J105" s="10" t="n"/>
-      <c r="K105" s="10" t="n"/>
-      <c r="L105" s="10" t="n"/>
-      <c r="M105" s="10" t="n"/>
-      <c r="N105" s="10" t="n"/>
-      <c r="O105" s="10" t="n"/>
-      <c r="P105" s="10" t="n"/>
-      <c r="Q105" s="10" t="n"/>
-      <c r="R105" s="10" t="n"/>
-      <c r="S105" s="10" t="n"/>
-      <c r="T105" s="10" t="n"/>
-      <c r="U105" s="10" t="n"/>
-      <c r="V105" s="10" t="n"/>
-      <c r="W105" s="10" t="n"/>
-      <c r="X105" s="10" t="n"/>
-      <c r="Y105" s="10" t="n"/>
-      <c r="Z105" s="10" t="n"/>
-      <c r="AA105" s="10" t="n"/>
-      <c r="AB105" s="10" t="n"/>
-      <c r="AC105" s="10" t="n"/>
-      <c r="AD105" s="10" t="n"/>
-      <c r="AE105" s="10" t="n"/>
-      <c r="AF105" s="10" t="n"/>
-      <c r="AG105" s="10" t="n"/>
-      <c r="AH105" s="10" t="n"/>
-      <c r="AI105" s="10" t="n"/>
-      <c r="AJ105" s="10" t="n"/>
-      <c r="AK105" s="11" t="n"/>
-    </row>
-    <row r="106" ht="306" customHeight="1">
-      <c r="C106" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：更新前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
-{
-  "tanka_id": 1,
-  "ja_id": 1,
-  "tanka_type": 1,
-  "tanka_code": "T001",
-  "tanka_name": "基本購読料（月額）",
-  "kingaku_zeikomi": 4900,
-  "kingaku_zeinuki": 4455,
-  "tax_rate": 10.0,
-  "tekiyo_start_date": "2026-01-01",
-  "tekiyo_end_date": null,
-  "active_flg": true,
-  "campaign_flg": false,
-  "biko": ""
-}</t>
         </is>
       </c>
       <c r="D106" s="10" t="n"/>
@@ -13203,17 +13222,17 @@
     <row r="107" ht="306" customHeight="1">
       <c r="C107" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> `after_value`：更新後のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+          <t>`before_value`：更新前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
 {
   "tanka_id": 1,
   "ja_id": 1,
   "tanka_type": 1,
   "tanka_code": "T001",
-  "tanka_name": "基本購読料（月額）改定",
-  "kingaku_zeikomi": 5200,
-  "kingaku_zeinuki": 4727,
+  "tanka_name": "基本購読料（月額）",
+  "kingaku_zeikomi": 4900,
+  "kingaku_zeinuki": 4455,
   "tax_rate": 10.0,
-  "tekiyo_start_date": "2026-04-01",
+  "tekiyo_start_date": "2026-01-01",
   "tekiyo_end_date": null,
   "active_flg": true,
   "campaign_flg": false,
@@ -13256,43 +13275,99 @@
       <c r="AJ107" s="10" t="n"/>
       <c r="AK107" s="11" t="n"/>
     </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="B108" s="27" t="inlineStr">
+    <row r="108" ht="306" customHeight="1">
+      <c r="C108" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> `after_value`：更新後のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+{
+  "tanka_id": 1,
+  "ja_id": 1,
+  "tanka_type": 1,
+  "tanka_code": "T001",
+  "tanka_name": "基本購読料（月額）改定",
+  "kingaku_zeikomi": 5200,
+  "kingaku_zeinuki": 4727,
+  "tax_rate": 10.0,
+  "tekiyo_start_date": "2026-04-01",
+  "tekiyo_end_date": null,
+  "active_flg": true,
+  "campaign_flg": false,
+  "biko": ""
+}</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="n"/>
+      <c r="E108" s="10" t="n"/>
+      <c r="F108" s="10" t="n"/>
+      <c r="G108" s="10" t="n"/>
+      <c r="H108" s="10" t="n"/>
+      <c r="I108" s="10" t="n"/>
+      <c r="J108" s="10" t="n"/>
+      <c r="K108" s="10" t="n"/>
+      <c r="L108" s="10" t="n"/>
+      <c r="M108" s="10" t="n"/>
+      <c r="N108" s="10" t="n"/>
+      <c r="O108" s="10" t="n"/>
+      <c r="P108" s="10" t="n"/>
+      <c r="Q108" s="10" t="n"/>
+      <c r="R108" s="10" t="n"/>
+      <c r="S108" s="10" t="n"/>
+      <c r="T108" s="10" t="n"/>
+      <c r="U108" s="10" t="n"/>
+      <c r="V108" s="10" t="n"/>
+      <c r="W108" s="10" t="n"/>
+      <c r="X108" s="10" t="n"/>
+      <c r="Y108" s="10" t="n"/>
+      <c r="Z108" s="10" t="n"/>
+      <c r="AA108" s="10" t="n"/>
+      <c r="AB108" s="10" t="n"/>
+      <c r="AC108" s="10" t="n"/>
+      <c r="AD108" s="10" t="n"/>
+      <c r="AE108" s="10" t="n"/>
+      <c r="AF108" s="10" t="n"/>
+      <c r="AG108" s="10" t="n"/>
+      <c r="AH108" s="10" t="n"/>
+      <c r="AI108" s="10" t="n"/>
+      <c r="AJ108" s="10" t="n"/>
+      <c r="AK108" s="11" t="n"/>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="B109" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="C109" s="41" t="inlineStr">
+    <row r="110" ht="18" customHeight="1">
+      <c r="C110" s="41" t="inlineStr">
         <is>
           <t>更新されたデータをdata オブジェクトとして返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="B110" s="27" t="inlineStr">
+    <row r="111" ht="18" customHeight="1">
+      <c r="B111" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="C111" s="41" t="inlineStr">
-        <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="C112" s="41" t="inlineStr">
         <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="C113" s="41" t="inlineStr">
+        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="216" customHeight="1">
-      <c r="C113" s="42" t="inlineStr">
+    <row r="114" ht="216" customHeight="1">
+      <c r="C114" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -13308,44 +13383,43 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D113" s="10" t="n"/>
-      <c r="E113" s="10" t="n"/>
-      <c r="F113" s="10" t="n"/>
-      <c r="G113" s="10" t="n"/>
-      <c r="H113" s="10" t="n"/>
-      <c r="I113" s="10" t="n"/>
-      <c r="J113" s="10" t="n"/>
-      <c r="K113" s="10" t="n"/>
-      <c r="L113" s="10" t="n"/>
-      <c r="M113" s="10" t="n"/>
-      <c r="N113" s="10" t="n"/>
-      <c r="O113" s="10" t="n"/>
-      <c r="P113" s="10" t="n"/>
-      <c r="Q113" s="10" t="n"/>
-      <c r="R113" s="10" t="n"/>
-      <c r="S113" s="10" t="n"/>
-      <c r="T113" s="10" t="n"/>
-      <c r="U113" s="10" t="n"/>
-      <c r="V113" s="10" t="n"/>
-      <c r="W113" s="10" t="n"/>
-      <c r="X113" s="10" t="n"/>
-      <c r="Y113" s="10" t="n"/>
-      <c r="Z113" s="10" t="n"/>
-      <c r="AA113" s="10" t="n"/>
-      <c r="AB113" s="10" t="n"/>
-      <c r="AC113" s="10" t="n"/>
-      <c r="AD113" s="10" t="n"/>
-      <c r="AE113" s="10" t="n"/>
-      <c r="AF113" s="10" t="n"/>
-      <c r="AG113" s="10" t="n"/>
-      <c r="AH113" s="10" t="n"/>
-      <c r="AI113" s="10" t="n"/>
-      <c r="AJ113" s="10" t="n"/>
-      <c r="AK113" s="11" t="n"/>
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="10" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
+      <c r="H114" s="10" t="n"/>
+      <c r="I114" s="10" t="n"/>
+      <c r="J114" s="10" t="n"/>
+      <c r="K114" s="10" t="n"/>
+      <c r="L114" s="10" t="n"/>
+      <c r="M114" s="10" t="n"/>
+      <c r="N114" s="10" t="n"/>
+      <c r="O114" s="10" t="n"/>
+      <c r="P114" s="10" t="n"/>
+      <c r="Q114" s="10" t="n"/>
+      <c r="R114" s="10" t="n"/>
+      <c r="S114" s="10" t="n"/>
+      <c r="T114" s="10" t="n"/>
+      <c r="U114" s="10" t="n"/>
+      <c r="V114" s="10" t="n"/>
+      <c r="W114" s="10" t="n"/>
+      <c r="X114" s="10" t="n"/>
+      <c r="Y114" s="10" t="n"/>
+      <c r="Z114" s="10" t="n"/>
+      <c r="AA114" s="10" t="n"/>
+      <c r="AB114" s="10" t="n"/>
+      <c r="AC114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="10" t="n"/>
+      <c r="AF114" s="10" t="n"/>
+      <c r="AG114" s="10" t="n"/>
+      <c r="AH114" s="10" t="n"/>
+      <c r="AI114" s="10" t="n"/>
+      <c r="AJ114" s="10" t="n"/>
+      <c r="AK114" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="281">
-    <mergeCell ref="B102:AK102"/>
+  <mergeCells count="282">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
@@ -13360,6 +13434,7 @@
     <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="T33:X33"/>
     <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="C102:AK102"/>
     <mergeCell ref="D48:L48"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M32:P32"/>
@@ -13372,6 +13447,7 @@
     <mergeCell ref="B56:I56"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="M46:P46"/>
+    <mergeCell ref="C108:AK108"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="M43:P43"/>
@@ -13383,13 +13459,11 @@
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
+    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="C112:AK112"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C91:AK91"/>
-    <mergeCell ref="C94:AK94"/>
-    <mergeCell ref="C109:AK109"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
     <mergeCell ref="D51:L51"/>
@@ -13398,6 +13472,7 @@
     <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="B10:I10"/>
+    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="A36:AK36"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
@@ -13410,6 +13485,7 @@
     <mergeCell ref="B74:I74"/>
     <mergeCell ref="B68:I68"/>
     <mergeCell ref="A78:AK78"/>
+    <mergeCell ref="C95:AK95"/>
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
@@ -13418,12 +13494,12 @@
     <mergeCell ref="Y40:AE40"/>
     <mergeCell ref="Y34:AB34"/>
     <mergeCell ref="AF49:AK49"/>
+    <mergeCell ref="B91:AK91"/>
     <mergeCell ref="C106:AK106"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="T30:X30"/>
-    <mergeCell ref="C107:AK107"/>
     <mergeCell ref="A21:AK21"/>
     <mergeCell ref="C39:L39"/>
     <mergeCell ref="T29:X29"/>
@@ -13438,16 +13514,18 @@
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="D47:L47"/>
     <mergeCell ref="AC29:AE29"/>
-    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B101:AK101"/>
     <mergeCell ref="Q44:S44"/>
     <mergeCell ref="C104:AK104"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="T54:X54"/>
     <mergeCell ref="Y53:AE53"/>
+    <mergeCell ref="D89:AK89"/>
     <mergeCell ref="AC31:AE31"/>
     <mergeCell ref="AF32:AK32"/>
+    <mergeCell ref="B103:AK103"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="AF41:AK41"/>
@@ -13458,7 +13536,6 @@
     <mergeCell ref="Q48:S48"/>
     <mergeCell ref="D88:AK88"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="C103:AK103"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="C99:AK99"/>
@@ -13467,7 +13544,6 @@
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="M51:P51"/>
-    <mergeCell ref="B95:AK95"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
@@ -13480,7 +13556,6 @@
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="T46:X46"/>
-    <mergeCell ref="B90:AK90"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="M27:P27"/>
@@ -13495,7 +13570,6 @@
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="Q50:S50"/>
-    <mergeCell ref="C96:AK96"/>
     <mergeCell ref="T32:X32"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
@@ -13519,16 +13593,16 @@
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="Q49:S49"/>
     <mergeCell ref="T50:X50"/>
-    <mergeCell ref="C89:AK89"/>
+    <mergeCell ref="C107:AK107"/>
     <mergeCell ref="T44:X44"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M34:P34"/>
     <mergeCell ref="Y43:AE43"/>
+    <mergeCell ref="D94:AK94"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="AF31:AK31"/>
     <mergeCell ref="C40:C54"/>
-    <mergeCell ref="B108:AK108"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="C63:AK63"/>
@@ -13536,6 +13610,7 @@
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
+    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="N15:AK15"/>
@@ -13571,7 +13646,7 @@
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="M41:P41"/>
-    <mergeCell ref="C111:AK111"/>
+    <mergeCell ref="B96:AK96"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="B14:I19"/>
@@ -13584,7 +13659,7 @@
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="B71:I71"/>
     <mergeCell ref="C92:AK92"/>
-    <mergeCell ref="D93:AK93"/>
+    <mergeCell ref="B111:AK111"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="D43:L43"/>
     <mergeCell ref="D83:AK83"/>
@@ -13608,9 +13683,9 @@
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="C90:AK90"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="C60:AK60"/>
-    <mergeCell ref="B110:AK110"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="C31:L31"/>
@@ -13618,8 +13693,9 @@
     <mergeCell ref="Y50:AE50"/>
     <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="M30:P30"/>
-    <mergeCell ref="B100:AK100"/>
+    <mergeCell ref="C110:AK110"/>
     <mergeCell ref="Q52:S52"/>
+    <mergeCell ref="B109:AK109"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="D45:L45"/>
     <mergeCell ref="M28:P28"/>
